--- a/tame_output/ON/bt/strategyON_20240910.xlsx
+++ b/tame_output/ON/bt/strategyON_20240910.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-658.2%</t>
+          <t>-658.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -49437,10 +49437,10 @@
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.96613418283312</v>
+        <v>-4.965529870273931</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.513981063383785</v>
+        <v>2.514222788407461</v>
       </c>
       <c r="F2082" t="n">
         <v>0.8205009694579811</v>

--- a/tame_output/ON/bt/strategyON_20240910.xlsx
+++ b/tame_output/ON/bt/strategyON_20240910.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.6%</t>
+          <t>422.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-658.1%</t>
+          <t>-657.1%</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-124.8%</t>
+          <t>-124.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-318.9%</t>
+          <t>-327.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-141.9%</t>
+          <t>-134.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>105.0%</t>
+          <t>106.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>58.0%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.348717527443574</v>
+        <v>-6.299946152217899</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3282313838621604</v>
+        <v>0.3477399339524303</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.09241126744213063</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.783365233552654</v>
+        <v>2.812628058688059</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.182929331483283</v>
+        <v>-6.134157956257608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3875860501511834</v>
+        <v>0.4070946002414533</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.09241126744213063</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.776404621457561</v>
+        <v>2.805667446592966</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.149566125004514</v>
+        <v>-6.10079474977884</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4153936871238342</v>
+        <v>0.434902237214104</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.09241126744213063</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.790866975838704</v>
+        <v>2.820129800974109</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.041306987881993</v>
+        <v>-5.992535612656318</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4532294624320379</v>
+        <v>0.4727380125223077</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.09241126744213063</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.785399096297899</v>
+        <v>2.814661921433304</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.918015853064862</v>
+        <v>-5.869244477839187</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.500044010369467</v>
+        <v>0.5195525604597369</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.01789150785067445</v>
+        <v>0.03087986737499987</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.856871871198754</v>
+        <v>2.886134696334159</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.865318985933571</v>
+        <v>-5.816547610707896</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5288237354593086</v>
+        <v>0.5483322855495785</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.03480535928061673</v>
+        <v>0.08357673450629105</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.896190969714854</v>
+        <v>2.925453794850259</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.621553543950126</v>
+        <v>-5.572782168724451</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6221106205997371</v>
+        <v>0.641619170690007</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.03480535928061673</v>
+        <v>0.08357673450629105</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.891971678061905</v>
+        <v>2.92123450319731</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.531777871573654</v>
+        <v>-5.483006496347979</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6601452034703419</v>
+        <v>0.6796537535606118</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.09640480419492675</v>
+        <v>0.1451761794206011</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.931055658930507</v>
+        <v>2.960318484065912</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.281927477624579</v>
+        <v>-5.233156102398905</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.752827436033674</v>
+        <v>0.7723359861239438</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.09640480419492675</v>
+        <v>0.1451761794206011</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.923797733914209</v>
+        <v>2.953060559049614</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.106035385157147</v>
+        <v>-5.057264009931473</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8267833965412956</v>
+        <v>0.8462919466315655</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.09640480419492675</v>
+        <v>0.1451761794206011</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.927396857434858</v>
+        <v>2.956659682570263</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.934588922134684</v>
+        <v>-4.885817546909009</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9086894878048346</v>
+        <v>0.9281980378951045</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2678512672173899</v>
+        <v>0.3166226424430642</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.04359224130289</v>
+        <v>3.072855066438294</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.854566635025563</v>
+        <v>-4.805795259799888</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.93971888026478</v>
+        <v>0.9592274303550499</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3478735543265108</v>
+        <v>0.3966449295521852</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.090626091184659</v>
+        <v>3.119888916320064</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.790930892791629</v>
+        <v>-4.742159517565954</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9698679782126711</v>
+        <v>0.989376528302941</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4115092965604454</v>
+        <v>0.4602806717861197</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.133502337579337</v>
+        <v>3.162765162714742</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.697233574575233</v>
+        <v>-4.648462199349559</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9885411642830246</v>
+        <v>1.008049714373295</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4115092965604454</v>
+        <v>0.4602806717861197</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.114696596363133</v>
+        <v>3.143959421498538</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.707736197640522</v>
+        <v>-4.658964822414847</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9860831916817865</v>
+        <v>1.005591741772057</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4010066734951565</v>
+        <v>0.4497780487208308</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.110138099148837</v>
+        <v>3.139400924284241</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.595249936971648</v>
+        <v>-4.546478561745973</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.035007009784157</v>
+        <v>1.054515559874426</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4010066734951565</v>
+        <v>0.4497780487208308</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.114067412983657</v>
+        <v>3.143330238119062</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.577536250093782</v>
+        <v>-4.528764874868108</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.042771068452643</v>
+        <v>1.062279618542913</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4041880023920733</v>
+        <v>0.4529593776177476</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.116654794239147</v>
+        <v>3.145917619374552</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.454061978780764</v>
+        <v>-4.405290603555089</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.089158848197843</v>
+        <v>1.108667398288113</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4041880023920733</v>
+        <v>0.4529593776177476</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.113652865459141</v>
+        <v>3.142915690594545</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.234041180743754</v>
+        <v>-4.185269805518079</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.178746204423262</v>
+        <v>1.198254754513532</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5454078474600536</v>
+        <v>0.5941792226857279</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.199963809510543</v>
+        <v>3.229226634645948</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.101173491680476</v>
+        <v>-4.052402116454801</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.247787462850396</v>
+        <v>1.267296012940666</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5454078474600536</v>
+        <v>0.5941792226857279</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.215857992312366</v>
+        <v>3.245120817447771</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.981000408315977</v>
+        <v>-3.932229033090302</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.297002540636498</v>
+        <v>1.316511090726767</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6655809308245525</v>
+        <v>0.7143523060502268</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.289107686771367</v>
+        <v>3.318370511906772</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.845747046986</v>
+        <v>-3.796975671760325</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.361191987729928</v>
+        <v>1.380700537820198</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8008342921545296</v>
+        <v>0.8496056673802039</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.380347806130794</v>
+        <v>3.409610631266198</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.905621874343693</v>
+        <v>-3.856850499118018</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.323279548188277</v>
+        <v>1.342788098278547</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7409594647968375</v>
+        <v>0.7897308400225118</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.330460401117604</v>
+        <v>3.359723226253009</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.785801643432855</v>
+        <v>-3.73703026820718</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.386496809786821</v>
+        <v>1.406005359877091</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7409594647968375</v>
+        <v>0.7897308400225118</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.345749570351813</v>
+        <v>3.375012395487217</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.788271349894661</v>
+        <v>-3.739499974668986</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.29315312652454</v>
+        <v>1.31266167661481</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7384897583350314</v>
+        <v>0.7872611335607056</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.251911945797171</v>
+        <v>3.281174770932575</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.856641536218671</v>
+        <v>-3.807870160992996</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.185066913480237</v>
+        <v>1.204575463570507</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.7965368325969205</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.176739226704201</v>
+        <v>3.206002051839605</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.968513815844822</v>
+        <v>-3.919742440619147</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.130754710261668</v>
+        <v>1.150263260351938</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.7965368325969205</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.167175935336092</v>
+        <v>3.196438760471497</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.024033891737411</v>
+        <v>-3.975262516511736</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.245577516596835</v>
+        <v>1.265086066687105</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.7965368325969205</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.304206772028295</v>
+        <v>3.333469597163699</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.848559631944942</v>
+        <v>-3.799788256719267</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.32033445250561</v>
+        <v>1.33984300259588</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.7965368325969205</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.308774004020083</v>
+        <v>3.338036829155487</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.840635257360028</v>
+        <v>-3.791863882134353</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.299246231100783</v>
+        <v>1.318754781191053</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.7965368325969205</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.28451603278129</v>
+        <v>3.313778857916694</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.834357054790179</v>
+        <v>-3.785585679564504</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.230295825530172</v>
+        <v>1.249804375620442</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7540436599410953</v>
+        <v>0.8028150351667696</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.216821267724649</v>
+        <v>3.246084092860053</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.774504435586456</v>
+        <v>-3.725733060360781</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.264409259643794</v>
+        <v>1.283917809734064</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7540436599410953</v>
+        <v>0.8028150351667696</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.226993654156781</v>
+        <v>3.256256479292186</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.688260972560078</v>
+        <v>-3.639489597334403</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.293852915428205</v>
+        <v>1.313361465518475</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7540436599410953</v>
+        <v>0.8028150351667696</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.221939924730641</v>
+        <v>3.251202749866046</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.733567791959058</v>
+        <v>-3.684796416733383</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.267505963113139</v>
+        <v>1.287014513203409</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7132334969318646</v>
+        <v>0.7620048721575388</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.189229602369628</v>
+        <v>3.218492427505033</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.76260089666136</v>
+        <v>-3.713829521435685</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.25644459426532</v>
+        <v>1.27595314435559</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7132334969318646</v>
+        <v>0.7620048721575388</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.18978147540273</v>
+        <v>3.219044300538135</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.669790415210501</v>
+        <v>-3.621019039984826</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.222841478737029</v>
+        <v>1.242350028827299</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8060439783827239</v>
+        <v>0.8548153536083981</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.174740456164611</v>
+        <v>3.204003281300016</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.714179884539928</v>
+        <v>-3.665408509314253</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.206959166929859</v>
+        <v>1.226467717020129</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7616545090532962</v>
+        <v>0.8104258842789704</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.149980250491556</v>
+        <v>3.17924307562696</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.830721489645271</v>
+        <v>-3.781950114419596</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.155418233399445</v>
+        <v>1.174926783489715</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6451129039479535</v>
+        <v>0.6938842791736277</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.075130995940073</v>
+        <v>3.104393821075477</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.870645584227843</v>
+        <v>-3.821874209002168</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.144939891397083</v>
+        <v>1.164448441487353</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6451129039479535</v>
+        <v>0.6938842791736277</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.08062229177074</v>
+        <v>3.109885116906145</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.898425982129196</v>
+        <v>-3.849654606903521</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.145324934005081</v>
+        <v>1.164833484095351</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6173325060466004</v>
+        <v>0.6661038812722746</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.075451254798467</v>
+        <v>3.104714079933872</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.016806654859334</v>
+        <v>-3.968035279633659</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9363283849136792</v>
+        <v>0.9558369350039491</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5501146538956242</v>
+        <v>0.5988860291212984</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.873476263508535</v>
+        <v>2.902739088643939</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.125420733302665</v>
+        <v>-4.07664935807699</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.013032414255552</v>
+        <v>1.032540964345822</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5501146538956242</v>
+        <v>0.5988860291212984</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.99362592422774</v>
+        <v>3.022888749363145</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.090011695054522</v>
+        <v>-4.041240319828847</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.041709055657133</v>
+        <v>1.061217605747403</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5501146538956242</v>
+        <v>0.5988860291212984</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.008138950330063</v>
+        <v>3.037401775465468</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.051628032496371</v>
+        <v>-4.002856657270696</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.054481962022762</v>
+        <v>1.073990512113032</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5884983164537754</v>
+        <v>0.6372696916794496</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.028588589207323</v>
+        <v>3.057851414342728</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.874511702461205</v>
+        <v>-3.82574032723553</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.12205752288213</v>
+        <v>1.1415660729724</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5884983164537754</v>
+        <v>0.6372696916794496</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.025317618052625</v>
+        <v>3.054580443188029</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.919603947294751</v>
+        <v>-3.870832572069076</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.104704016710625</v>
+        <v>1.124212566800895</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5266022732843856</v>
+        <v>0.5753736485100598</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.988863383912904</v>
+        <v>3.018126209048309</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.740228526055983</v>
+        <v>-3.691457150830308</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.170241160512546</v>
+        <v>1.189749710602816</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6833790314551043</v>
+        <v>0.7321504066807785</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.07671641412175</v>
+        <v>3.105979239257154</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.785242739576589</v>
+        <v>-3.736471364350914</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.133042930435894</v>
+        <v>1.152551480526164</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6530301361404997</v>
+        <v>0.7018015113661739</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.039314532264576</v>
+        <v>3.068577357399981</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.052247249849025</v>
+        <v>-4.00347587462335</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.031932688665865</v>
+        <v>1.051441238756135</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4586670980975511</v>
+        <v>0.5074384733232253</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.928388271777753</v>
+        <v>2.957651096913158</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.153445031286197</v>
+        <v>-4.104673656060522</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9906574979874976</v>
+        <v>1.010166048077767</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3902582845522319</v>
+        <v>0.4390296597779061</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.886546905547063</v>
+        <v>2.915809730682468</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.146934064671885</v>
+        <v>-4.09816268944621</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9908618461875394</v>
+        <v>1.010370396277809</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3902582845522319</v>
+        <v>0.4390296597779061</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.88414686710138</v>
+        <v>2.913409692236784</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.127895936964587</v>
+        <v>-4.079124561738912</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9950018164787031</v>
+        <v>1.014510366568973</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3320746732210373</v>
+        <v>0.3808460484467116</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.845761419510908</v>
+        <v>2.875024244646312</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.180411739239408</v>
+        <v>-4.131640364013733</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.093289897202965</v>
+        <v>1.112798447293235</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3320746732210373</v>
+        <v>0.3808460484467116</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.965055821145098</v>
+        <v>2.994318646280503</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.194278500573326</v>
+        <v>-4.145507125347651</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.088576521655532</v>
+        <v>1.108085071745802</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2942167564872144</v>
+        <v>0.3429881317128887</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.943174400090938</v>
+        <v>2.972437225226343</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.153795508650981</v>
+        <v>-4.105024133425306</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.110778248821396</v>
+        <v>1.130286798911666</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2942167564872144</v>
+        <v>0.3429881317128887</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.949182930487864</v>
+        <v>2.978445755623269</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.006052538415979</v>
+        <v>-3.957281163190304</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.067825658192596</v>
+        <v>1.087334208282866</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4620241137220976</v>
+        <v>0.5107954889477718</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.947817566105993</v>
+        <v>2.977080391241398</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.089873759690677</v>
+        <v>-4.041102384465002</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.037090791214198</v>
+        <v>1.056599341304468</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4620241137220976</v>
+        <v>0.5107954889477718</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.950611187637474</v>
+        <v>2.979874012772879</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.083721053637893</v>
+        <v>-4.034949678412217</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.04021422202697</v>
+        <v>1.05972277211724</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4681768197748818</v>
+        <v>0.5169481950005561</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.954965159660803</v>
+        <v>2.984227984796208</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.100530351788395</v>
+        <v>-4.051758976562719</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.032570979506879</v>
+        <v>1.052079529597149</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4513675216243802</v>
+        <v>0.5001388968500544</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.943960057510613</v>
+        <v>2.973222882646017</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.038232353012273</v>
+        <v>-3.989460977786597</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.123825732814149</v>
+        <v>1.143334282904419</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4966617858988223</v>
+        <v>0.5454331611244965</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.037472169872099</v>
+        <v>3.066734995007503</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.836442155347115</v>
+        <v>-3.787670780121439</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.006833813594339</v>
+        <v>1.026342363684609</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6946799780679767</v>
+        <v>0.7434513532936509</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.958575086887719</v>
+        <v>2.987837912023123</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.887328868033309</v>
+        <v>-3.838557492807634</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.056769360842037</v>
+        <v>1.076277910932307</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6437932653817822</v>
+        <v>0.6925646406074564</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.998333291598177</v>
+        <v>3.027596116733581</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.800718125383502</v>
+        <v>-3.751946750157827</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.106041394018003</v>
+        <v>1.125549944108273</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7224189965869404</v>
+        <v>0.7711903718126146</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.060136466437315</v>
+        <v>3.08939929157272</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.860927423388786</v>
+        <v>-3.812156048163111</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.080493655640561</v>
+        <v>1.100002205730831</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6622096985816559</v>
+        <v>0.7109810738073301</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.022546868458817</v>
+        <v>3.051809693594221</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.811740774704435</v>
+        <v>-3.76296939947876</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.09865993315423</v>
+        <v>1.1181684832445</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6622096985816559</v>
+        <v>0.7109810738073301</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.021038486498745</v>
+        <v>3.05030131163415</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.767367643065866</v>
+        <v>-3.718596267840191</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.116272053245094</v>
+        <v>1.135780603335364</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7065828302202245</v>
+        <v>0.7553542054458987</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.047525232917323</v>
+        <v>3.076788058052727</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.789847993924751</v>
+        <v>-3.741076618699076</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.101673707040131</v>
+        <v>1.1211822571304</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7065828302202245</v>
+        <v>0.7553542054458987</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.041919027055913</v>
+        <v>3.071181852191318</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.742192263363695</v>
+        <v>-3.663988801384226</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.127117756292358</v>
+        <v>1.158399141084145</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7542385607812802</v>
+        <v>0.8324420227607489</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.076894222420351</v>
+        <v>3.123816299608032</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.641674104864941</v>
+        <v>-3.563470642885471</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.172217393066584</v>
+        <v>1.203498777858372</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8547567192800347</v>
+        <v>0.9329601812595034</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.142097490894328</v>
+        <v>3.18901956808201</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.625768775432588</v>
+        <v>-3.547565313453119</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.165334197315397</v>
+        <v>1.196615582107185</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7756440585707958</v>
+        <v>0.8538475205502645</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.081384566944657</v>
+        <v>3.128306644132339</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.58093037382419</v>
+        <v>-3.502726911844721</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.187367260569385</v>
+        <v>1.218648645361173</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7801874915156652</v>
+        <v>0.8583909534951339</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.088208329322208</v>
+        <v>3.135130406509889</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.600428830066198</v>
+        <v>-3.522225368086729</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.18372881770366</v>
+        <v>1.215010202495447</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7321028502357609</v>
+        <v>0.8103063122152296</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.063518484185343</v>
+        <v>3.110440561373024</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.556225992980298</v>
+        <v>-3.478022531000828</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.207289555065857</v>
+        <v>1.238570939857645</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7763056873216614</v>
+        <v>0.8545091493011301</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.095919788964721</v>
+        <v>3.142841866152402</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.563785658817345</v>
+        <v>-3.485582196837875</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.202675689200286</v>
+        <v>1.233957073992074</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8311090913314807</v>
+        <v>0.9093125533109494</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.12721183183986</v>
+        <v>3.174133909027541</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.405494241278073</v>
+        <v>-3.327290779298603</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.317240021399035</v>
+        <v>1.348521406190822</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8311090913314807</v>
+        <v>0.9093125533109494</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.178459597022899</v>
+        <v>3.22538167421058</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.197852237643596</v>
+        <v>-3.119648775664127</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.398737527447078</v>
+        <v>1.430018912238866</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.038751094965957</v>
+        <v>1.116954556945426</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.301485503797838</v>
+        <v>3.348407580985519</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.146820144921068</v>
+        <v>-3.068616682941599</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.414098592774359</v>
+        <v>1.445379977566147</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.089783187688485</v>
+        <v>1.167986649667954</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.327052987669625</v>
+        <v>3.373975064857306</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.081595963793863</v>
+        <v>-3.003392501814393</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.457375669317947</v>
+        <v>1.488657054109734</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.155007368815691</v>
+        <v>1.233210830795159</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.383374900438653</v>
+        <v>3.430296977626334</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.044168943722729</v>
+        <v>-2.96596548174326</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.46830744964568</v>
+        <v>1.499588834437468</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.160258906844872</v>
+        <v>1.238462368824341</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.382486795555443</v>
+        <v>3.429408872743124</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.064280599757437</v>
+        <v>-2.986077137777968</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.461519579563038</v>
+        <v>1.492800964354825</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.171286251842292</v>
+        <v>1.24948971382176</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.390359994885134</v>
+        <v>3.437282072072816</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.035867336657553</v>
+        <v>-2.957663874678084</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.633442655824202</v>
+        <v>1.664724040615989</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.112310689095863</v>
+        <v>1.190514151075331</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.515532428258488</v>
+        <v>3.562454505446169</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.961085075632541</v>
+        <v>-2.882881613653072</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.783468469452024</v>
+        <v>1.814749854243811</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.187092950120875</v>
+        <v>1.265296412100344</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.680514694091313</v>
+        <v>3.727436771278994</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.935000991368733</v>
+        <v>-2.856797529389264</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.785610079171406</v>
+        <v>1.816891463963193</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.187092950120875</v>
+        <v>1.265296412100344</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.672222670105172</v>
+        <v>3.719144747292853</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.847123078259612</v>
+        <v>-2.768919616280143</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.818954439998834</v>
+        <v>1.850235824790621</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.303018592544226</v>
+        <v>1.381222054523695</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.739971251142962</v>
+        <v>3.786893328330643</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.838230616866329</v>
+        <v>-2.76002715488686</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.840065830282939</v>
+        <v>1.871347215074726</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.303018592544226</v>
+        <v>1.381222054523695</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.757525656869753</v>
+        <v>3.804447734057435</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.006706733836207</v>
+        <v>-2.928503271856738</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.764530430899572</v>
+        <v>1.795811815691359</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.275070756827646</v>
+        <v>1.353274218807114</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.732612002844389</v>
+        <v>3.77953408003207</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782711</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.560450541206767</v>
+        <v>-2.482247079227298</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.924302605139209</v>
+        <v>1.955583989930997</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.180352087158013</v>
+        <v>1.258555549137482</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.657050498230471</v>
+        <v>3.703972575418152</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.537729437523614</v>
+        <v>-2.459525975544145</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.924055069109375</v>
+        <v>1.955336453901162</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.180352087158013</v>
+        <v>1.258555549137482</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.647714520727376</v>
+        <v>3.694636597915057</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.666931250817657</v>
+        <v>-2.588727788838188</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.031280469642927</v>
+        <v>2.062561854434714</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.051150273863971</v>
+        <v>1.129353735843439</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.729099558602119</v>
+        <v>3.7760216357898</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.692805649291683</v>
+        <v>-2.614602187312213</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.058008532746963</v>
+        <v>2.089289917538751</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.096061882575712</v>
+        <v>1.174265344555181</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.79312434632281</v>
+        <v>3.840046423510492</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799967</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.685750959076509</v>
+        <v>-2.60754749709704</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.057505764822578</v>
+        <v>2.088787149614365</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.103116572790886</v>
+        <v>1.181320034770354</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.79403251644146</v>
+        <v>3.840954593629141</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331118</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.658799734750021</v>
+        <v>-2.580596272770552</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.078292408197915</v>
+        <v>2.109573792989702</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.117996918818605</v>
+        <v>1.196200380798073</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.812966877702833</v>
+        <v>3.859888954890514</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.680343962580808</v>
+        <v>-2.602140500601339</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.253777849210559</v>
+        <v>2.285059234002347</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.117996918818605</v>
+        <v>1.196200380798073</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.997070009847793</v>
+        <v>4.043992087035474</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.70275208038568</v>
+        <v>-2.624548618406211</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.236931296991604</v>
+        <v>2.268212681783391</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.117996918818605</v>
+        <v>1.196200380798073</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.989186704750786</v>
+        <v>4.036108781938467</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.73097631596328</v>
+        <v>-2.652772853983811</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.227695602310201</v>
+        <v>2.258976987101988</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.135973671269913</v>
+        <v>1.214177133249382</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.002026755771208</v>
+        <v>4.04894883295889</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.74041724185181</v>
+        <v>-2.662213779872341</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.280172949676636</v>
+        <v>2.311454334468424</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.258400788813305</v>
+        <v>1.336604250792774</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.13173674401909</v>
+        <v>4.178658821206771</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.829293873020284</v>
+        <v>-2.751090411040815</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.247513391754548</v>
+        <v>2.278794776546335</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.169524157644831</v>
+        <v>1.2477276196243</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.081301859863307</v>
+        <v>4.128223937050988</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.90562385062119</v>
+        <v>-2.827420388641721</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.21509321360796</v>
+        <v>2.246374598399748</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.169524157644831</v>
+        <v>1.2477276196243</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.079413672757082</v>
+        <v>4.126335749944763</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.999287795298732</v>
+        <v>-2.921084333319262</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.172447865339806</v>
+        <v>2.203729250131594</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.07586021296729</v>
+        <v>1.154063674946758</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.01803553555342</v>
+        <v>4.064957612741101</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343068</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.160856220825987</v>
+        <v>-3.082652758846518</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.106254505339056</v>
+        <v>2.137535890130843</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9490772891694103</v>
+        <v>1.027280751148879</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.940399791484844</v>
+        <v>3.987321868672526</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389351</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.269156882696106</v>
+        <v>-3.190953420716637</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.076007647456927</v>
+        <v>2.107289032248715</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9490772891694103</v>
+        <v>1.027280751148879</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.953473198350763</v>
+        <v>4.000395275538444</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.28696085441685</v>
+        <v>-3.208757392437381</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.060891255551569</v>
+        <v>2.092172640343357</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8785426662642091</v>
+        <v>0.9567461282436778</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.903157621390582</v>
+        <v>3.950079698578263</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006978</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.314861641526323</v>
+        <v>-3.236658179546854</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.048254981834782</v>
+        <v>2.07953636662657</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8439457421212743</v>
+        <v>0.922149204100743</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.880923508031823</v>
+        <v>3.927845585219504</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787389</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.437387744229217</v>
+        <v>-3.359184282249748</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.996008984730824</v>
+        <v>2.027290369522611</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7214196394183804</v>
+        <v>0.7996231013978491</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.804172290387286</v>
+        <v>3.851094367574967</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.61934808158594</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.667902240414806</v>
+        <v>-3.589698778435337</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.970509145847092</v>
+        <v>2.001790530638879</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4909051432327917</v>
+        <v>0.5691086052122604</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.732569552266436</v>
+        <v>3.779491629454117</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814667</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.01664732563925</v>
+        <v>-3.93844386365978</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.971322830759161</v>
+        <v>2.002604215550948</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.4603606512933626</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.807632498916945</v>
+        <v>3.854554576104626</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.17063374341539</v>
+        <v>-4.092430281435921</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.978708532794345</v>
+        <v>2.009989917586132</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.4603606512933626</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.876612768062584</v>
+        <v>3.923534845250265</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.120111839587724</v>
+        <v>-4.041908377608255</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.984968496445532</v>
+        <v>2.016249881237319</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.4603606512933626</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.862663970182705</v>
+        <v>3.909586047370387</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.372586993595449</v>
+        <v>-4.29438353161598</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.895848923897856</v>
+        <v>1.927130308689644</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.4603606512933626</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.874534459238119</v>
+        <v>3.921456536425801</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67402853597316</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.665482750074861</v>
+        <v>-4.587279288095392</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.779901155825035</v>
+        <v>1.811182540616822</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.4603606512933626</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.875744993757063</v>
+        <v>3.922667070944744</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.852146878209669</v>
+        <v>-4.7739434162302</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.709357246798433</v>
+        <v>1.740638631590221</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.355418218489334</v>
+        <v>0.4336216804688027</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.863823353489649</v>
+        <v>3.91074543067733</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.998167565123631</v>
+        <v>-4.919964103144162</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.646026824769038</v>
+        <v>1.677308209560825</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.346335126695477</v>
+        <v>0.4245385886749457</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.853451351149524</v>
+        <v>3.900373428337205</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.089881574233217</v>
+        <v>-5.011678112253747</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.771545277824248</v>
+        <v>1.802826662616035</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.346335126695477</v>
+        <v>0.4245385886749457</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.015655407848568</v>
+        <v>4.062577485036249</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071553</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.121533233293186</v>
+        <v>-5.043329771313717</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.753731252164074</v>
+        <v>1.785012636955861</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3411666694510368</v>
+        <v>0.4193701314305055</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.007400971465718</v>
+        <v>4.054323048653399</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.203468051562069</v>
+        <v>-5.1252645895826</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.731186742425012</v>
+        <v>1.762468127216799</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3312319238639566</v>
+        <v>0.4094353858434253</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.011669541681961</v>
+        <v>4.058591618869642</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.305444173810477</v>
+        <v>-5.227240711831008</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.699321931981551</v>
+        <v>1.730603316773339</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.229255801615549</v>
+        <v>0.3074592635950177</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.959409506788819</v>
+        <v>4.0063315839765</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.195437890333255</v>
+        <v>-5.117234428353786</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.735477332616616</v>
+        <v>1.766758717408403</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2524603735328242</v>
+        <v>0.3306638355122929</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.965485137183359</v>
+        <v>4.012407214371041</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.052378314592329</v>
+        <v>-4.97417485261286</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.79695117363496</v>
+        <v>1.828232558426748</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2604738001228035</v>
+        <v>0.3386772621022722</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.974543203859321</v>
+        <v>4.021465281047003</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.750931589120492</v>
+        <v>-4.672728127141022</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.924790746706231</v>
+        <v>1.956072131498019</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5619205255946408</v>
+        <v>0.6401239875741095</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.16267212202496</v>
+        <v>4.209594199212641</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.775521833355675</v>
+        <v>-4.697318371376206</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.915925826764868</v>
+        <v>1.947207211556655</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5619205255946408</v>
+        <v>0.6401239875741095</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.16364329977767</v>
+        <v>4.210565376965351</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.724483457349155</v>
+        <v>-4.646279995369686</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.937184081547232</v>
+        <v>1.968465466339019</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5619205255946408</v>
+        <v>0.6401239875741095</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.164486204157425</v>
+        <v>4.211408281345107</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.683344162482524</v>
+        <v>-4.605140700503055</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.97267789836803</v>
+        <v>2.003959283159817</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6030598204612716</v>
+        <v>0.6812632824407403</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.20820787995155</v>
+        <v>4.255129957139231</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.586709250463884</v>
+        <v>-4.508505788484415</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.82751585929942</v>
+        <v>1.858797244091208</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6996947324799115</v>
+        <v>0.7778981944593802</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.082372823286669</v>
+        <v>4.129294900474349</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.717289984994727</v>
+        <v>-4.639086523015258</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.778785609561047</v>
+        <v>1.810066994352835</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.569113997949069</v>
+        <v>0.6473174599285377</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.007526426642126</v>
+        <v>4.054448503829808</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.552793650803765</v>
+        <v>-4.474590188824296</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.829010962313515</v>
+        <v>1.860292347105302</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7336103321400309</v>
+        <v>0.8118137941194996</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.090651046232787</v>
+        <v>4.137573123420467</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.475695049261892</v>
+        <v>-4.397491587282423</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.859038113366694</v>
+        <v>1.890319498158481</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7336103321400309</v>
+        <v>0.8118137941194996</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.089838756669216</v>
+        <v>4.136760833856897</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.486080244151782</v>
+        <v>-4.407876782172313</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.86475281453581</v>
+        <v>1.896034199327598</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7232251372501416</v>
+        <v>0.8014285992296103</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.093476418860355</v>
+        <v>4.140398496048036</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.504668402874007</v>
+        <v>-4.426464940894538</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.928154556823345</v>
+        <v>1.959435941615133</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7046369785279163</v>
+        <v>0.782840440507385</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.153160529403445</v>
+        <v>4.200082606591126</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.504966949570043</v>
+        <v>-4.426763487590573</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.924904148963229</v>
+        <v>1.956185533755017</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7043384318318804</v>
+        <v>0.7825418938113491</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.149850412204122</v>
+        <v>4.196772489391803</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.404143815879615</v>
+        <v>-4.325940353900146</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.969764297378792</v>
+        <v>2.001045682170579</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.7168026473162342</v>
+        <v>0.7950061092957029</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.161859836434125</v>
+        <v>4.208781913621807</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.213362455127208</v>
+        <v>-4.135158993147739</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.046206095158298</v>
+        <v>2.077487479950086</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9075840080686416</v>
+        <v>0.9857874700481103</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.276457906364113</v>
+        <v>4.323379983551795</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.106399097277786</v>
+        <v>-4.028195635298317</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.068828284035663</v>
+        <v>2.100109668827451</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9660486160284431</v>
+        <v>1.044252078007912</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.291373516877591</v>
+        <v>4.338295594065272</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.051068509376024</v>
+        <v>-3.972865047396555</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.125927455808426</v>
+        <v>2.157208840600214</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.021379203930205</v>
+        <v>1.099582665909674</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.359538806230707</v>
+        <v>4.406460883418387</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.039014382463061</v>
+        <v>-3.960810920483592</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.124435674475049</v>
+        <v>2.155717059266837</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.033433330843168</v>
+        <v>1.111636792822637</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.360457850279922</v>
+        <v>4.407379927467603</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.080169502031282</v>
+        <v>-4.001966040051814</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.109854256831897</v>
+        <v>2.141135641623684</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9922782112749471</v>
+        <v>1.070481673254416</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.337645408723125</v>
+        <v>4.384567485910806</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.012120939339752</v>
+        <v>-3.933917477360284</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.149924707786392</v>
+        <v>2.181206092578178</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.060326773966477</v>
+        <v>1.138530235945946</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.391325572215925</v>
+        <v>4.438247649403607</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.243721332509253</v>
+        <v>-4.165517870529785</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.077487220692185</v>
+        <v>2.108768605483972</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.060326773966477</v>
+        <v>1.138530235945946</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.41152824238952</v>
+        <v>4.458450319577201</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.293772878038472</v>
+        <v>-4.215569416059004</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.04107283854738</v>
+        <v>2.072354223339167</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.060326773966477</v>
+        <v>1.138530235945946</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.395134478456402</v>
+        <v>4.442056555644083</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.468879710614917</v>
+        <v>-4.390676248635449</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.931282019110268</v>
+        <v>1.962563403902055</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.060326773966477</v>
+        <v>1.138530235945946</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.355386392049868</v>
+        <v>4.40230846923755</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.437593690074461</v>
+        <v>-4.359390228094994</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.950819046323391</v>
+        <v>1.982100431115177</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.091612794506932</v>
+        <v>1.169816256486401</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.381180623371081</v>
+        <v>4.428102700558763</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.284568297961177</v>
+        <v>-4.206364835981709</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.111200202741609</v>
+        <v>2.142481587533395</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.244638186620216</v>
+        <v>1.322841648599685</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.572166858211957</v>
+        <v>4.619088935399637</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.312875611834447</v>
+        <v>-4.23467214985498</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.287343502100593</v>
+        <v>2.31862488689238</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.244638186620216</v>
+        <v>1.322841648599685</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.759633083120249</v>
+        <v>4.80655516030793</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.479468836947969</v>
+        <v>-4.401265374968502</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.190109163409267</v>
+        <v>2.221390548201053</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.078044961506694</v>
+        <v>1.156248423486163</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.629080099406218</v>
+        <v>4.676002176593899</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.456433043586403</v>
+        <v>-4.378229581606936</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.202999883415611</v>
+        <v>2.234281268207397</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.078044961506694</v>
+        <v>1.156248423486163</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.632756502067935</v>
+        <v>4.679678579255617</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.427187063130707</v>
+        <v>-4.348983601151239</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.212316330721385</v>
+        <v>2.243597715513171</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.078044961506694</v>
+        <v>1.156248423486163</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.630374557191431</v>
+        <v>4.677296634379112</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.534112611008558</v>
+        <v>-4.455909149029091</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.166839350727879</v>
+        <v>2.198120735519666</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9711194136288425</v>
+        <v>1.049322875608311</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.563512467622355</v>
+        <v>4.610434544810037</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.679131169515807</v>
+        <v>-4.600927707536339</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.110260729468214</v>
+        <v>2.141542114260001</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.8261008551215939</v>
+        <v>0.9043043171010627</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.47793013466124</v>
+        <v>4.524852211848922</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.797472935300524</v>
+        <v>-4.719269473321057</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.16285526241208</v>
+        <v>2.194136647203867</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9149903556639528</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.584272997056727</v>
+        <v>4.631195074244409</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.848883357621232</v>
+        <v>-4.770679895641765</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.140076790609736</v>
+        <v>2.171358175401522</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9149903556639528</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.582058694182666</v>
+        <v>4.628980771370347</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.928302808828984</v>
+        <v>-4.850099346849516</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.108212138200924</v>
+        <v>2.139493522992711</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9149903556639528</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.581961822256956</v>
+        <v>4.628883899444637</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.023765806746201</v>
+        <v>-4.945562344766734</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.070020832592081</v>
+        <v>2.101302217383867</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9149903556639528</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.581955715814999</v>
+        <v>4.628877793002681</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.959389895895487</v>
+        <v>-4.881186433916019</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.093867593494977</v>
+        <v>2.125148978286764</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.9011628045351991</v>
+        <v>0.979366266514668</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.618677658888038</v>
+        <v>4.66559973607572</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.01475905802768</v>
+        <v>-4.936555596048213</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.077453746389827</v>
+        <v>2.108735131181613</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.9011628045351991</v>
+        <v>0.979366266514668</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.624411476635765</v>
+        <v>4.671333553823446</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.060196837858507</v>
+        <v>-4.98199337587904</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.058816997800428</v>
+        <v>2.090098382592214</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.8583178138570395</v>
+        <v>0.9365212758365082</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.598242845571802</v>
+        <v>4.645164922759482</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.971990003710929</v>
+        <v>-4.893786541731462</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.113974124309778</v>
+        <v>2.145255509101565</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.8583178138570395</v>
+        <v>0.9365212758365082</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.618117238422121</v>
+        <v>4.665039315609802</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.86595500850562</v>
+        <v>-4.787751546526152</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.140088822916629</v>
+        <v>2.171370207708416</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.8583178138570395</v>
+        <v>0.9365212758365082</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.601817938946849</v>
+        <v>4.648740016134529</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.682743345372525</v>
+        <v>-4.604539883393057</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.215804437633913</v>
+        <v>2.2470858224257</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.8583178138570395</v>
+        <v>0.9365212758365082</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.604248888410894</v>
+        <v>4.651170965598575</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.611021898358674</v>
+        <v>-4.532818436379206</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.210284202287343</v>
+        <v>2.24156558707913</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.9300392608708902</v>
+        <v>1.008242722850359</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.613072942467094</v>
+        <v>4.659995019654775</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.588648872750968</v>
+        <v>-4.5104454107715</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.166149158451597</v>
+        <v>2.197430543243383</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.9412950119837917</v>
+        <v>1.01949847396326</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.566742139056006</v>
+        <v>4.613664216243688</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.621665168661712</v>
+        <v>-4.543461706682245</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.338140844972655</v>
+        <v>2.369422229764441</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.8718576353170402</v>
+        <v>0.9500610972965087</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.710277917941311</v>
+        <v>4.757199995128992</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.610137533012104</v>
+        <v>-4.531934071032636</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.334673125060747</v>
+        <v>2.365954509852534</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.9308582935184027</v>
+        <v>1.009061755497871</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.737599538690377</v>
+        <v>4.784521615878059</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.707479034354472</v>
+        <v>-4.629275572375005</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.299404637045588</v>
+        <v>2.330686021837375</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.8864381113529143</v>
+        <v>0.9646415733323828</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.714615541912873</v>
+        <v>4.761537619100555</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.793335063694439</v>
+        <v>-4.715131601714972</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.26631330750244</v>
+        <v>2.297594692294227</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.8440620421267793</v>
+        <v>0.9222655041062477</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.69044098257003</v>
+        <v>4.737363059757711</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.802171861110558</v>
+        <v>-4.723968399131091</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.245197790356494</v>
+        <v>2.27647917514828</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.8366198694854285</v>
+        <v>0.914823331464897</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.668394880805722</v>
+        <v>4.715316957993402</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.893554423676017</v>
+        <v>-4.81535096169655</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.21880927637536</v>
+        <v>2.250090661167147</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.7452373069199703</v>
+        <v>0.8234407688994387</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.623729854311496</v>
+        <v>4.670651931499177</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.881847705689011</v>
+        <v>-4.803644243709543</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.325620221394431</v>
+        <v>2.356901606186217</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.7569440249069767</v>
+        <v>0.8351474868864451</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.732882142927968</v>
+        <v>4.779804220115649</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.782184201605348</v>
+        <v>-4.703980739625881</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.3685179617593</v>
+        <v>2.399799346551087</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.8201311081106631</v>
+        <v>0.8983345700901316</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.773826731581584</v>
+        <v>4.820748808769266</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.7925002997717</v>
+        <v>-4.714296837792233</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.577296355770818</v>
+        <v>2.608577740562604</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.8201311081106631</v>
+        <v>0.8983345700901316</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.986731564859642</v>
+        <v>5.033653642047324</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.792406331754328</v>
+        <v>-4.71420286977486</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.576512609889856</v>
+        <v>2.607793994681643</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.8205009694579811</v>
+        <v>0.8987044314374496</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.986132148580123</v>
+        <v>5.033054225767804</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.799625155954172</v>
+        <v>-4.721421693974705</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.567857066154272</v>
+        <v>2.599138450946059</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.8205009694579811</v>
+        <v>0.8987044314374496</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.980364134524477</v>
+        <v>5.027286211712158</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.798676732836133</v>
+        <v>-4.720473270856666</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.568236435401488</v>
+        <v>2.599517820193275</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.8205009694579811</v>
+        <v>0.8987044314374496</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.980364134524477</v>
+        <v>5.027286211712158</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.836354670845794</v>
+        <v>3.846779419099446</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.965529870273931</v>
+        <v>-4.955045263117913</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.514222788407461</v>
+        <v>2.518416631269868</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.8205009694579811</v>
+        <v>0.8987044314374496</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.993091742505569</v>
+        <v>5.04001381969325</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240910.xlsx
+++ b/tame_output/ON/bt/strategyON_20240910.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>59.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.8%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-657.1%</t>
+          <t>-654.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-124.4%</t>
+          <t>-123.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-327.6%</t>
+          <t>-318.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-134.1%</t>
+          <t>-141.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>106.7%</t>
+          <t>105.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.299946152217899</v>
+        <v>-6.348717527443574</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3477399339524303</v>
+        <v>0.3282313838621604</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.09241126744213063</v>
+        <v>-0.1411826426678049</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.812628058688059</v>
+        <v>2.783365233552654</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.134157956257608</v>
+        <v>-6.182929331483283</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4070946002414533</v>
+        <v>0.3875860501511834</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.09241126744213063</v>
+        <v>-0.1411826426678049</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.805667446592966</v>
+        <v>2.776404621457561</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.10079474977884</v>
+        <v>-6.149566125004514</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.434902237214104</v>
+        <v>0.4153936871238342</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.09241126744213063</v>
+        <v>-0.1411826426678049</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.820129800974109</v>
+        <v>2.790866975838704</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.992535612656318</v>
+        <v>-6.041306987881993</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4727380125223077</v>
+        <v>0.4532294624320379</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.09241126744213063</v>
+        <v>-0.1411826426678049</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.814661921433304</v>
+        <v>2.785399096297899</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.869244477839187</v>
+        <v>-5.918015853064862</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5195525604597369</v>
+        <v>0.500044010369467</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.03087986737499987</v>
+        <v>-0.01789150785067445</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.886134696334159</v>
+        <v>2.856871871198754</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.816547610707896</v>
+        <v>-5.865318985933571</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5483322855495785</v>
+        <v>0.5288237354593086</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.08357673450629105</v>
+        <v>0.03480535928061673</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.925453794850259</v>
+        <v>2.896190969714854</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.572782168724451</v>
+        <v>-5.621553543950126</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.641619170690007</v>
+        <v>0.6221106205997371</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.08357673450629105</v>
+        <v>0.03480535928061673</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.92123450319731</v>
+        <v>2.891971678061905</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.483006496347979</v>
+        <v>-5.531777871573654</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6796537535606118</v>
+        <v>0.6601452034703419</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1451761794206011</v>
+        <v>0.09640480419492675</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.960318484065912</v>
+        <v>2.931055658930507</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.233156102398905</v>
+        <v>-5.281927477624579</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7723359861239438</v>
+        <v>0.752827436033674</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1451761794206011</v>
+        <v>0.09640480419492675</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.953060559049614</v>
+        <v>2.923797733914209</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.057264009931473</v>
+        <v>-5.106035385157147</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8462919466315655</v>
+        <v>0.8267833965412956</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1451761794206011</v>
+        <v>0.09640480419492675</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.956659682570263</v>
+        <v>2.927396857434858</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.885817546909009</v>
+        <v>-4.934588922134684</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9281980378951045</v>
+        <v>0.9086894878048346</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3166226424430642</v>
+        <v>0.2678512672173899</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.072855066438294</v>
+        <v>3.04359224130289</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.805795259799888</v>
+        <v>-4.854566635025563</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9592274303550499</v>
+        <v>0.93971888026478</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3966449295521852</v>
+        <v>0.3478735543265108</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.119888916320064</v>
+        <v>3.090626091184659</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.742159517565954</v>
+        <v>-4.790930892791629</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.989376528302941</v>
+        <v>0.9698679782126711</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4602806717861197</v>
+        <v>0.4115092965604454</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.162765162714742</v>
+        <v>3.133502337579337</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.648462199349559</v>
+        <v>-4.697233574575233</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.008049714373295</v>
+        <v>0.9885411642830246</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4602806717861197</v>
+        <v>0.4115092965604454</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.143959421498538</v>
+        <v>3.114696596363133</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.658964822414847</v>
+        <v>-4.707736197640522</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.005591741772057</v>
+        <v>0.9860831916817865</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4497780487208308</v>
+        <v>0.4010066734951565</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.139400924284241</v>
+        <v>3.110138099148837</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.546478561745973</v>
+        <v>-4.595249936971648</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.054515559874426</v>
+        <v>1.035007009784157</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4497780487208308</v>
+        <v>0.4010066734951565</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.143330238119062</v>
+        <v>3.114067412983657</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.528764874868108</v>
+        <v>-4.577536250093782</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.062279618542913</v>
+        <v>1.042771068452643</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4529593776177476</v>
+        <v>0.4041880023920733</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.145917619374552</v>
+        <v>3.116654794239147</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.405290603555089</v>
+        <v>-4.454061978780764</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.108667398288113</v>
+        <v>1.089158848197843</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4529593776177476</v>
+        <v>0.4041880023920733</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.142915690594545</v>
+        <v>3.113652865459141</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.185269805518079</v>
+        <v>-4.234041180743754</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.198254754513532</v>
+        <v>1.178746204423262</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5941792226857279</v>
+        <v>0.5454078474600536</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.229226634645948</v>
+        <v>3.199963809510543</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.052402116454801</v>
+        <v>-4.101173491680476</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.267296012940666</v>
+        <v>1.247787462850396</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5941792226857279</v>
+        <v>0.5454078474600536</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.245120817447771</v>
+        <v>3.215857992312366</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.932229033090302</v>
+        <v>-3.981000408315977</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.316511090726767</v>
+        <v>1.297002540636498</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7143523060502268</v>
+        <v>0.6655809308245525</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.318370511906772</v>
+        <v>3.289107686771367</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.796975671760325</v>
+        <v>-3.845747046986</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.380700537820198</v>
+        <v>1.361191987729928</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8496056673802039</v>
+        <v>0.8008342921545296</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.409610631266198</v>
+        <v>3.380347806130794</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.856850499118018</v>
+        <v>-3.905621874343693</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.342788098278547</v>
+        <v>1.323279548188277</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7897308400225118</v>
+        <v>0.7409594647968375</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.359723226253009</v>
+        <v>3.330460401117604</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.73703026820718</v>
+        <v>-3.785801643432855</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.406005359877091</v>
+        <v>1.386496809786821</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7897308400225118</v>
+        <v>0.7409594647968375</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.375012395487217</v>
+        <v>3.345749570351813</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.739499974668986</v>
+        <v>-3.788271349894661</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.31266167661481</v>
+        <v>1.29315312652454</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7872611335607056</v>
+        <v>0.7384897583350314</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.281174770932575</v>
+        <v>3.251911945797171</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.807870160992996</v>
+        <v>-3.856641536218671</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.204575463570507</v>
+        <v>1.185066913480237</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7965368325969205</v>
+        <v>0.7477654573712463</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.206002051839605</v>
+        <v>3.176739226704201</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.919742440619147</v>
+        <v>-3.968513815844822</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.150263260351938</v>
+        <v>1.130754710261668</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7965368325969205</v>
+        <v>0.7477654573712463</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.196438760471497</v>
+        <v>3.167175935336092</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.975262516511736</v>
+        <v>-4.024033891737411</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.265086066687105</v>
+        <v>1.245577516596835</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7965368325969205</v>
+        <v>0.7477654573712463</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.333469597163699</v>
+        <v>3.304206772028295</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.799788256719267</v>
+        <v>-3.848559631944942</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.33984300259588</v>
+        <v>1.32033445250561</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7965368325969205</v>
+        <v>0.7477654573712463</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.338036829155487</v>
+        <v>3.308774004020083</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.791863882134353</v>
+        <v>-3.840635257360028</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.318754781191053</v>
+        <v>1.299246231100783</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7965368325969205</v>
+        <v>0.7477654573712463</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.313778857916694</v>
+        <v>3.28451603278129</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.785585679564504</v>
+        <v>-3.834357054790179</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.249804375620442</v>
+        <v>1.230295825530172</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8028150351667696</v>
+        <v>0.7540436599410953</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.246084092860053</v>
+        <v>3.216821267724649</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.725733060360781</v>
+        <v>-3.743154131757624</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.283917809734064</v>
+        <v>1.276949381175327</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8028150351667696</v>
+        <v>0.7540436599410953</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.256256479292186</v>
+        <v>3.226993654156781</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.639489597334403</v>
+        <v>-3.656910668731246</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.313361465518475</v>
+        <v>1.306393036959738</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8028150351667696</v>
+        <v>0.7540436599410953</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.251202749866046</v>
+        <v>3.221939924730641</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.684796416733383</v>
+        <v>-3.702217488130226</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.287014513203409</v>
+        <v>1.280046084644672</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7620048721575388</v>
+        <v>0.7132334969318646</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.218492427505033</v>
+        <v>3.189229602369628</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.713829521435685</v>
+        <v>-3.731250592832528</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.27595314435559</v>
+        <v>1.268984715796853</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7620048721575388</v>
+        <v>0.7132334969318646</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.219044300538135</v>
+        <v>3.18978147540273</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.621019039984826</v>
+        <v>-3.638440111381668</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.242350028827299</v>
+        <v>1.235381600268562</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8548153536083981</v>
+        <v>0.8060439783827239</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.204003281300016</v>
+        <v>3.174740456164611</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.665408509314253</v>
+        <v>-3.682829580711096</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.226467717020129</v>
+        <v>1.219499288461392</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8104258842789704</v>
+        <v>0.7616545090532962</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.17924307562696</v>
+        <v>3.149980250491556</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.781950114419596</v>
+        <v>-3.799371185816439</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.174926783489715</v>
+        <v>1.167958354930978</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6938842791736277</v>
+        <v>0.6451129039479535</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.104393821075477</v>
+        <v>3.075130995940073</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.821874209002168</v>
+        <v>-3.839295280399011</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.164448441487353</v>
+        <v>1.157480012928616</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6938842791736277</v>
+        <v>0.6451129039479535</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.109885116906145</v>
+        <v>3.08062229177074</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.849654606903521</v>
+        <v>-3.867075678300364</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.164833484095351</v>
+        <v>1.157865055536614</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6661038812722746</v>
+        <v>0.6173325060466004</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.104714079933872</v>
+        <v>3.075451254798467</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.968035279633659</v>
+        <v>-3.985456351030502</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9558369350039491</v>
+        <v>0.948868506445212</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5988860291212984</v>
+        <v>0.5501146538956242</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.902739088643939</v>
+        <v>2.873476263508535</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.07664935807699</v>
+        <v>-4.094070429473833</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.032540964345822</v>
+        <v>1.025572535787085</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5988860291212984</v>
+        <v>0.5501146538956242</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.022888749363145</v>
+        <v>2.99362592422774</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.041240319828847</v>
+        <v>-4.05866139122569</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.061217605747403</v>
+        <v>1.054249177188666</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5988860291212984</v>
+        <v>0.5501146538956242</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.037401775465468</v>
+        <v>3.008138950330063</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.002856657270696</v>
+        <v>-4.020277728667539</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.073990512113032</v>
+        <v>1.067022083554295</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6372696916794496</v>
+        <v>0.5884983164537754</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.057851414342728</v>
+        <v>3.028588589207323</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.82574032723553</v>
+        <v>-3.843161398632373</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.1415660729724</v>
+        <v>1.134597644413663</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6372696916794496</v>
+        <v>0.5884983164537754</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.054580443188029</v>
+        <v>3.025317618052625</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.870832572069076</v>
+        <v>-3.888253643465919</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.124212566800895</v>
+        <v>1.117244138242158</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5753736485100598</v>
+        <v>0.5266022732843856</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.018126209048309</v>
+        <v>2.988863383912904</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.691457150830308</v>
+        <v>-3.708878222227151</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.189749710602816</v>
+        <v>1.182781282044079</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7321504066807785</v>
+        <v>0.6833790314551043</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.105979239257154</v>
+        <v>3.07671641412175</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.736471364350914</v>
+        <v>-3.753892435747757</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.152551480526164</v>
+        <v>1.145583051967426</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7018015113661739</v>
+        <v>0.6530301361404997</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.068577357399981</v>
+        <v>3.039314532264576</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.00347587462335</v>
+        <v>-4.020896946020192</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.051441238756135</v>
+        <v>1.044472810197398</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5074384733232253</v>
+        <v>0.4586670980975511</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.957651096913158</v>
+        <v>2.928388271777753</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.104673656060522</v>
+        <v>-4.122094727457365</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.010166048077767</v>
+        <v>1.00319761951903</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4390296597779061</v>
+        <v>0.3902582845522319</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.915809730682468</v>
+        <v>2.886546905547063</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.09816268944621</v>
+        <v>-4.115583760843053</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.010370396277809</v>
+        <v>1.003401967719072</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4390296597779061</v>
+        <v>0.3902582845522319</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.913409692236784</v>
+        <v>2.88414686710138</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.079124561738912</v>
+        <v>-4.096545633135755</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.014510366568973</v>
+        <v>1.007541938010236</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3808460484467116</v>
+        <v>0.3320746732210373</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.875024244646312</v>
+        <v>2.845761419510908</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.131640364013733</v>
+        <v>-4.149061435410576</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.112798447293235</v>
+        <v>1.105830018734498</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3808460484467116</v>
+        <v>0.3320746732210373</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.994318646280503</v>
+        <v>2.965055821145098</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.145507125347651</v>
+        <v>-4.162928196744494</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.108085071745802</v>
+        <v>1.101116643187064</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3429881317128887</v>
+        <v>0.2942167564872144</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.972437225226343</v>
+        <v>2.943174400090938</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.105024133425306</v>
+        <v>-4.122445204822148</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.130286798911666</v>
+        <v>1.123318370352929</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3429881317128887</v>
+        <v>0.2942167564872144</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.978445755623269</v>
+        <v>2.949182930487864</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.957281163190304</v>
+        <v>-3.974702234587146</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.087334208282866</v>
+        <v>1.080365779724129</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5107954889477718</v>
+        <v>0.4620241137220976</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.977080391241398</v>
+        <v>2.947817566105993</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.041102384465002</v>
+        <v>-4.058523455861844</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.056599341304468</v>
+        <v>1.049630912745731</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5107954889477718</v>
+        <v>0.4620241137220976</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.979874012772879</v>
+        <v>2.950611187637474</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.034949678412217</v>
+        <v>-4.05237074980906</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.05972277211724</v>
+        <v>1.052754343558503</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5169481950005561</v>
+        <v>0.4681768197748818</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.984227984796208</v>
+        <v>2.954965159660803</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.051758976562719</v>
+        <v>-4.069180047959562</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.052079529597149</v>
+        <v>1.045111101038412</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5001388968500544</v>
+        <v>0.4513675216243802</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.973222882646017</v>
+        <v>2.943960057510613</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.989460977786597</v>
+        <v>-4.00688204918344</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.143334282904419</v>
+        <v>1.136365854345682</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5454331611244965</v>
+        <v>0.4966617858988223</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.066734995007503</v>
+        <v>3.037472169872099</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.787670780121439</v>
+        <v>-3.805091851518283</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.026342363684609</v>
+        <v>1.019373935125872</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7434513532936509</v>
+        <v>0.6946799780679767</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.987837912023123</v>
+        <v>2.958575086887719</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.838557492807634</v>
+        <v>-3.855978564204477</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.076277910932307</v>
+        <v>1.069309482373569</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6925646406074564</v>
+        <v>0.6437932653817822</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.027596116733581</v>
+        <v>2.998333291598177</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.751946750157827</v>
+        <v>-3.76936782155467</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.125549944108273</v>
+        <v>1.118581515549536</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7711903718126146</v>
+        <v>0.7224189965869404</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.08939929157272</v>
+        <v>3.060136466437315</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.812156048163111</v>
+        <v>-3.829577119559954</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.100002205730831</v>
+        <v>1.093033777172094</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7109810738073301</v>
+        <v>0.6622096985816559</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.051809693594221</v>
+        <v>3.022546868458817</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.76296939947876</v>
+        <v>-3.780390470875603</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.1181684832445</v>
+        <v>1.111200054685763</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7109810738073301</v>
+        <v>0.6622096985816559</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.05030131163415</v>
+        <v>3.021038486498745</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.718596267840191</v>
+        <v>-3.736017339237034</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.135780603335364</v>
+        <v>1.128812174776627</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7553542054458987</v>
+        <v>0.7065828302202245</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.076788058052727</v>
+        <v>3.047525232917323</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.741076618699076</v>
+        <v>-3.758497690095919</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.1211822571304</v>
+        <v>1.114213828571663</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7553542054458987</v>
+        <v>0.7065828302202245</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.071181852191318</v>
+        <v>3.041919027055913</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.663988801384226</v>
+        <v>-3.710841959534864</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.158399141084145</v>
+        <v>1.13965787782389</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8324420227607489</v>
+        <v>0.7542385607812802</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.123816299608032</v>
+        <v>3.076894222420351</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.563470642885471</v>
+        <v>-3.610323801036109</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.203498777858372</v>
+        <v>1.184757514598117</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9329601812595034</v>
+        <v>0.8547567192800347</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.18901956808201</v>
+        <v>3.142097490894328</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.547565313453119</v>
+        <v>-3.594418471603757</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.196615582107185</v>
+        <v>1.17787431884693</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8538475205502645</v>
+        <v>0.7756440585707958</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.128306644132339</v>
+        <v>3.081384566944657</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.502726911844721</v>
+        <v>-3.549580069995359</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.218648645361173</v>
+        <v>1.199907382100918</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8583909534951339</v>
+        <v>0.7801874915156652</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.135130406509889</v>
+        <v>3.088208329322208</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.522225368086729</v>
+        <v>-3.569078526237367</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.215010202495447</v>
+        <v>1.196268939235192</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8103063122152296</v>
+        <v>0.7321028502357609</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.110440561373024</v>
+        <v>3.063518484185343</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.478022531000828</v>
+        <v>-3.524875689151466</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.238570939857645</v>
+        <v>1.21982967659739</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8545091493011301</v>
+        <v>0.7763056873216614</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.142841866152402</v>
+        <v>3.095919788964721</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.485582196837875</v>
+        <v>-3.532435354988513</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.233957073992074</v>
+        <v>1.215215810731819</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9093125533109494</v>
+        <v>0.8311090913314807</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.174133909027541</v>
+        <v>3.12721183183986</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.327290779298603</v>
+        <v>-3.374143937449241</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.348521406190822</v>
+        <v>1.329780142930567</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9093125533109494</v>
+        <v>0.8311090913314807</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.22538167421058</v>
+        <v>3.178459597022899</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.119648775664127</v>
+        <v>-3.166501933814765</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.430018912238866</v>
+        <v>1.411277648978611</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.116954556945426</v>
+        <v>1.038751094965957</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.348407580985519</v>
+        <v>3.301485503797838</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.068616682941599</v>
+        <v>-3.115469841092237</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.445379977566147</v>
+        <v>1.426638714305892</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.167986649667954</v>
+        <v>1.089783187688485</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.373975064857306</v>
+        <v>3.327052987669625</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.003392501814393</v>
+        <v>-3.050245659965031</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.488657054109734</v>
+        <v>1.469915790849479</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.233210830795159</v>
+        <v>1.155007368815691</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.430296977626334</v>
+        <v>3.383374900438653</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.96596548174326</v>
+        <v>-3.012818639893897</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.499588834437468</v>
+        <v>1.480847571177213</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.238462368824341</v>
+        <v>1.160258906844872</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.429408872743124</v>
+        <v>3.382486795555443</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.986077137777968</v>
+        <v>-3.032930295928606</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.492800964354825</v>
+        <v>1.47405970109457</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.24948971382176</v>
+        <v>1.171286251842292</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.437282072072816</v>
+        <v>3.390359994885134</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.957663874678084</v>
+        <v>-3.004517032828722</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.664724040615989</v>
+        <v>1.645982777355734</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.190514151075331</v>
+        <v>1.112310689095863</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.562454505446169</v>
+        <v>3.515532428258488</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.882881613653072</v>
+        <v>-2.929734771803709</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.814749854243811</v>
+        <v>1.796008590983557</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.265296412100344</v>
+        <v>1.187092950120875</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.727436771278994</v>
+        <v>3.680514694091313</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.856797529389264</v>
+        <v>-2.903650687539901</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.816891463963193</v>
+        <v>1.798150200702939</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.265296412100344</v>
+        <v>1.187092950120875</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.719144747292853</v>
+        <v>3.672222670105172</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.768919616280143</v>
+        <v>-2.815772774430781</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.850235824790621</v>
+        <v>1.831494561530366</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.381222054523695</v>
+        <v>1.303018592544226</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.786893328330643</v>
+        <v>3.739971251142962</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.76002715488686</v>
+        <v>-2.806880313037497</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.871347215074726</v>
+        <v>1.852605951814471</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.381222054523695</v>
+        <v>1.303018592544226</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.804447734057435</v>
+        <v>3.757525656869753</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.928503271856738</v>
+        <v>-2.975356430007375</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.795811815691359</v>
+        <v>1.777070552431104</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.353274218807114</v>
+        <v>1.275070756827646</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.77953408003207</v>
+        <v>3.732612002844389</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782711</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.482247079227298</v>
+        <v>-2.529100237377935</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.955583989930997</v>
+        <v>1.936842726670742</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.258555549137482</v>
+        <v>1.180352087158013</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.703972575418152</v>
+        <v>3.657050498230471</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.459525975544145</v>
+        <v>-2.506379133694783</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.955336453901162</v>
+        <v>1.936595190640907</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.258555549137482</v>
+        <v>1.180352087158013</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.694636597915057</v>
+        <v>3.647714520727376</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.588727788838188</v>
+        <v>-2.635580946988825</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.062561854434714</v>
+        <v>2.043820591174459</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.129353735843439</v>
+        <v>1.051150273863971</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.7760216357898</v>
+        <v>3.729099558602119</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.614602187312213</v>
+        <v>-2.661455345462851</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.089289917538751</v>
+        <v>2.070548654278496</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.174265344555181</v>
+        <v>1.096061882575712</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.840046423510492</v>
+        <v>3.79312434632281</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799967</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.60754749709704</v>
+        <v>-2.654400655247677</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.088787149614365</v>
+        <v>2.07004588635411</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.181320034770354</v>
+        <v>1.103116572790886</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.840954593629141</v>
+        <v>3.79403251644146</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331118</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.580596272770552</v>
+        <v>-2.627449430921189</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.109573792989702</v>
+        <v>2.090832529729447</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.196200380798073</v>
+        <v>1.117996918818605</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.859888954890514</v>
+        <v>3.812966877702833</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.602140500601339</v>
+        <v>-2.648993658751976</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.285059234002347</v>
+        <v>2.266317970742092</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.196200380798073</v>
+        <v>1.117996918818605</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.043992087035474</v>
+        <v>3.997070009847793</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.624548618406211</v>
+        <v>-2.671401776556849</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.268212681783391</v>
+        <v>2.249471418523136</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.196200380798073</v>
+        <v>1.117996918818605</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.036108781938467</v>
+        <v>3.989186704750786</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.652772853983811</v>
+        <v>-2.699626012134449</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.258976987101988</v>
+        <v>2.240235723841733</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.214177133249382</v>
+        <v>1.135973671269913</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.04894883295889</v>
+        <v>4.002026755771208</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.662213779872341</v>
+        <v>-2.709066938022979</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.311454334468424</v>
+        <v>2.292713071208169</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.336604250792774</v>
+        <v>1.258400788813305</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.178658821206771</v>
+        <v>4.13173674401909</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.751090411040815</v>
+        <v>-2.797943569191453</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.278794776546335</v>
+        <v>2.26005351328608</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.2477276196243</v>
+        <v>1.169524157644831</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.128223937050988</v>
+        <v>4.081301859863307</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.827420388641721</v>
+        <v>-2.874273546792359</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.246374598399748</v>
+        <v>2.227633335139493</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.2477276196243</v>
+        <v>1.169524157644831</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.126335749944763</v>
+        <v>4.079413672757082</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.921084333319262</v>
+        <v>-2.9679374914699</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.203729250131594</v>
+        <v>2.184987986871339</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.154063674946758</v>
+        <v>1.07586021296729</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.064957612741101</v>
+        <v>4.01803553555342</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.082652758846518</v>
+        <v>-3.129505916997155</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.137535890130843</v>
+        <v>2.118794626870589</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.027280751148879</v>
+        <v>0.9490772891694103</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.987321868672526</v>
+        <v>3.940399791484844</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.190953420716637</v>
+        <v>-3.237806578867275</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.107289032248715</v>
+        <v>2.08854776898846</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.027280751148879</v>
+        <v>0.9490772891694103</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.000395275538444</v>
+        <v>3.953473198350763</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.208757392437381</v>
+        <v>-3.255610550588019</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.092172640343357</v>
+        <v>2.073431377083102</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9567461282436778</v>
+        <v>0.8785426662642091</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.950079698578263</v>
+        <v>3.903157621390582</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006978</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.236658179546854</v>
+        <v>-3.283511337697492</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.07953636662657</v>
+        <v>2.060795103366315</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.922149204100743</v>
+        <v>0.8439457421212743</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.927845585219504</v>
+        <v>3.880923508031823</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787389</v>
+        <v>3.68489577878739</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.359184282249748</v>
+        <v>-3.406037440400385</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.027290369522611</v>
+        <v>2.008549106262356</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7996231013978491</v>
+        <v>0.7214196394183804</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.851094367574967</v>
+        <v>3.804172290387286</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.61934808158594</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.589698778435337</v>
+        <v>-3.636551936585974</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.001790530638879</v>
+        <v>1.983049267378624</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5691086052122604</v>
+        <v>0.4909051432327917</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.779491629454117</v>
+        <v>3.732569552266436</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814667</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.93844386365978</v>
+        <v>-3.985297021810418</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.002604215550948</v>
+        <v>1.983862952290694</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4603606512933626</v>
+        <v>0.3821571893138939</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.854554576104626</v>
+        <v>3.807632498916945</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237096</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.092430281435921</v>
+        <v>-4.139283439586558</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.009989917586132</v>
+        <v>1.991248654325878</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4603606512933626</v>
+        <v>0.3821571893138939</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.923534845250265</v>
+        <v>3.876612768062584</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.041908377608255</v>
+        <v>-4.088761535758892</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.016249881237319</v>
+        <v>1.997508617977064</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4603606512933626</v>
+        <v>0.3821571893138939</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.909586047370387</v>
+        <v>3.862663970182705</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609755</v>
+        <v>3.656332733609756</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.29438353161598</v>
+        <v>-4.341236689766617</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.927130308689644</v>
+        <v>1.908389045429389</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4603606512933626</v>
+        <v>0.3821571893138939</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.921456536425801</v>
+        <v>3.874534459238119</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.67402853597316</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.587279288095392</v>
+        <v>-4.634132446246029</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.811182540616822</v>
+        <v>1.792441277356568</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4603606512933626</v>
+        <v>0.3821571893138939</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.922667070944744</v>
+        <v>3.875744993757063</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251947</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.7739434162302</v>
+        <v>-4.820796574380837</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.740638631590221</v>
+        <v>1.721897368329966</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4336216804688027</v>
+        <v>0.355418218489334</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.91074543067733</v>
+        <v>3.863823353489649</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916203</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.919964103144162</v>
+        <v>-4.966817261294799</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.677308209560825</v>
+        <v>1.65856694630057</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4245385886749457</v>
+        <v>0.346335126695477</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.900373428337205</v>
+        <v>3.853451351149524</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.011678112253747</v>
+        <v>-5.058531270404384</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.802826662616035</v>
+        <v>1.784085399355781</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4245385886749457</v>
+        <v>0.346335126695477</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.062577485036249</v>
+        <v>4.015655407848568</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071553</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.043329771313717</v>
+        <v>-5.090182929464353</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.785012636955861</v>
+        <v>1.766271373695607</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4193701314305055</v>
+        <v>0.3411666694510368</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.054323048653399</v>
+        <v>4.007400971465718</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.1252645895826</v>
+        <v>-5.172117747733236</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.762468127216799</v>
+        <v>1.743726863956545</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4094353858434253</v>
+        <v>0.3312319238639566</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.058591618869642</v>
+        <v>4.011669541681961</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.227240711831008</v>
+        <v>-5.274093869981644</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.730603316773339</v>
+        <v>1.711862053513084</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3074592635950177</v>
+        <v>0.229255801615549</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.0063315839765</v>
+        <v>3.959409506788819</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.117234428353786</v>
+        <v>-5.164087586504422</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.766758717408403</v>
+        <v>1.748017454148148</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3306638355122929</v>
+        <v>0.2524603735328242</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.012407214371041</v>
+        <v>3.965485137183359</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.97417485261286</v>
+        <v>-5.021028010763496</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.828232558426748</v>
+        <v>1.809491295166493</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3386772621022722</v>
+        <v>0.2604738001228035</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.021465281047003</v>
+        <v>3.974543203859321</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.672728127141022</v>
+        <v>-4.719581285291659</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.956072131498019</v>
+        <v>1.937330868237764</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6401239875741095</v>
+        <v>0.5619205255946408</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.209594199212641</v>
+        <v>4.16267212202496</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.697318371376206</v>
+        <v>-4.744171529526843</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.947207211556655</v>
+        <v>1.928465948296401</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6401239875741095</v>
+        <v>0.5619205255946408</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.210565376965351</v>
+        <v>4.16364329977767</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.646279995369686</v>
+        <v>-4.693133153520322</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.968465466339019</v>
+        <v>1.949724203078765</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6401239875741095</v>
+        <v>0.5619205255946408</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.211408281345107</v>
+        <v>4.164486204157425</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.605140700503055</v>
+        <v>-4.651993858653691</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.003959283159817</v>
+        <v>1.985218019899563</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6812632824407403</v>
+        <v>0.6030598204612716</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.255129957139231</v>
+        <v>4.20820787995155</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.508505788484415</v>
+        <v>-4.555358946635051</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.858797244091208</v>
+        <v>1.840055980830953</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7778981944593802</v>
+        <v>0.6996947324799115</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.129294900474349</v>
+        <v>4.082372823286669</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.639086523015258</v>
+        <v>-4.685939681165894</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.810066994352835</v>
+        <v>1.79132573109258</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6473174599285377</v>
+        <v>0.569113997949069</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.054448503829808</v>
+        <v>4.007526426642126</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.474590188824296</v>
+        <v>-4.521443346974932</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.860292347105302</v>
+        <v>1.841551083845048</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8118137941194996</v>
+        <v>0.7336103321400309</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.137573123420467</v>
+        <v>4.090651046232787</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.397491587282423</v>
+        <v>-4.444344745433059</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.890319498158481</v>
+        <v>1.871578234898226</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8118137941194996</v>
+        <v>0.7336103321400309</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.136760833856897</v>
+        <v>4.089838756669216</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.407876782172313</v>
+        <v>-4.454729940322949</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.896034199327598</v>
+        <v>1.877292936067343</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8014285992296103</v>
+        <v>0.7232251372501416</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.140398496048036</v>
+        <v>4.093476418860355</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.426464940894538</v>
+        <v>-4.473318099045174</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.959435941615133</v>
+        <v>1.940694678354878</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.782840440507385</v>
+        <v>0.7046369785279163</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.200082606591126</v>
+        <v>4.153160529403445</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.426763487590573</v>
+        <v>-4.47361664574121</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.956185533755017</v>
+        <v>1.937444270494762</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7825418938113491</v>
+        <v>0.7043384318318804</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.196772489391803</v>
+        <v>4.149850412204122</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.325940353900146</v>
+        <v>-4.372793512050782</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.001045682170579</v>
+        <v>1.982304418910325</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.7950061092957029</v>
+        <v>0.7168026473162342</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.208781913621807</v>
+        <v>4.161859836434125</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.135158993147739</v>
+        <v>-4.182012151298375</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.077487479950086</v>
+        <v>2.058746216689831</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9857874700481103</v>
+        <v>0.9075840080686416</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.323379983551795</v>
+        <v>4.276457906364113</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.028195635298317</v>
+        <v>-4.075048793448953</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.100109668827451</v>
+        <v>2.081368405567196</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.044252078007912</v>
+        <v>0.9660486160284431</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.338295594065272</v>
+        <v>4.291373516877591</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.972865047396555</v>
+        <v>-4.019718205547191</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.157208840600214</v>
+        <v>2.138467577339959</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.099582665909674</v>
+        <v>1.021379203930205</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.406460883418387</v>
+        <v>4.359538806230707</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.960810920483592</v>
+        <v>-4.007664078634228</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.155717059266837</v>
+        <v>2.136975796006582</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.111636792822637</v>
+        <v>1.033433330843168</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.407379927467603</v>
+        <v>4.360457850279922</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.001966040051814</v>
+        <v>-4.048819198202449</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.141135641623684</v>
+        <v>2.12239437836343</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.070481673254416</v>
+        <v>0.9922782112749471</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.384567485910806</v>
+        <v>4.337645408723125</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.933917477360284</v>
+        <v>-3.980770635510919</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.181206092578178</v>
+        <v>2.162464829317924</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.138530235945946</v>
+        <v>1.060326773966477</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.438247649403607</v>
+        <v>4.391325572215925</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.165517870529785</v>
+        <v>-4.21237102868042</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.108768605483972</v>
+        <v>2.090027342223718</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.138530235945946</v>
+        <v>1.060326773966477</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.458450319577201</v>
+        <v>4.41152824238952</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.215569416059004</v>
+        <v>-4.262422574209639</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.072354223339167</v>
+        <v>2.053612960078913</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.138530235945946</v>
+        <v>1.060326773966477</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.442056555644083</v>
+        <v>4.395134478456402</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.390676248635449</v>
+        <v>-4.437529406786084</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.962563403902055</v>
+        <v>1.943822140641801</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.138530235945946</v>
+        <v>1.060326773966477</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.40230846923755</v>
+        <v>4.355386392049868</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.359390228094994</v>
+        <v>-4.406243386245628</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.982100431115177</v>
+        <v>1.963359167854923</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.169816256486401</v>
+        <v>1.091612794506932</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.428102700558763</v>
+        <v>4.381180623371081</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.206364835981709</v>
+        <v>-4.253217994132344</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.142481587533395</v>
+        <v>2.123740324273141</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.322841648599685</v>
+        <v>1.244638186620216</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.619088935399637</v>
+        <v>4.572166858211957</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.23467214985498</v>
+        <v>-4.281525308005614</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.31862488689238</v>
+        <v>2.299883623632126</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.322841648599685</v>
+        <v>1.244638186620216</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.80655516030793</v>
+        <v>4.759633083120249</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.401265374968502</v>
+        <v>-4.448118533119136</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.221390548201053</v>
+        <v>2.202649284940799</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.156248423486163</v>
+        <v>1.078044961506694</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.676002176593899</v>
+        <v>4.629080099406218</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.378229581606936</v>
+        <v>-4.42508273975757</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.234281268207397</v>
+        <v>2.215540004947144</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.156248423486163</v>
+        <v>1.078044961506694</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.679678579255617</v>
+        <v>4.632756502067935</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.348983601151239</v>
+        <v>-4.395836759301874</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.243597715513171</v>
+        <v>2.224856452252918</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.156248423486163</v>
+        <v>1.078044961506694</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.677296634379112</v>
+        <v>4.630374557191431</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.455909149029091</v>
+        <v>-4.502762307179725</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.198120735519666</v>
+        <v>2.179379472259412</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.049322875608311</v>
+        <v>0.9711194136288425</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.610434544810037</v>
+        <v>4.563512467622355</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.600927707536339</v>
+        <v>-4.647780865686974</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.141542114260001</v>
+        <v>2.122800850999747</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9043043171010627</v>
+        <v>0.8261008551215939</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.524852211848922</v>
+        <v>4.47793013466124</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.719269473321057</v>
+        <v>-4.766122631471691</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.194136647203867</v>
+        <v>2.175395383943613</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9149903556639528</v>
+        <v>0.836786893684484</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.631195074244409</v>
+        <v>4.584272997056727</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.770679895641765</v>
+        <v>-4.817533053792399</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.171358175401522</v>
+        <v>2.152616912141268</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9149903556639528</v>
+        <v>0.836786893684484</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.628980771370347</v>
+        <v>4.582058694182666</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.850099346849516</v>
+        <v>-4.896952505000151</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.139493522992711</v>
+        <v>2.120752259732457</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9149903556639528</v>
+        <v>0.836786893684484</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.628883899444637</v>
+        <v>4.581961822256956</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.945562344766734</v>
+        <v>-4.992415502917368</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.101302217383867</v>
+        <v>2.082560954123614</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9149903556639528</v>
+        <v>0.836786893684484</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.628877793002681</v>
+        <v>4.581955715814999</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.881186433916019</v>
+        <v>-4.928039592066654</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.125148978286764</v>
+        <v>2.10640771502651</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.979366266514668</v>
+        <v>0.9011628045351991</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.66559973607572</v>
+        <v>4.618677658888038</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.936555596048213</v>
+        <v>-4.983408754198847</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.108735131181613</v>
+        <v>2.089993867921359</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.979366266514668</v>
+        <v>0.9011628045351991</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.671333553823446</v>
+        <v>4.624411476635765</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.98199337587904</v>
+        <v>-5.028846534029674</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.090098382592214</v>
+        <v>2.071357119331961</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9365212758365082</v>
+        <v>0.8583178138570395</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.645164922759482</v>
+        <v>4.598242845571802</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.893786541731462</v>
+        <v>-4.940639699882096</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.145255509101565</v>
+        <v>2.126514245841311</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9365212758365082</v>
+        <v>0.8583178138570395</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.665039315609802</v>
+        <v>4.618117238422121</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.787751546526152</v>
+        <v>-4.834604704676787</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.171370207708416</v>
+        <v>2.152628944448162</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9365212758365082</v>
+        <v>0.8583178138570395</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.648740016134529</v>
+        <v>4.601817938946849</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.604539883393057</v>
+        <v>-4.651393041543692</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.2470858224257</v>
+        <v>2.228344559165446</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9365212758365082</v>
+        <v>0.8583178138570395</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.651170965598575</v>
+        <v>4.604248888410894</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.532818436379206</v>
+        <v>-4.579671594529841</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.24156558707913</v>
+        <v>2.222824323818876</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.008242722850359</v>
+        <v>0.9300392608708902</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.659995019654775</v>
+        <v>4.613072942467094</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.5104454107715</v>
+        <v>-4.557298568922135</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.197430543243383</v>
+        <v>2.17868927998313</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.01949847396326</v>
+        <v>0.9412950119837917</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.613664216243688</v>
+        <v>4.566742139056006</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.543461706682245</v>
+        <v>-4.590314864832879</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.369422229764441</v>
+        <v>2.350680966504187</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9500610972965087</v>
+        <v>0.8718576353170402</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.757199995128992</v>
+        <v>4.710277917941311</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.531934071032636</v>
+        <v>-4.578787229183271</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.365954509852534</v>
+        <v>2.34721324659228</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.009061755497871</v>
+        <v>0.9308582935184027</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.784521615878059</v>
+        <v>4.737599538690377</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.629275572375005</v>
+        <v>-4.676128730525639</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.330686021837375</v>
+        <v>2.311944758577121</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.9646415733323828</v>
+        <v>0.8864381113529143</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.761537619100555</v>
+        <v>4.714615541912873</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.715131601714972</v>
+        <v>-4.761984759865606</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.297594692294227</v>
+        <v>2.278853429033973</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9222655041062477</v>
+        <v>0.8440620421267793</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.737363059757711</v>
+        <v>4.69044098257003</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.723968399131091</v>
+        <v>-4.770821557281725</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.27647917514828</v>
+        <v>2.257737911888027</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.914823331464897</v>
+        <v>0.8366198694854285</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.715316957993402</v>
+        <v>4.668394880805722</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.81535096169655</v>
+        <v>-4.862204119847184</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.250090661167147</v>
+        <v>2.231349397906893</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.8234407688994387</v>
+        <v>0.7452373069199703</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.670651931499177</v>
+        <v>4.623729854311496</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.803644243709543</v>
+        <v>-4.850497401860178</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.356901606186217</v>
+        <v>2.338160342925963</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.8351474868864451</v>
+        <v>0.7569440249069767</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.779804220115649</v>
+        <v>4.732882142927968</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.703980739625881</v>
+        <v>-4.750833897776515</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.399799346551087</v>
+        <v>2.381058083290833</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.8983345700901316</v>
+        <v>0.8201311081106631</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.820748808769266</v>
+        <v>4.773826731581584</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.714296837792233</v>
+        <v>-4.761149995942867</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.608577740562604</v>
+        <v>2.589836477302351</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.8983345700901316</v>
+        <v>0.8201311081106631</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.033653642047324</v>
+        <v>4.986731564859642</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.71420286977486</v>
+        <v>-4.761056027925495</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.607793994681643</v>
+        <v>2.589052731421389</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.8987044314374496</v>
+        <v>0.8205009694579811</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.033054225767804</v>
+        <v>4.986132148580123</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.721421693974705</v>
+        <v>-4.768274852125339</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.599138450946059</v>
+        <v>2.580397187685805</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.8987044314374496</v>
+        <v>0.8205009694579811</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.027286211712158</v>
+        <v>4.980364134524477</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.720473270856666</v>
+        <v>-4.767326429007301</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.599517820193275</v>
+        <v>2.580776556933021</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.8987044314374496</v>
+        <v>0.8205009694579811</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.027286211712158</v>
+        <v>4.980364134524477</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.846779419099446</v>
+        <v>3.877146832689213</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.955045263117913</v>
+        <v>-4.924394887262924</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.518416631269868</v>
+        <v>2.530676781611863</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.8987044314374496</v>
+        <v>0.8205009694579811</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.04001381969325</v>
+        <v>4.993091742505569</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240910.xlsx
+++ b/tame_output/ON/bt/strategyON_20240910.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.3%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-40.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>138.5%</t>
+          <t>140.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-41.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-46.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.0%</t>
+          <t>-643.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-123.2%</t>
+          <t>-129.7%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-318.6%</t>
+          <t>-317.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-141.9%</t>
+          <t>-123.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>105.0%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,42 +1456,42 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>5.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2082"/>
+  <dimension ref="A1:G2083"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.057119799856059</v>
+        <v>2.948613372791267</v>
       </c>
       <c r="D1905" t="n">
         <v>-6.752974685246547</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3555735014436934</v>
+        <v>0.2470670743789012</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.3680014132188442</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.836318951924753</v>
+        <v>2.727812524859961</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.059934860543696</v>
+        <v>2.951428433478904</v>
       </c>
       <c r="D1906" t="n">
         <v>-6.597236352686805</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4206838951552268</v>
+        <v>0.3121774680904346</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.2122630806591026</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.932577012148235</v>
+        <v>2.824070585083442</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.072841201767355</v>
+        <v>2.964334774702563</v>
       </c>
       <c r="D1907" t="n">
         <v>-6.512271685957485</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4675761030706136</v>
+        <v>0.3590696760058214</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.127298413929783</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.996462153409485</v>
+        <v>2.887955726344693</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.944865272168136</v>
+        <v>2.836358845103343</v>
       </c>
       <c r="D1908" t="n">
         <v>-6.617861675730589</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2973641775621529</v>
+        <v>0.1888577504973603</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.2328884037028874</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.805132229946404</v>
+        <v>2.696625802881611</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.993409614045222</v>
+        <v>2.88490318698043</v>
       </c>
       <c r="D1909" t="n">
         <v>-6.549627091105162</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3732023532894102</v>
+        <v>0.2646959262246176</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.2144730808303514</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.864725765547012</v>
+        <v>2.756219338482219</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.876788805406815</v>
+        <v>2.768282378342023</v>
       </c>
       <c r="D1910" t="n">
         <v>-6.401687049697562</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3157575612140429</v>
+        <v>0.2072511341492502</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.1941521649217938</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.760297506453739</v>
+        <v>2.651791079388947</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.868074819153337</v>
+        <v>2.759568392088545</v>
       </c>
       <c r="D1911" t="n">
         <v>-6.348717527443574</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3282313838621604</v>
+        <v>0.2197249567973678</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.1411826426678049</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.783365233552654</v>
+        <v>2.674858806487862</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.861114207058244</v>
+        <v>2.752607779993451</v>
       </c>
       <c r="D1912" t="n">
         <v>-6.182929331483283</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3875860501511834</v>
+        <v>0.2790796230863908</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.1411826426678049</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.776404621457561</v>
+        <v>2.667898194392769</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.875576561439387</v>
+        <v>2.767070134374594</v>
       </c>
       <c r="D1913" t="n">
         <v>-6.149566125004514</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4153936871238342</v>
+        <v>0.3068872600590415</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.1411826426678049</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.790866975838704</v>
+        <v>2.682360548773912</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.870108681898582</v>
+        <v>2.76160225483379</v>
       </c>
       <c r="D1914" t="n">
         <v>-6.041306987881993</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4532294624320379</v>
+        <v>0.3447230353672452</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.1411826426678049</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.785399096297899</v>
+        <v>2.676892669233107</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.867606775909159</v>
+        <v>2.759100348844366</v>
       </c>
       <c r="D1915" t="n">
         <v>-5.918015853064862</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.500044010369467</v>
+        <v>0.3915375833046744</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.01789150785067445</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.856871871198754</v>
+        <v>2.748365444133962</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.875307754146484</v>
+        <v>2.766801327081692</v>
       </c>
       <c r="D1916" t="n">
         <v>-5.865318985933571</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5288237354593086</v>
+        <v>0.420317308394516</v>
       </c>
       <c r="F1916" t="n">
         <v>0.03480535928061673</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.896190969714854</v>
+        <v>2.787684542650062</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.871088462493535</v>
+        <v>2.762582035428742</v>
       </c>
       <c r="D1917" t="n">
         <v>-5.621553543950126</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6221106205997371</v>
+        <v>0.5136041935349445</v>
       </c>
       <c r="F1917" t="n">
         <v>0.03480535928061673</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.891971678061905</v>
+        <v>2.783465250997113</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.873212776413551</v>
+        <v>2.764706349348758</v>
       </c>
       <c r="D1918" t="n">
         <v>-5.531777871573654</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6601452034703419</v>
+        <v>0.5516387764055493</v>
       </c>
       <c r="F1918" t="n">
         <v>0.09640480419492675</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.931055658930507</v>
+        <v>2.822549231865715</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.865954851397253</v>
+        <v>2.75744842433246</v>
       </c>
       <c r="D1919" t="n">
         <v>-5.281927477624579</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.752827436033674</v>
+        <v>0.6443210089688813</v>
       </c>
       <c r="F1919" t="n">
         <v>0.09640480419492675</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.923797733914209</v>
+        <v>2.815291306849417</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.869553974917902</v>
+        <v>2.761047547853109</v>
       </c>
       <c r="D1920" t="n">
         <v>-5.106035385157147</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8267833965412956</v>
+        <v>0.718276969476503</v>
       </c>
       <c r="F1920" t="n">
         <v>0.09640480419492675</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.927396857434858</v>
+        <v>2.818890430370065</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.882881480972455</v>
+        <v>2.774375053907663</v>
       </c>
       <c r="D1921" t="n">
         <v>-4.934588922134684</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9086894878048346</v>
+        <v>0.800183060740042</v>
       </c>
       <c r="F1921" t="n">
         <v>0.2678512672173899</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.04359224130289</v>
+        <v>2.935085814238097</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.881901958588752</v>
+        <v>2.77339553152396</v>
       </c>
       <c r="D1922" t="n">
         <v>-4.854566635025563</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.93971888026478</v>
+        <v>0.8312124531999874</v>
       </c>
       <c r="F1922" t="n">
         <v>0.3478735543265108</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.090626091184659</v>
+        <v>2.982119664119867</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.88659675964307</v>
+        <v>2.778090332578277</v>
       </c>
       <c r="D1923" t="n">
         <v>-4.790930892791629</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9698679782126711</v>
+        <v>0.8613615511478785</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4115092965604454</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.133502337579337</v>
+        <v>3.024995910514545</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.867791018426865</v>
+        <v>2.759284591362073</v>
       </c>
       <c r="D1924" t="n">
         <v>-4.697233574575233</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9885411642830246</v>
+        <v>0.880034737218232</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4115092965604454</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.114696596363133</v>
+        <v>3.00619016929834</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.869534095051743</v>
+        <v>2.76102766798695</v>
       </c>
       <c r="D1925" t="n">
         <v>-4.707736197640522</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9860831916817865</v>
+        <v>0.8775767646169939</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4010066734951565</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.110138099148837</v>
+        <v>3.001631672084044</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.873463408886563</v>
+        <v>2.76495698182177</v>
       </c>
       <c r="D1926" t="n">
         <v>-4.595249936971648</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.035007009784157</v>
+        <v>0.926500582719364</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4010066734951565</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.114067412983657</v>
+        <v>3.005560985918864</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.874141992803903</v>
+        <v>2.76563556573911</v>
       </c>
       <c r="D1927" t="n">
         <v>-4.577536250093782</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.042771068452643</v>
+        <v>0.9342646413878501</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4041880023920733</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.116654794239147</v>
+        <v>3.008148367174354</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.871140064023896</v>
+        <v>2.762633636959104</v>
       </c>
       <c r="D1928" t="n">
         <v>-4.454061978780764</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.089158848197843</v>
+        <v>0.9806524211330507</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4041880023920733</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.113652865459141</v>
+        <v>3.005146438394348</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.872719101034511</v>
+        <v>2.764212673969718</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.234041180743754</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.178746204423262</v>
+        <v>1.070239777358469</v>
       </c>
       <c r="F1929" t="n">
         <v>0.5454078474600536</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.199963809510543</v>
+        <v>3.09145738244575</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.888613283836334</v>
+        <v>2.780106856771541</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.101173491680476</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.247787462850396</v>
+        <v>1.139281035785604</v>
       </c>
       <c r="F1930" t="n">
         <v>0.5454078474600536</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.215857992312366</v>
+        <v>3.107351565247574</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.889759128276636</v>
+        <v>2.781252701211843</v>
       </c>
       <c r="D1931" t="n">
         <v>-3.981000408315977</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.297002540636498</v>
+        <v>1.188496113571705</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6655809308245525</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.289107686771367</v>
+        <v>3.180601259706575</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.899847230838076</v>
+        <v>2.791340803773283</v>
       </c>
       <c r="D1932" t="n">
         <v>-3.845747046986</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.361191987729928</v>
+        <v>1.252685560665136</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8008342921545296</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.380347806130794</v>
+        <v>3.271841379066001</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.885884722239501</v>
+        <v>2.777378295174709</v>
       </c>
       <c r="D1933" t="n">
         <v>-3.905621874343693</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.323279548188277</v>
+        <v>1.214773121123484</v>
       </c>
       <c r="F1933" t="n">
         <v>0.7409594647968375</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.330460401117604</v>
+        <v>3.221953974052811</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.90117389147371</v>
+        <v>2.792667464408917</v>
       </c>
       <c r="D1934" t="n">
         <v>-3.785801643432855</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.386496809786821</v>
+        <v>1.277990382722028</v>
       </c>
       <c r="F1934" t="n">
         <v>0.7409594647968375</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.345749570351813</v>
+        <v>3.23724314328702</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.808818090796152</v>
+        <v>2.700311663731359</v>
       </c>
       <c r="D1935" t="n">
         <v>-3.788271349894661</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.29315312652454</v>
+        <v>1.184646699459747</v>
       </c>
       <c r="F1935" t="n">
         <v>0.7384897583350314</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.251911945797171</v>
+        <v>3.143405518732378</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.728079952281453</v>
+        <v>2.61957352521666</v>
       </c>
       <c r="D1936" t="n">
         <v>-3.856641536218671</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.185066913480237</v>
+        <v>1.076560486415445</v>
       </c>
       <c r="F1936" t="n">
         <v>0.7477654573712463</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.176739226704201</v>
+        <v>3.068232799639409</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.718516660913344</v>
+        <v>2.610010233848552</v>
       </c>
       <c r="D1937" t="n">
         <v>-3.968513815844822</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.130754710261668</v>
+        <v>1.022248283196876</v>
       </c>
       <c r="F1937" t="n">
         <v>0.7477654573712463</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.167175935336092</v>
+        <v>3.0586695082713</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.855547497605547</v>
+        <v>2.747041070540754</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.024033891737411</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.245577516596835</v>
+        <v>1.137071089532042</v>
       </c>
       <c r="F1938" t="n">
         <v>0.7477654573712463</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.304206772028295</v>
+        <v>3.195700344963502</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.860114729597334</v>
+        <v>2.751608302532542</v>
       </c>
       <c r="D1939" t="n">
         <v>-3.848559631944942</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.32033445250561</v>
+        <v>1.211828025440818</v>
       </c>
       <c r="F1939" t="n">
         <v>0.7477654573712463</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.308774004020083</v>
+        <v>3.20026757695529</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.835856758358541</v>
+        <v>2.727350331293749</v>
       </c>
       <c r="D1940" t="n">
         <v>-3.840635257360028</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.299246231100783</v>
+        <v>1.19073980403599</v>
       </c>
       <c r="F1940" t="n">
         <v>0.7477654573712463</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.28451603278129</v>
+        <v>3.176009605716497</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.764395071759991</v>
+        <v>2.655888644695199</v>
       </c>
       <c r="D1941" t="n">
         <v>-3.834357054790179</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.230295825530172</v>
+        <v>1.12178939846538</v>
       </c>
       <c r="F1941" t="n">
         <v>0.7540436599410953</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.216821267724649</v>
+        <v>3.108314840659856</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.774567458192124</v>
+        <v>2.666061031127331</v>
       </c>
       <c r="D1942" t="n">
         <v>-3.743154131757624</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.276949381175327</v>
+        <v>1.168442954110534</v>
       </c>
       <c r="F1942" t="n">
         <v>0.7540436599410953</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.226993654156781</v>
+        <v>3.118487227091988</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.769513728765984</v>
+        <v>2.661007301701191</v>
       </c>
       <c r="D1943" t="n">
         <v>-3.656910668731246</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.306393036959738</v>
+        <v>1.197886609894945</v>
       </c>
       <c r="F1943" t="n">
         <v>0.7540436599410953</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.221939924730641</v>
+        <v>3.113433497665849</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.761289504210509</v>
+        <v>2.652783077145717</v>
       </c>
       <c r="D1944" t="n">
         <v>-3.702217488130226</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.280046084644672</v>
+        <v>1.171539657579879</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7132334969318646</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.189229602369628</v>
+        <v>3.080723175304836</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.761841377243611</v>
+        <v>2.653334950178818</v>
       </c>
       <c r="D1945" t="n">
         <v>-3.731250592832528</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.268984715796853</v>
+        <v>1.16047828873206</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7132334969318646</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.18978147540273</v>
+        <v>3.081275048337937</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.691114069134977</v>
+        <v>2.582607642070184</v>
       </c>
       <c r="D1946" t="n">
         <v>-3.638440111381668</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.235381600268562</v>
+        <v>1.126875173203769</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8060439783827239</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.174740456164611</v>
+        <v>3.066234029099819</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.692987545059577</v>
+        <v>2.584481117994785</v>
       </c>
       <c r="D1947" t="n">
         <v>-3.682829580711096</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.219499288461392</v>
+        <v>1.110992861396599</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7616545090532962</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.149980250491556</v>
+        <v>3.041473823426763</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.6880632535713</v>
+        <v>2.579556826506508</v>
       </c>
       <c r="D1948" t="n">
         <v>-3.799371185816439</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.167958354930978</v>
+        <v>1.059451927866185</v>
       </c>
       <c r="F1948" t="n">
         <v>0.6451129039479535</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.075130995940073</v>
+        <v>2.96662456887528</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.693554549401968</v>
+        <v>2.585048122337175</v>
       </c>
       <c r="D1949" t="n">
         <v>-3.839295280399011</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.157480012928616</v>
+        <v>1.048973585863824</v>
       </c>
       <c r="F1949" t="n">
         <v>0.6451129039479535</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.08062229177074</v>
+        <v>2.972115864705947</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.705051751170507</v>
+        <v>2.596545324105714</v>
       </c>
       <c r="D1950" t="n">
         <v>-3.867075678300364</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.157865055536614</v>
+        <v>1.049358628471821</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6173325060466004</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.075451254798467</v>
+        <v>2.966944827733675</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.54340747117116</v>
+        <v>2.434901044106367</v>
       </c>
       <c r="D1951" t="n">
         <v>-3.985456351030502</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.948868506445212</v>
+        <v>0.8403620793804194</v>
       </c>
       <c r="F1951" t="n">
         <v>0.5501146538956242</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.873476263508535</v>
+        <v>2.764969836443742</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.663557131890366</v>
+        <v>2.555050704825573</v>
       </c>
       <c r="D1952" t="n">
         <v>-4.094070429473833</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.025572535787085</v>
+        <v>0.9170661087222927</v>
       </c>
       <c r="F1952" t="n">
         <v>0.5501146538956242</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.99362592422774</v>
+        <v>2.885119497162948</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.678070157992689</v>
+        <v>2.569563730927896</v>
       </c>
       <c r="D1953" t="n">
         <v>-4.05866139122569</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.054249177188666</v>
+        <v>0.9457427501238729</v>
       </c>
       <c r="F1953" t="n">
         <v>0.5501146538956242</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.008138950330063</v>
+        <v>2.899632523265271</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.675489599335057</v>
+        <v>2.566983172270265</v>
       </c>
       <c r="D1954" t="n">
         <v>-4.020277728667539</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.067022083554295</v>
+        <v>0.9585156564895019</v>
       </c>
       <c r="F1954" t="n">
         <v>0.5884983164537754</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.028588589207323</v>
+        <v>2.92008216214253</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.672218628180359</v>
+        <v>2.563712201115567</v>
       </c>
       <c r="D1955" t="n">
         <v>-3.843161398632373</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.134597644413663</v>
+        <v>1.02609121734887</v>
       </c>
       <c r="F1955" t="n">
         <v>0.5884983164537754</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.025317618052625</v>
+        <v>2.916811190987832</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.672902019942272</v>
+        <v>2.56439559287748</v>
       </c>
       <c r="D1956" t="n">
         <v>-3.888253643465919</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.117244138242158</v>
+        <v>1.008737711177365</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5266022732843856</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.988863383912904</v>
+        <v>2.880356956848111</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.666688995248687</v>
+        <v>2.558182568183894</v>
       </c>
       <c r="D1957" t="n">
         <v>-3.708878222227151</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.182781282044079</v>
+        <v>1.074274854979286</v>
       </c>
       <c r="F1957" t="n">
         <v>0.6833790314551043</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.07671641412175</v>
+        <v>2.968209987056957</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.647496450580276</v>
+        <v>2.538990023515484</v>
       </c>
       <c r="D1958" t="n">
         <v>-3.753892435747757</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.145583051967426</v>
+        <v>1.037076624902634</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6530301361404997</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.039314532264576</v>
+        <v>2.930808105199784</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.653188012919222</v>
+        <v>2.54468158585443</v>
       </c>
       <c r="D1959" t="n">
         <v>-4.020896946020192</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.044472810197398</v>
+        <v>0.9359663831326053</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4586670980975511</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.928388271777753</v>
+        <v>2.819881844712961</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.652391934815724</v>
+        <v>2.543885507750931</v>
       </c>
       <c r="D1960" t="n">
         <v>-4.122094727457365</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.00319761951903</v>
+        <v>0.8946911924542378</v>
       </c>
       <c r="F1960" t="n">
         <v>0.3902582845522319</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.886546905547063</v>
+        <v>2.778040478482271</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.64999189637004</v>
+        <v>2.541485469305248</v>
       </c>
       <c r="D1961" t="n">
         <v>-4.115583760843053</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.003401967719072</v>
+        <v>0.8948955406542796</v>
       </c>
       <c r="F1961" t="n">
         <v>0.3902582845522319</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.88414686710138</v>
+        <v>2.775640440036587</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.646516615578285</v>
+        <v>2.538010188513493</v>
       </c>
       <c r="D1962" t="n">
         <v>-4.096545633135755</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.007541938010236</v>
+        <v>0.8990355109454433</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3320746732210373</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.845761419510908</v>
+        <v>2.737254992446116</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.765811017212476</v>
+        <v>2.657304590147683</v>
       </c>
       <c r="D1963" t="n">
         <v>-4.149061435410576</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.105830018734498</v>
+        <v>0.9973235916697054</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3320746732210373</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.965055821145098</v>
+        <v>2.856549394080306</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.766644346198609</v>
+        <v>2.658137919133817</v>
       </c>
       <c r="D1964" t="n">
         <v>-4.162928196744494</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.101116643187064</v>
+        <v>0.9926102161222718</v>
       </c>
       <c r="F1964" t="n">
         <v>0.2942167564872144</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.943174400090938</v>
+        <v>2.834667973026145</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.772652876595535</v>
+        <v>2.664146449530743</v>
       </c>
       <c r="D1965" t="n">
         <v>-4.122445204822148</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.123318370352929</v>
+        <v>1.014811943288136</v>
       </c>
       <c r="F1965" t="n">
         <v>0.2942167564872144</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.949182930487864</v>
+        <v>2.840676503423071</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.670603097872735</v>
+        <v>2.562096670807942</v>
       </c>
       <c r="D1966" t="n">
         <v>-3.974702234587146</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.080365779724129</v>
+        <v>0.9718593526593362</v>
       </c>
       <c r="F1966" t="n">
         <v>0.4620241137220976</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.947817566105993</v>
+        <v>2.839311139041201</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.673396719404216</v>
+        <v>2.564890292339423</v>
       </c>
       <c r="D1967" t="n">
         <v>-4.058523455861844</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.049630912745731</v>
+        <v>0.941124485680938</v>
       </c>
       <c r="F1967" t="n">
         <v>0.4620241137220976</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.950611187637474</v>
+        <v>2.842104760572682</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.674059067795874</v>
+        <v>2.565552640731081</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.05237074980906</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.052754343558503</v>
+        <v>0.9442479164937101</v>
       </c>
       <c r="F1968" t="n">
         <v>0.4681768197748818</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.954965159660803</v>
+        <v>2.846458732596011</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.673139544535984</v>
+        <v>2.564633117471192</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.069180047959562</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.045111101038412</v>
+        <v>0.9366046739736196</v>
       </c>
       <c r="F1969" t="n">
         <v>0.4513675216243802</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.943960057510613</v>
+        <v>2.83545363044582</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.739475098332805</v>
+        <v>2.630968671268012</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.00688204918344</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.136365854345682</v>
+        <v>1.027859427280889</v>
       </c>
       <c r="F1970" t="n">
         <v>0.4966617858988223</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.037472169872099</v>
+        <v>2.928965742807306</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.541767100046932</v>
+        <v>2.43326067298214</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.805091851518283</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.019373935125872</v>
+        <v>0.9108675080610795</v>
       </c>
       <c r="F1971" t="n">
         <v>0.6946799780679767</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.958575086887719</v>
+        <v>2.850068659822926</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.612057332369107</v>
+        <v>2.503550905304315</v>
       </c>
       <c r="D1972" t="n">
         <v>-3.855978564204477</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.069309482373569</v>
+        <v>0.9608030553087767</v>
       </c>
       <c r="F1972" t="n">
         <v>0.6437932653817822</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.998333291598177</v>
+        <v>2.889826864533384</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.626685068485151</v>
+        <v>2.518178641420358</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.76936782155467</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.118581515549536</v>
+        <v>1.010075088484743</v>
       </c>
       <c r="F1973" t="n">
         <v>0.7224189965869404</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.060136466437315</v>
+        <v>2.951630039372523</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.625221049309823</v>
+        <v>2.51671462224503</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.829577119559954</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.093033777172094</v>
+        <v>0.9845273501073013</v>
       </c>
       <c r="F1974" t="n">
         <v>0.6622096985816559</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.022546868458817</v>
+        <v>2.914040441394024</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.623712667349751</v>
+        <v>2.515206240284959</v>
       </c>
       <c r="D1975" t="n">
         <v>-3.780390470875603</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.111200054685763</v>
+        <v>1.00269362762097</v>
       </c>
       <c r="F1975" t="n">
         <v>0.6622096985816559</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.021038486498745</v>
+        <v>2.912532059433953</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.623575534785187</v>
+        <v>2.515069107720395</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.736017339237034</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.128812174776627</v>
+        <v>1.020305747711834</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7065828302202245</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.047525232917323</v>
+        <v>2.93901880585253</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.617969328923778</v>
+        <v>2.509462901858985</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.758497690095919</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.114213828571663</v>
+        <v>1.005707401506871</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7065828302202245</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.041919027055913</v>
+        <v>2.93341259999112</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190327</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.624351085951583</v>
+        <v>2.51584465888679</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.710841959534864</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.13965787782389</v>
+        <v>1.031151450759097</v>
       </c>
       <c r="F1978" t="n">
         <v>0.7542385607812802</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.076894222420351</v>
+        <v>2.968387795355558</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569619</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.629243459326307</v>
+        <v>2.520737032261515</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.610323801036109</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.184757514598117</v>
+        <v>1.076251087533324</v>
       </c>
       <c r="F1979" t="n">
         <v>0.8547567192800347</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.142097490894328</v>
+        <v>3.033591063829536</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557296</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.61599813180218</v>
+        <v>2.507491704737387</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.594418471603757</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.17787431884693</v>
+        <v>1.069367891782137</v>
       </c>
       <c r="F1980" t="n">
         <v>0.7756440585707958</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.081384566944657</v>
+        <v>2.972878139879865</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.620095834412808</v>
+        <v>2.511589407348016</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.549580069995359</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.199907382100918</v>
+        <v>1.091400955036125</v>
       </c>
       <c r="F1981" t="n">
         <v>0.7801874915156652</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.088208329322208</v>
+        <v>2.979701902257415</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.624256774043886</v>
+        <v>2.515750346979094</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.569078526237367</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.196268939235192</v>
+        <v>1.0877625121704</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7321028502357609</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.063518484185343</v>
+        <v>2.95501205712055</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.630136376571723</v>
+        <v>2.521629949506931</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.524875689151466</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.21982967659739</v>
+        <v>1.111323249532597</v>
       </c>
       <c r="F1983" t="n">
         <v>0.7763056873216614</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.095919788964721</v>
+        <v>2.987413361899928</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.628546377040971</v>
+        <v>2.520039949976178</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.532435354988513</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.215215810731819</v>
+        <v>1.106709383667026</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8311090913314807</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.12721183183986</v>
+        <v>3.018705404775067</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.679794142224011</v>
+        <v>2.571287715159218</v>
       </c>
       <c r="D1985" t="n">
         <v>-3.374143937449241</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.329780142930567</v>
+        <v>1.221273715865774</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8311090913314807</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.178459597022899</v>
+        <v>3.069953169958107</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.678234846818264</v>
+        <v>2.569728419753471</v>
       </c>
       <c r="D1986" t="n">
         <v>-3.166501933814765</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.411277648978611</v>
+        <v>1.302771221913818</v>
       </c>
       <c r="F1986" t="n">
         <v>1.038751094965957</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.301485503797838</v>
+        <v>3.192979076733045</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.673183075056534</v>
+        <v>2.564676647991741</v>
       </c>
       <c r="D1987" t="n">
         <v>-3.115469841092237</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.426638714305892</v>
+        <v>1.318132287241099</v>
       </c>
       <c r="F1987" t="n">
         <v>1.089783187688485</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.327052987669625</v>
+        <v>3.218546560604832</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404855</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.690370479149239</v>
+        <v>2.581864052084446</v>
       </c>
       <c r="D1988" t="n">
         <v>-3.050245659965031</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.469915790849479</v>
+        <v>1.361409363784686</v>
       </c>
       <c r="F1988" t="n">
         <v>1.155007368815691</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.383374900438653</v>
+        <v>3.274868473373861</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.686331451448519</v>
+        <v>2.577825024383726</v>
       </c>
       <c r="D1989" t="n">
         <v>-3.012818639893897</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.480847571177213</v>
+        <v>1.37234114411242</v>
       </c>
       <c r="F1989" t="n">
         <v>1.160258906844872</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.382486795555443</v>
+        <v>3.27398036849065</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.687588243779759</v>
+        <v>2.579081816714967</v>
       </c>
       <c r="D1990" t="n">
         <v>-3.032930295928606</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.47405970109457</v>
+        <v>1.365553274029777</v>
       </c>
       <c r="F1990" t="n">
         <v>1.171286251842292</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.390359994885134</v>
+        <v>3.281853567820342</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636289</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.84814601480097</v>
+        <v>2.739639587736177</v>
       </c>
       <c r="D1991" t="n">
         <v>-3.004517032828722</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.645982777355734</v>
+        <v>1.537476350290942</v>
       </c>
       <c r="F1991" t="n">
         <v>1.112310689095863</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.515532428258488</v>
+        <v>3.407026001193695</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957628</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.968258924018787</v>
+        <v>2.859752496953995</v>
       </c>
       <c r="D1992" t="n">
         <v>-2.929734771803709</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.796008590983557</v>
+        <v>1.687502163918764</v>
       </c>
       <c r="F1992" t="n">
         <v>1.187092950120875</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.680514694091313</v>
+        <v>3.57200826702652</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.959966900032646</v>
+        <v>2.851460472967854</v>
       </c>
       <c r="D1993" t="n">
         <v>-2.903650687539901</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.798150200702939</v>
+        <v>1.689643773638146</v>
       </c>
       <c r="F1993" t="n">
         <v>1.187092950120875</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.672222670105172</v>
+        <v>3.563716243040379</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896933</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.958160095616426</v>
+        <v>2.849653668551633</v>
       </c>
       <c r="D1994" t="n">
         <v>-2.815772774430781</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.831494561530366</v>
+        <v>1.722988134465574</v>
       </c>
       <c r="F1994" t="n">
         <v>1.303018592544226</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.739971251142962</v>
+        <v>3.631464824078169</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959861</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.975714501343217</v>
+        <v>2.867208074278425</v>
       </c>
       <c r="D1995" t="n">
         <v>-2.806880313037497</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.852605951814471</v>
+        <v>1.744099524749678</v>
       </c>
       <c r="F1995" t="n">
         <v>1.303018592544226</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.757525656869753</v>
+        <v>3.64901922980496</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945369</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.967569548747801</v>
+        <v>2.859063121683008</v>
       </c>
       <c r="D1996" t="n">
         <v>-2.975356430007375</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.777070552431104</v>
+        <v>1.668564125366311</v>
       </c>
       <c r="F1996" t="n">
         <v>1.275070756827646</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.732612002844389</v>
+        <v>3.624105575779596</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782711</v>
+        <v>3.795574066782713</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.948839245935663</v>
+        <v>2.84033281887087</v>
       </c>
       <c r="D1997" t="n">
         <v>-2.529100237377935</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.936842726670742</v>
+        <v>1.828336299605949</v>
       </c>
       <c r="F1997" t="n">
         <v>1.180352087158013</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.657050498230471</v>
+        <v>3.548544071165678</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.78467134563264</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.939503268432567</v>
+        <v>2.830996841367775</v>
       </c>
       <c r="D1998" t="n">
         <v>-2.506379133694783</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.936595190640907</v>
+        <v>1.828088763576115</v>
       </c>
       <c r="F1998" t="n">
         <v>1.180352087158013</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.647714520727376</v>
+        <v>3.539208093662583</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777677</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.098409394283737</v>
+        <v>2.989902967218944</v>
       </c>
       <c r="D1999" t="n">
         <v>-2.635580946988825</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.043820591174459</v>
+        <v>1.935314164109667</v>
       </c>
       <c r="F1999" t="n">
         <v>1.051150273863971</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.729099558602119</v>
+        <v>3.620593131537326</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644416</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.135487216777383</v>
+        <v>3.02698078971259</v>
       </c>
       <c r="D2000" t="n">
         <v>-2.661455345462851</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.070548654278496</v>
+        <v>1.962042227213703</v>
       </c>
       <c r="F2000" t="n">
         <v>1.096061882575712</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.79312434632281</v>
+        <v>3.684617919258018</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799967</v>
+        <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.132162572766928</v>
+        <v>3.023656145702136</v>
       </c>
       <c r="D2001" t="n">
         <v>-2.654400655247677</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.07004588635411</v>
+        <v>1.961539459289318</v>
       </c>
       <c r="F2001" t="n">
         <v>1.103116572790886</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.79403251644146</v>
+        <v>3.685526089376667</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331118</v>
+        <v>3.76667349633112</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.14216872641167</v>
+        <v>3.033662299346877</v>
       </c>
       <c r="D2002" t="n">
         <v>-2.627449430921189</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.090832529729447</v>
+        <v>1.982326102664654</v>
       </c>
       <c r="F2002" t="n">
         <v>1.117996918818605</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.812966877702833</v>
+        <v>3.70446045063804</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784112</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.32627185855663</v>
+        <v>3.217765431491837</v>
       </c>
       <c r="D2003" t="n">
         <v>-2.648993658751976</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.266317970742092</v>
+        <v>2.157811543677299</v>
       </c>
       <c r="F2003" t="n">
         <v>1.117996918818605</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.997070009847793</v>
+        <v>3.888563582783</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.74392550571443</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.318388553459623</v>
+        <v>3.20988212639483</v>
       </c>
       <c r="D2004" t="n">
         <v>-2.671401776556849</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.249471418523136</v>
+        <v>2.140964991458343</v>
       </c>
       <c r="F2004" t="n">
         <v>1.117996918818605</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.989186704750786</v>
+        <v>3.880680277685993</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155036</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.32044255300926</v>
+        <v>3.211936125944467</v>
       </c>
       <c r="D2005" t="n">
         <v>-2.699626012134449</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.240235723841733</v>
+        <v>2.131729296776941</v>
       </c>
       <c r="F2005" t="n">
         <v>1.135973671269913</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.002026755771208</v>
+        <v>3.893520328706416</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.376696270731107</v>
+        <v>3.268189843666315</v>
       </c>
       <c r="D2006" t="n">
         <v>-2.709066938022979</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.292713071208169</v>
+        <v>2.184206644143376</v>
       </c>
       <c r="F2006" t="n">
         <v>1.258400788813305</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.13173674401909</v>
+        <v>4.023230316954297</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.379587365276408</v>
+        <v>3.271080938211615</v>
       </c>
       <c r="D2007" t="n">
         <v>-2.797943569191453</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.26005351328608</v>
+        <v>2.151547086221287</v>
       </c>
       <c r="F2007" t="n">
         <v>1.169524157644831</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.081301859863307</v>
+        <v>3.972795432798514</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347707</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.377699178170183</v>
+        <v>3.269192751105391</v>
       </c>
       <c r="D2008" t="n">
         <v>-2.874273546792359</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.227633335139493</v>
+        <v>2.1191269080747</v>
       </c>
       <c r="F2008" t="n">
         <v>1.169524157644831</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.079413672757082</v>
+        <v>3.970907245692289</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.372519407773046</v>
+        <v>3.264012980708253</v>
       </c>
       <c r="D2009" t="n">
         <v>-2.9679374914699</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.184987986871339</v>
+        <v>2.076481559806546</v>
       </c>
       <c r="F2009" t="n">
         <v>1.07586021296729</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.01803553555342</v>
+        <v>3.909529108488627</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343068</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.370953417983198</v>
+        <v>3.262446990918405</v>
       </c>
       <c r="D2010" t="n">
         <v>-3.129505916997155</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.118794626870589</v>
+        <v>2.010288199805796</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9490772891694103</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.940399791484844</v>
+        <v>3.831893364420051</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389351</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.384026824849117</v>
+        <v>3.275520397784324</v>
       </c>
       <c r="D2011" t="n">
         <v>-3.237806578867275</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.08854776898846</v>
+        <v>1.980041341923667</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9490772891694103</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.953473198350763</v>
+        <v>3.844966771285971</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.749882691378396</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.376032021632057</v>
+        <v>3.267525594567264</v>
       </c>
       <c r="D2012" t="n">
         <v>-3.255610550588019</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.073431377083102</v>
+        <v>1.964924950018309</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8785426662642091</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.903157621390582</v>
+        <v>3.79465119432579</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006978</v>
+        <v>3.715819895006979</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.374556062759059</v>
+        <v>3.266049635694266</v>
       </c>
       <c r="D2013" t="n">
         <v>-3.283511337697492</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.060795103366315</v>
+        <v>1.952288676301522</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8439457421212743</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.880923508031823</v>
+        <v>3.772417080967031</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787391</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.371320506736257</v>
+        <v>3.262814079671465</v>
       </c>
       <c r="D2014" t="n">
         <v>-3.406037440400385</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.008549106262356</v>
+        <v>1.900042679197563</v>
       </c>
       <c r="F2014" t="n">
         <v>0.7214196394183804</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.804172290387286</v>
+        <v>3.695665863322493</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.61934808158594</v>
+        <v>3.619348081585942</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.438026466326761</v>
+        <v>3.329520039261968</v>
       </c>
       <c r="D2015" t="n">
         <v>-3.636551936585974</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.983049267378624</v>
+        <v>1.874542840313832</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4909051432327917</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.732569552266436</v>
+        <v>3.624063125201644</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814667</v>
+        <v>3.640750087814669</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.578338185328608</v>
+        <v>3.469831758263815</v>
       </c>
       <c r="D2016" t="n">
         <v>-3.985297021810418</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.983862952290694</v>
+        <v>1.875356525225901</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3821571893138939</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.807632498916945</v>
+        <v>3.699126071852152</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237099</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.647318454474248</v>
+        <v>3.538812027409455</v>
       </c>
       <c r="D2017" t="n">
         <v>-4.139283439586558</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.991248654325878</v>
+        <v>1.882742227261085</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3821571893138939</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.876612768062584</v>
+        <v>3.768106340997792</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423392</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.633369656594369</v>
+        <v>3.524863229529576</v>
       </c>
       <c r="D2018" t="n">
         <v>-4.088761535758892</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.997508617977064</v>
+        <v>1.889002190912272</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3821571893138939</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.862663970182705</v>
+        <v>3.754157543117913</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609758</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.645240145649783</v>
+        <v>3.53673371858499</v>
       </c>
       <c r="D2019" t="n">
         <v>-4.341236689766617</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.908389045429389</v>
+        <v>1.799882618364596</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3821571893138939</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.874534459238119</v>
+        <v>3.766028032173327</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67402853597316</v>
+        <v>3.674028535973162</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.646450680168726</v>
+        <v>3.537944253103934</v>
       </c>
       <c r="D2020" t="n">
         <v>-4.634132446246029</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.792441277356568</v>
+        <v>1.683934850291775</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3821571893138939</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.875744993757063</v>
+        <v>3.76723856669227</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.650572422396048</v>
+        <v>3.542065995331255</v>
       </c>
       <c r="D2021" t="n">
         <v>-4.820796574380837</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.721897368329966</v>
+        <v>1.613390941265173</v>
       </c>
       <c r="F2021" t="n">
         <v>0.355418218489334</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.863823353489649</v>
+        <v>3.755316926424856</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.645650275132237</v>
+        <v>3.537143848067445</v>
       </c>
       <c r="D2022" t="n">
         <v>-4.966817261294799</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.65856694630057</v>
+        <v>1.550060519235778</v>
       </c>
       <c r="F2022" t="n">
         <v>0.346335126695477</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.853451351149524</v>
+        <v>3.744944924084731</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830332</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.807854331831281</v>
+        <v>3.699347904766489</v>
       </c>
       <c r="D2023" t="n">
         <v>-5.058531270404384</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.784085399355781</v>
+        <v>1.675578972290988</v>
       </c>
       <c r="F2023" t="n">
         <v>0.346335126695477</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.015655407848568</v>
+        <v>3.907148980783775</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071553</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.802700969795096</v>
+        <v>3.694194542730303</v>
       </c>
       <c r="D2024" t="n">
         <v>-5.090182929464353</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.766271373695607</v>
+        <v>1.657764946630814</v>
       </c>
       <c r="F2024" t="n">
         <v>0.3411666694510368</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.007400971465718</v>
+        <v>3.898894544400925</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.812930387363587</v>
+        <v>3.704423960298794</v>
       </c>
       <c r="D2025" t="n">
         <v>-5.172117747733236</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.743726863956545</v>
+        <v>1.635220436891752</v>
       </c>
       <c r="F2025" t="n">
         <v>0.3312319238639566</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.011669541681961</v>
+        <v>3.903163114617168</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.821856025819489</v>
+        <v>3.713349598754697</v>
       </c>
       <c r="D2026" t="n">
         <v>-5.274093869981644</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.711862053513084</v>
+        <v>1.603355626448292</v>
       </c>
       <c r="F2026" t="n">
         <v>0.229255801615549</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.959409506788819</v>
+        <v>3.850903079724026</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231808</v>
+        <v>3.79829678423181</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.814008913063665</v>
+        <v>3.705502485998872</v>
       </c>
       <c r="D2027" t="n">
         <v>-5.164087586504422</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.748017454148148</v>
+        <v>1.639511027083356</v>
       </c>
       <c r="F2027" t="n">
         <v>0.2524603735328242</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.965485137183359</v>
+        <v>3.856978710118567</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818525</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.818258923785639</v>
+        <v>3.709752496720846</v>
       </c>
       <c r="D2028" t="n">
         <v>-5.021028010763496</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.809491295166493</v>
+        <v>1.7009848681017</v>
       </c>
       <c r="F2028" t="n">
         <v>0.2604738001228035</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.974543203859321</v>
+        <v>3.866036776794529</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.825519806668175</v>
+        <v>3.717013379603382</v>
       </c>
       <c r="D2029" t="n">
         <v>-4.719581285291659</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.937330868237764</v>
+        <v>1.828824441172971</v>
       </c>
       <c r="F2029" t="n">
         <v>0.5619205255946408</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.16267212202496</v>
+        <v>4.054165694960167</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.826490984420885</v>
+        <v>3.717984557356093</v>
       </c>
       <c r="D2030" t="n">
         <v>-4.744171529526843</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.928465948296401</v>
+        <v>1.819959521231608</v>
       </c>
       <c r="F2030" t="n">
         <v>0.5619205255946408</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.16364329977767</v>
+        <v>4.055136872712877</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.718827461735848</v>
       </c>
       <c r="D2031" t="n">
         <v>-4.693133153520322</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.949724203078765</v>
+        <v>1.841217776013972</v>
       </c>
       <c r="F2031" t="n">
         <v>0.5619205255946408</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.164486204157425</v>
+        <v>4.055979777092633</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.737865560609994</v>
       </c>
       <c r="D2032" t="n">
         <v>-4.651993858653691</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.985218019899563</v>
+        <v>1.87671159283477</v>
       </c>
       <c r="F2032" t="n">
         <v>0.6030598204612716</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.20820787995155</v>
+        <v>4.099701452886757</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.554049556733928</v>
       </c>
       <c r="D2033" t="n">
         <v>-4.555358946635051</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.840055980830953</v>
+        <v>1.73154955376616</v>
       </c>
       <c r="F2033" t="n">
         <v>0.6996947324799115</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.082372823286669</v>
+        <v>3.973866396221876</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.557551600807892</v>
       </c>
       <c r="D2034" t="n">
         <v>-4.685939681165894</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.79132573109258</v>
+        <v>1.682819304027788</v>
       </c>
       <c r="F2034" t="n">
         <v>0.569113997949069</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.007526426642126</v>
+        <v>3.899019999577334</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.541978419883975</v>
       </c>
       <c r="D2035" t="n">
         <v>-4.521443346974932</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.841551083845048</v>
+        <v>1.733044656780255</v>
       </c>
       <c r="F2035" t="n">
         <v>0.7336103321400309</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.090651046232787</v>
+        <v>3.982144619167994</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.541166130320405</v>
       </c>
       <c r="D2036" t="n">
         <v>-4.444344745433059</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.871578234898226</v>
+        <v>1.763071807833434</v>
       </c>
       <c r="F2036" t="n">
         <v>0.7336103321400309</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.089838756669216</v>
+        <v>3.981332329604424</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.551034909445477</v>
       </c>
       <c r="D2037" t="n">
         <v>-4.454729940322949</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.877292936067343</v>
+        <v>1.76878650900255</v>
       </c>
       <c r="F2037" t="n">
         <v>0.7232251372501416</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.093476418860355</v>
+        <v>3.984969991795563</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.621871915221902</v>
       </c>
       <c r="D2038" t="n">
         <v>-4.473318099045174</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.940694678354878</v>
+        <v>1.832188251290086</v>
       </c>
       <c r="F2038" t="n">
         <v>0.7046369785279163</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.153160529403445</v>
+        <v>4.044654102338653</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.618740926040201</v>
       </c>
       <c r="D2039" t="n">
         <v>-4.47361664574121</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.937444270494762</v>
+        <v>1.82893784342997</v>
       </c>
       <c r="F2039" t="n">
         <v>0.7043384318318804</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.149850412204122</v>
+        <v>4.04134398513933</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.623271820979592</v>
       </c>
       <c r="D2040" t="n">
         <v>-4.372793512050782</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.982304418910325</v>
+        <v>1.873797991845532</v>
       </c>
       <c r="F2040" t="n">
         <v>0.7168026473162342</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.161859836434125</v>
+        <v>4.053353409369333</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.623401074458136</v>
       </c>
       <c r="D2041" t="n">
         <v>-4.182012151298375</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.058746216689831</v>
+        <v>1.950239789625038</v>
       </c>
       <c r="F2041" t="n">
         <v>0.9075840080686416</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.276457906364113</v>
+        <v>4.167951479299321</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.603237920195732</v>
       </c>
       <c r="D2042" t="n">
         <v>-4.075048793448953</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.081368405567196</v>
+        <v>1.972861978502404</v>
       </c>
       <c r="F2042" t="n">
         <v>0.9660486160284431</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.291373516877591</v>
+        <v>4.182867089812798</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.63820485680779</v>
       </c>
       <c r="D2043" t="n">
         <v>-4.019718205547191</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.138467577339959</v>
+        <v>2.029961150275167</v>
       </c>
       <c r="F2043" t="n">
         <v>1.021379203930205</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.359538806230707</v>
+        <v>4.251032379165914</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.631891424709228</v>
       </c>
       <c r="D2044" t="n">
         <v>-4.007664078634228</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.136975796006582</v>
+        <v>2.028469368941789</v>
       </c>
       <c r="F2044" t="n">
         <v>1.033433330843168</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.360457850279922</v>
+        <v>4.25195142321513</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.633772054893364</v>
       </c>
       <c r="D2045" t="n">
         <v>-4.048819198202449</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.12239437836343</v>
+        <v>2.013887951298637</v>
       </c>
       <c r="F2045" t="n">
         <v>0.9922782112749471</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.337645408723125</v>
+        <v>4.229138981658332</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.646623080771247</v>
       </c>
       <c r="D2046" t="n">
         <v>-3.980770635510919</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.162464829317924</v>
+        <v>2.053958402253132</v>
       </c>
       <c r="F2046" t="n">
         <v>1.060326773966477</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.391325572215925</v>
+        <v>4.282819145151133</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013426</v>
+        <v>3.645256780013428</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.666825750944841</v>
       </c>
       <c r="D2047" t="n">
         <v>-4.21237102868042</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.090027342223718</v>
+        <v>1.981520915158925</v>
       </c>
       <c r="F2047" t="n">
         <v>1.060326773966477</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.41152824238952</v>
+        <v>4.303021815324727</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498971</v>
+        <v>3.666747201498973</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.758938414076515</v>
+        <v>3.650431987011723</v>
       </c>
       <c r="D2048" t="n">
         <v>-4.262422574209639</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.053612960078913</v>
+        <v>1.94510653301412</v>
       </c>
       <c r="F2048" t="n">
         <v>1.060326773966477</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.395134478456402</v>
+        <v>4.28662805139161</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.6700487028001</v>
+        <v>3.670048702800102</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.719190327669982</v>
+        <v>3.610683900605189</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.437529406786084</v>
+        <v>-4.329953313139472</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.943822140641801</v>
+        <v>1.878346151035653</v>
       </c>
       <c r="F2049" t="n">
         <v>1.060326773966477</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.355386392049868</v>
+        <v>4.246879964985076</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660852</v>
+        <v>3.745573148660854</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.726212946666922</v>
+        <v>3.617706519602129</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.406243386245628</v>
+        <v>-4.298667292599017</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.963359167854923</v>
+        <v>1.897883178248775</v>
       </c>
       <c r="F2050" t="n">
         <v>1.091612794506932</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.381180623371081</v>
+        <v>4.272674196306289</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73057047339509</v>
+        <v>3.730570473395091</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.825383946239826</v>
+        <v>3.716877519175034</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.253217994132344</v>
+        <v>-4.145641900485733</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.123740324273141</v>
+        <v>2.058264334666994</v>
       </c>
       <c r="F2051" t="n">
         <v>1.244638186620216</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.572166858211957</v>
+        <v>4.463660431147164</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.012850171148119</v>
+        <v>3.904343744083326</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.281525308005614</v>
+        <v>-4.173949214359003</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.299883623632126</v>
+        <v>2.234407634025978</v>
       </c>
       <c r="F2052" t="n">
         <v>1.244638186620216</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.759633083120249</v>
+        <v>4.651126656055457</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.982253122502201</v>
+        <v>3.873746695437409</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.448118533119136</v>
+        <v>-4.340542439472525</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.202649284940799</v>
+        <v>2.137173295334652</v>
       </c>
       <c r="F2053" t="n">
         <v>1.078044961506694</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.629080099406218</v>
+        <v>4.520573672341426</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285649</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.985929525163919</v>
+        <v>3.877423098099127</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.42508273975757</v>
+        <v>-4.317506646110959</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.215540004947144</v>
+        <v>2.150064015340996</v>
       </c>
       <c r="F2054" t="n">
         <v>1.078044961506694</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.632756502067935</v>
+        <v>4.524250075003144</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.983547580287414</v>
+        <v>3.875041153222622</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.395836759301874</v>
+        <v>-4.288260665655263</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.224856452252918</v>
+        <v>2.15938046264677</v>
       </c>
       <c r="F2055" t="n">
         <v>1.078044961506694</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.630374557191431</v>
+        <v>4.521868130126639</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.980840819445049</v>
+        <v>3.872334392380257</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.502762307179725</v>
+        <v>-4.395186213533114</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.179379472259412</v>
+        <v>2.113903482653265</v>
       </c>
       <c r="F2056" t="n">
         <v>0.9711194136288425</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.563512467622355</v>
+        <v>4.455006040557563</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.982269621588284</v>
+        <v>3.873763194523491</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.647780865686974</v>
+        <v>-4.540204772040362</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.122800850999747</v>
+        <v>2.057324861393599</v>
       </c>
       <c r="F2057" t="n">
         <v>0.8261008551215939</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.47793013466124</v>
+        <v>4.369423707596448</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.082200860846037</v>
+        <v>3.973694433781244</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.766122631471691</v>
+        <v>-4.65854653782508</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.175395383943613</v>
+        <v>2.109919394337465</v>
       </c>
       <c r="F2058" t="n">
         <v>0.836786893684484</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.584272997056727</v>
+        <v>4.475766569991935</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790805</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.079986557971975</v>
+        <v>3.971480130907183</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.817533053792399</v>
+        <v>-4.709956960145788</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.152616912141268</v>
+        <v>2.08714092253512</v>
       </c>
       <c r="F2059" t="n">
         <v>0.836786893684484</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.582058694182666</v>
+        <v>4.473552267117873</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437331</v>
+        <v>3.704757949437333</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.079889686046265</v>
+        <v>3.971383258981472</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.896952505000151</v>
+        <v>-4.78937641135354</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.120752259732457</v>
+        <v>2.055276270126309</v>
       </c>
       <c r="F2060" t="n">
         <v>0.836786893684484</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.581961822256956</v>
+        <v>4.473455395192163</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298398</v>
+        <v>3.736804952298399</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.079883579604308</v>
+        <v>3.971377152539516</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.992415502917368</v>
+        <v>-4.884839409270757</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.082560954123614</v>
+        <v>2.017084964517466</v>
       </c>
       <c r="F2061" t="n">
         <v>0.836786893684484</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.581955715814999</v>
+        <v>4.473449288750206</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218</v>
+        <v>3.715372960218001</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.077979976166919</v>
+        <v>3.969473549102126</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.928039592066654</v>
+        <v>-4.820463498420042</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.10640771502651</v>
+        <v>2.040931725420362</v>
       </c>
       <c r="F2062" t="n">
         <v>0.9011628045351991</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.618677658888038</v>
+        <v>4.510171231823246</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353535</v>
+        <v>3.736089413353537</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.083713793914646</v>
+        <v>3.975207366849853</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.983408754198847</v>
+        <v>-4.875832660552236</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.089993867921359</v>
+        <v>2.024517878315211</v>
       </c>
       <c r="F2063" t="n">
         <v>0.9011628045351991</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.624411476635765</v>
+        <v>4.515905049570972</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.73682287011328</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.083252157257578</v>
+        <v>3.974745730192785</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.028846534029674</v>
+        <v>-4.921270440383063</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.071357119331961</v>
+        <v>2.005881129725812</v>
       </c>
       <c r="F2064" t="n">
         <v>0.8583178138570395</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.598242845571802</v>
+        <v>4.489736418507009</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113687</v>
+        <v>3.790272500113689</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.103126550107897</v>
+        <v>3.994620123043104</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.940639699882096</v>
+        <v>-4.833063606235485</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.126514245841311</v>
+        <v>2.061038256235163</v>
       </c>
       <c r="F2065" t="n">
         <v>0.8583178138570395</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.618117238422121</v>
+        <v>4.509610811357328</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016443</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.086827250632624</v>
+        <v>3.978320823567832</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.834604704676787</v>
+        <v>-4.727028611030176</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.152628944448162</v>
+        <v>2.087152954842014</v>
       </c>
       <c r="F2066" t="n">
         <v>0.8583178138570395</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.601817938946849</v>
+        <v>4.493311511882056</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.794705093307674</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.08925820009667</v>
+        <v>3.980751773031877</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.651393041543692</v>
+        <v>-4.54381694789708</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.228344559165446</v>
+        <v>2.162868569559298</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.8583178138570395</v>
+        <v>1.041529476990135</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.604248888410894</v>
+        <v>4.605669459225958</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.055049385944559</v>
+        <v>3.946542958879767</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.579671594529841</v>
+        <v>-4.472095500883229</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.222824323818876</v>
+        <v>2.157348334212728</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.9300392608708902</v>
+        <v>1.113250924003985</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.613072942467094</v>
+        <v>4.614493513282158</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394116</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.001965131865731</v>
+        <v>3.893458704800938</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.557298568922135</v>
+        <v>-4.449722475275523</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.17868927998313</v>
+        <v>2.113213290376982</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.9412950119837917</v>
+        <v>1.124506675116887</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.566742139056006</v>
+        <v>4.56816270987107</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456732</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.187163336751087</v>
+        <v>4.078656909686294</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.590314864832879</v>
+        <v>-4.482738771186268</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.350680966504187</v>
+        <v>2.285204976898039</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.8718576353170402</v>
+        <v>1.055069298450135</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.710277917941311</v>
+        <v>4.711698488756375</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883676</v>
+        <v>3.71376253688368</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.179084562579336</v>
+        <v>4.070578135514543</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.578787229183271</v>
+        <v>-4.471211135536659</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.34721324659228</v>
+        <v>2.281737256986132</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.9308582935184027</v>
+        <v>1.114069956651498</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.737599538690377</v>
+        <v>4.739020109505442</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236299</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.182752675101124</v>
+        <v>4.074246248036332</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.676128730525639</v>
+        <v>-4.568552636879028</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.311944758577121</v>
+        <v>2.246468768970973</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.8864381113529143</v>
+        <v>1.069649774486009</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.714615541912873</v>
+        <v>4.716036112727937</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427683</v>
+        <v>3.705201079427686</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.184003757293962</v>
+        <v>4.07549733022917</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.761984759865606</v>
+        <v>-4.654408666218995</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.278853429033973</v>
+        <v>2.213377439427824</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.8440620421267793</v>
+        <v>1.027273705259874</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.69044098257003</v>
+        <v>4.691861553385094</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610384</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.166422959114464</v>
+        <v>4.057916532049672</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.770821557281725</v>
+        <v>-4.663245463635114</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.257737911888027</v>
+        <v>2.192261922281879</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.8366198694854285</v>
+        <v>1.019831532618523</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.668394880805722</v>
+        <v>4.669815451620786</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667454</v>
+        <v>3.715544411667458</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.176587470159514</v>
+        <v>4.068081043094721</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.862204119847184</v>
+        <v>-4.754628026200573</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.231349397906893</v>
+        <v>2.165873408300745</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.7452373069199703</v>
+        <v>0.9284489700530651</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.623729854311496</v>
+        <v>4.62515042512656</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.67397837488919</v>
+        <v>3.673978374889193</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.278715727983782</v>
+        <v>4.170209300918989</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.850497401860178</v>
+        <v>-4.742921308213567</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.338160342925963</v>
+        <v>2.272684353319815</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.7569440249069767</v>
+        <v>0.9401556880400715</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.732882142927968</v>
+        <v>4.734302713743032</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409566</v>
+        <v>3.682476099409569</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.281748066715187</v>
+        <v>4.173241639650394</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.750833897776515</v>
+        <v>-4.643257804129904</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.381058083290833</v>
+        <v>2.315582093684685</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.8201311081106631</v>
+        <v>1.003342771243758</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.773826731581584</v>
+        <v>4.775247302396649</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452574</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.494652899993245</v>
+        <v>4.386146472928452</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.761149995942867</v>
+        <v>-4.653573902296256</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.589836477302351</v>
+        <v>2.524360487696202</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.8201311081106631</v>
+        <v>1.003342771243758</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.986731564859642</v>
+        <v>4.988152135674707</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762286</v>
+        <v>3.623960959762289</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.493831566905334</v>
+        <v>4.385325139840542</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.761056027925495</v>
+        <v>-4.653479934278884</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.589052731421389</v>
+        <v>2.523576741815241</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.8205009694579811</v>
+        <v>1.003712632591076</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.986132148580123</v>
+        <v>4.987552719395188</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988017</v>
+        <v>3.63321346798802</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.488063552849688</v>
+        <v>4.379557125784896</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.768274852125339</v>
+        <v>-4.660698758478728</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.580397187685805</v>
+        <v>2.514921198079657</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.8205009694579811</v>
+        <v>1.003712632591076</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.980364134524477</v>
+        <v>4.981784705339542</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740926</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.488063552849688</v>
+        <v>4.379557125784896</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.767326429007301</v>
+        <v>-4.659750335360689</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.580776556933021</v>
+        <v>2.515300567326872</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.8205009694579811</v>
+        <v>1.003712632591076</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.980364134524477</v>
+        <v>4.981784705339542</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,45 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.877146832689213</v>
+        <v>3.673485397508232</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.50079116083078</v>
+        <v>4.392284733765988</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.924394887262924</v>
+        <v>-4.816818793616314</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.530676781611863</v>
+        <v>2.465200792005715</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.8205009694579811</v>
+        <v>1.003712632591076</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.993091742505569</v>
+        <v>4.994512313320634</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="2" t="n">
+        <v>45545</v>
+      </c>
+      <c r="B2083" t="n">
+        <v>3.806741384178846</v>
+      </c>
+      <c r="C2083" t="n">
+        <v>4.525388456506701</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>-4.816818793616314</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>2.465200792005715</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>1.003712632591076</v>
+      </c>
+      <c r="G2083" t="n">
+        <v>4.518452253493069</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240910.xlsx
+++ b/tame_output/ON/bt/strategyON_20240910.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-40.8%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>140.9%</t>
+          <t>158.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-53.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.7%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.7%</t>
+          <t>422.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-643.3%</t>
+          <t>-660.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-129.7%</t>
+          <t>-125.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-317.4%</t>
+          <t>-353.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-123.6%</t>
+          <t>-113.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911636</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213492</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.499461964536028</v>
+        <v>-8.382578673907894</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2399668618950543</v>
+        <v>-0.1932135456438004</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.253826633672349</v>
+        <v>-1.136943343044216</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.407878368029695</v>
+        <v>2.478008342406575</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.674586381922571</v>
+        <v>-8.557703091294437</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2954614081021552</v>
+        <v>-0.2487080918509013</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.428951051058893</v>
+        <v>-1.312067760430759</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.317358938345286</v>
+        <v>2.387488912722166</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.909038475937061</v>
+        <v>-8.792155185308927</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3964614106095468</v>
+        <v>-0.3497080943582929</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.428951051058893</v>
+        <v>-1.312067760430759</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.310139773443689</v>
+        <v>2.38026974782057</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.013413206963508</v>
+        <v>-8.896529916335373</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4448834937941015</v>
+        <v>-0.3981301775428476</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.533325782085339</v>
+        <v>-1.416442491457205</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.240842744053846</v>
+        <v>2.310972718430726</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.175926672662092</v>
+        <v>-9.059043382033957</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5087730902349792</v>
+        <v>-0.4620197739837253</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.630959212504025</v>
+        <v>-1.514075921875892</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.18337847564119</v>
+        <v>2.25350845001807</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.301963466030381</v>
+        <v>-9.185080175402247</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5564940789531803</v>
+        <v>-0.5097407627019264</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.48882429906615</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.20122317795615</v>
+        <v>2.27135315233303</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.24489169413445</v>
+        <v>-9.128008403506316</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5296750345084069</v>
+        <v>-0.482921718257153</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.48882429906615</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.205213513642551</v>
+        <v>2.275343488019431</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.386563535858571</v>
+        <v>-9.269680245230436</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5878189980967967</v>
+        <v>-0.5410656818455428</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.48882429906615</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.20373828674381</v>
+        <v>2.273868261120689</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.336972691433736</v>
+        <v>-9.220089400805602</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5529292501619909</v>
+        <v>-0.506175933910737</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.556116745269449</v>
+        <v>-1.439233454641315</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.248546203563582</v>
+        <v>2.318676177940462</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.18805435696188</v>
+        <v>-9.071171066333745</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5064130500199311</v>
+        <v>-0.4596597337686772</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.524867154534276</v>
+        <v>-1.407983863906142</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.254244824358003</v>
+        <v>2.324374798734883</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.96220920424247</v>
+        <v>-8.845325913614335</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4064959158959582</v>
+        <v>-0.3597425996447048</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.366057188318979</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.28897990274651</v>
+        <v>2.35910987712339</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.837630547904878</v>
+        <v>-8.720747257276743</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3555253088048627</v>
+        <v>-0.3087719925536088</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.366057188318979</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.290119047302569</v>
+        <v>2.360249021679449</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.812593866336368</v>
+        <v>-8.695710575708233</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3428768620153511</v>
+        <v>-0.2961235457640972</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.340728100768243</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.307950273995118</v>
+        <v>2.378080248371998</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.740460691048487</v>
+        <v>-8.623577400420352</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3082898876615623</v>
+        <v>-0.2615365714103084</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.340728100768243</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.313683978233754</v>
+        <v>2.383813952610634</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669094298438839</v>
+        <v>-8.552211007810705</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2894805930115685</v>
+        <v>-0.2427272767603146</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.269361708158595</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.346766551405678</v>
+        <v>2.416896525782558</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.575635264453615</v>
+        <v>-8.45875197382548</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2619804607303862</v>
+        <v>-0.2152271444791323</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.269361708158595</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.33688307009277</v>
+        <v>2.40701304446965</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.564982082900183</v>
+        <v>-8.448098792272049</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2595537486083872</v>
+        <v>-0.2128004323571333</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.269361708158595</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.335048509593396</v>
+        <v>2.405178483970277</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467075044223693</v>
+        <v>-8.350191753595558</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.220691248111252</v>
+        <v>-0.1739379318599981</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.318259248926172</v>
+        <v>-1.201375958298039</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.37553964453627</v>
+        <v>2.44566961891315</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443121503247735</v>
+        <v>-8.3262382126196</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.210441325575375</v>
+        <v>-0.1636880093241211</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.294305707950215</v>
+        <v>-1.177422417322081</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.390580275267338</v>
+        <v>2.460710249644218</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179061564924938</v>
+        <v>-8.062178274296803</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1180776664080083</v>
+        <v>-0.07132435015675487</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.030245769627419</v>
+        <v>-0.9133624789992849</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.535755922099263</v>
+        <v>2.605885896476143</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.4719819414201</v>
+        <v>-7.355098650791965</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1619671493336261</v>
+        <v>0.2087204655848796</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.030245769627419</v>
+        <v>-0.9133624789992849</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.532968888438962</v>
+        <v>2.603098862815842</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.431797643053909</v>
+        <v>-7.314914352425775</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1783844925679436</v>
+        <v>0.2251378088191971</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9900614712612278</v>
+        <v>-0.8731781806330942</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.557423091346518</v>
+        <v>2.627553065723398</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.268397772114547</v>
+        <v>-7.151514481486412</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2431112621644456</v>
+        <v>0.289864578415699</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8266616003218653</v>
+        <v>-0.7097783096937317</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.654829835130893</v>
+        <v>2.724959809507773</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.034916549884948</v>
+        <v>-6.918033259256814</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3444281798941371</v>
+        <v>0.391181496145391</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5931803780922668</v>
+        <v>-0.4762970874641331</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.802842997306504</v>
+        <v>2.872972971683384</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.885250158877433</v>
+        <v>-6.768366868249299</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4014025259841842</v>
+        <v>0.4481558422354377</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5002768868497308</v>
+        <v>-0.3833935962215972</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.855692881739067</v>
+        <v>2.925822856115947</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>2.948613372791267</v>
+        <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.752974685246547</v>
+        <v>-6.651892026726289</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2470670743789012</v>
+        <v>0.3960065648517963</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3680014132188442</v>
+        <v>-0.2669187546985879</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.727812524859961</v>
+        <v>2.896968547036907</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
-        <v>2.951428433478904</v>
+        <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.597236352686805</v>
+        <v>-6.496153694166547</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3121774680904346</v>
+        <v>0.4611169585633297</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2122630806591026</v>
+        <v>-0.1111804221388464</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.824070585083442</v>
+        <v>2.993226607260389</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>2.964334774702563</v>
+        <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.512271685957485</v>
+        <v>-6.411189027437228</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3590696760058214</v>
+        <v>0.5080091664787161</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.127298413929783</v>
+        <v>-0.02621575540952681</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.887955726344693</v>
+        <v>3.057111748521639</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.836358845103343</v>
+        <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.617861675730589</v>
+        <v>-6.516779017210332</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1888577504973603</v>
+        <v>0.3377972409702559</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2328884037028874</v>
+        <v>-0.1318057451826312</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.696625802881611</v>
+        <v>2.865781825058558</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.88490318698043</v>
+        <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.549627091105162</v>
+        <v>-6.448544432584905</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2646959262246176</v>
+        <v>0.4136354166975131</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2144730808303514</v>
+        <v>-0.1133904223100952</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.756219338482219</v>
+        <v>2.925375360659165</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.768282378342023</v>
+        <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.401687049697562</v>
+        <v>-6.300604391177306</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2072511341492502</v>
+        <v>0.3561906246221458</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1941521649217938</v>
+        <v>-0.09306950640153761</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.651791079388947</v>
+        <v>2.820947101565893</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.759568392088545</v>
+        <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.348717527443574</v>
+        <v>-6.247634868923317</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2197249567973678</v>
+        <v>0.3686644472702629</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.04009998414754873</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.674858806487862</v>
+        <v>2.844014828664808</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.752607779993451</v>
+        <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.182929331483283</v>
+        <v>-6.081846672963026</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2790796230863908</v>
+        <v>0.4280191135592863</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.04009998414754873</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.667898194392769</v>
+        <v>2.837054216569715</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.767070134374594</v>
+        <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.149566125004514</v>
+        <v>-6.048483466484257</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3068872600590415</v>
+        <v>0.4558267505319367</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.04009998414754873</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.682360548773912</v>
+        <v>2.851516570950858</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.76160225483379</v>
+        <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.041306987881993</v>
+        <v>-5.940224329361736</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3447230353672452</v>
+        <v>0.4936625258401404</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.04009998414754873</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.676892669233107</v>
+        <v>2.846048691410053</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.759100348844366</v>
+        <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.918015853064862</v>
+        <v>-5.816933194544605</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3915375833046744</v>
+        <v>0.5404770737775699</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.01789150785067445</v>
+        <v>0.08319115066958177</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.748365444133962</v>
+        <v>2.917521466310908</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.766801327081692</v>
+        <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.865318985933571</v>
+        <v>-5.764236327413314</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.420317308394516</v>
+        <v>0.5692567988674115</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.03480535928061673</v>
+        <v>0.135888017800873</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.787684542650062</v>
+        <v>2.956840564827008</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.762582035428742</v>
+        <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.621553543950126</v>
+        <v>-5.520470885429869</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5136041935349445</v>
+        <v>0.66254368400784</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.03480535928061673</v>
+        <v>0.135888017800873</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.783465250997113</v>
+        <v>2.952621273174059</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.764706349348758</v>
+        <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.531777871573654</v>
+        <v>-5.430695213053397</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5516387764055493</v>
+        <v>0.7005782668784448</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.09640480419492675</v>
+        <v>0.197487462715183</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.822549231865715</v>
+        <v>2.991705254042661</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.75744842433246</v>
+        <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.281927477624579</v>
+        <v>-5.180844819104323</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6443210089688813</v>
+        <v>0.7932604994417769</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.09640480419492675</v>
+        <v>0.197487462715183</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.815291306849417</v>
+        <v>2.984447329026363</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.761047547853109</v>
+        <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.106035385157147</v>
+        <v>-5.004952726636891</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.718276969476503</v>
+        <v>0.8672164599493983</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.09640480419492675</v>
+        <v>0.197487462715183</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.818890430370065</v>
+        <v>2.988046452547012</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.774375053907663</v>
+        <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.934588922134684</v>
+        <v>-4.833506263614427</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.800183060740042</v>
+        <v>0.9491225512129373</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2678512672173899</v>
+        <v>0.3689339257376461</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.935085814238097</v>
+        <v>3.104241836415043</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.77339553152396</v>
+        <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.854566635025563</v>
+        <v>-4.753483976505306</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8312124531999874</v>
+        <v>0.9801519436728827</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3478735543265108</v>
+        <v>0.4489562128467671</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.982119664119867</v>
+        <v>3.151275686296813</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.778090332578277</v>
+        <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.790930892791629</v>
+        <v>-4.689848234271372</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8613615511478785</v>
+        <v>1.010301041620774</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4115092965604454</v>
+        <v>0.5125919550807017</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.024995910514545</v>
+        <v>3.194151932691491</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.759284591362073</v>
+        <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.697233574575233</v>
+        <v>-4.596150916054976</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.880034737218232</v>
+        <v>1.028974227691128</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4115092965604454</v>
+        <v>0.5125919550807017</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.00619016929834</v>
+        <v>3.175346191475287</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.76102766798695</v>
+        <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.707736197640522</v>
+        <v>-4.606653539120265</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8775767646169939</v>
+        <v>1.026516255089889</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4010066734951565</v>
+        <v>0.5020893320154127</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.001631672084044</v>
+        <v>3.170787694260991</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.76495698182177</v>
+        <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.595249936971648</v>
+        <v>-4.494167278451391</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.926500582719364</v>
+        <v>1.075440073192259</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4010066734951565</v>
+        <v>0.5020893320154127</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.005560985918864</v>
+        <v>3.174717008095811</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.76563556573911</v>
+        <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.577536250093782</v>
+        <v>-4.476453591573526</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9342646413878501</v>
+        <v>1.083204131860745</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4041880023920733</v>
+        <v>0.5052706609123295</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.008148367174354</v>
+        <v>3.177304389351301</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.762633636959104</v>
+        <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.454061978780764</v>
+        <v>-4.352979320260507</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9806524211330507</v>
+        <v>1.129591911605946</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4041880023920733</v>
+        <v>0.5052706609123295</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.005146438394348</v>
+        <v>3.174302460571294</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.764212673969718</v>
+        <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.234041180743754</v>
+        <v>-4.132958522223497</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.070239777358469</v>
+        <v>1.219179267831365</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5454078474600536</v>
+        <v>0.6464905059803098</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.09145738244575</v>
+        <v>3.260613404622696</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.780106856771541</v>
+        <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.101173491680476</v>
+        <v>-4.000090833160218</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.139281035785604</v>
+        <v>1.288220526258499</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5454078474600536</v>
+        <v>0.6464905059803098</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.107351565247574</v>
+        <v>3.27650758742452</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.781252701211843</v>
+        <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.981000408315977</v>
+        <v>-3.879917749795719</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.188496113571705</v>
+        <v>1.337435604044601</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6655809308245525</v>
+        <v>0.7666635893448087</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.180601259706575</v>
+        <v>3.349757281883521</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.791340803773283</v>
+        <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.845747046986</v>
+        <v>-3.744664388465742</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.252685560665136</v>
+        <v>1.401625051138031</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8008342921545296</v>
+        <v>0.9019169506747858</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.271841379066001</v>
+        <v>3.440997401242948</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.777378295174709</v>
+        <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.905621874343693</v>
+        <v>-3.804539215823434</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.214773121123484</v>
+        <v>1.36371261159638</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7409594647968375</v>
+        <v>0.8420421233170937</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.221953974052811</v>
+        <v>3.391109996229758</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.792667464408917</v>
+        <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.785801643432855</v>
+        <v>-3.684718984912597</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.277990382722028</v>
+        <v>1.426929873194924</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7409594647968375</v>
+        <v>0.8420421233170937</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.23724314328702</v>
+        <v>3.406399165463966</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.700311663731359</v>
+        <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.788271349894661</v>
+        <v>-3.687188691374403</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.184646699459747</v>
+        <v>1.333586189932643</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7384897583350314</v>
+        <v>0.8395724168552876</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.143405518732378</v>
+        <v>3.312561540909324</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.61957352521666</v>
+        <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.856641536218671</v>
+        <v>-3.755558877698413</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.076560486415445</v>
+        <v>1.22549997688834</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.8488481158915026</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.068232799639409</v>
+        <v>3.237388821816355</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.610010233848552</v>
+        <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.968513815844822</v>
+        <v>-3.867431157324563</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.022248283196876</v>
+        <v>1.171187773669771</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.8488481158915026</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.0586695082713</v>
+        <v>3.227825530448246</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.747041070540754</v>
+        <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.024033891737411</v>
+        <v>-3.922951233217153</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.137071089532042</v>
+        <v>1.286010580004938</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.8488481158915026</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.195700344963502</v>
+        <v>3.364856367140448</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.751608302532542</v>
+        <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.848559631944942</v>
+        <v>-3.747476973424684</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.211828025440818</v>
+        <v>1.360767515913713</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.8488481158915026</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.20026757695529</v>
+        <v>3.369423599132236</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.727350331293749</v>
+        <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.840635257360028</v>
+        <v>-3.73955259883977</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.19073980403599</v>
+        <v>1.339679294508886</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.8488481158915026</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.176009605716497</v>
+        <v>3.345165627893443</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.655888644695199</v>
+        <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.834357054790179</v>
+        <v>-3.733274396269921</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.12178939846538</v>
+        <v>1.270728888938276</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7540436599410953</v>
+        <v>0.8551263184613516</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.108314840659856</v>
+        <v>3.277470862836803</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.666061031127331</v>
+        <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.743154131757624</v>
+        <v>-3.673421777066197</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.168442954110534</v>
+        <v>1.304842323051897</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7540436599410953</v>
+        <v>0.8551263184613516</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.118487227091988</v>
+        <v>3.287643249268935</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.661007301701191</v>
+        <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.656910668731246</v>
+        <v>-3.58717831403982</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.197886609894945</v>
+        <v>1.334285978836308</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7540436599410953</v>
+        <v>0.8551263184613516</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.113433497665849</v>
+        <v>3.282589519842795</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.652783077145717</v>
+        <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.702217488130226</v>
+        <v>-3.6324851334388</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.171539657579879</v>
+        <v>1.307939026521242</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7132334969318646</v>
+        <v>0.8143161554521208</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.080723175304836</v>
+        <v>3.249879197481782</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.653334950178818</v>
+        <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.731250592832528</v>
+        <v>-3.661518238141102</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.16047828873206</v>
+        <v>1.296877657673423</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7132334969318646</v>
+        <v>0.8143161554521208</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.081275048337937</v>
+        <v>3.250431070514884</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.582607642070184</v>
+        <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.638440111381668</v>
+        <v>-3.568707756690242</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.126875173203769</v>
+        <v>1.263274542145132</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8060439783827239</v>
+        <v>0.9071266369029801</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.066234029099819</v>
+        <v>3.235390051276765</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.584481117994785</v>
+        <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.682829580711096</v>
+        <v>-3.61309722601967</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.110992861396599</v>
+        <v>1.247392230337962</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7616545090532962</v>
+        <v>0.8627371675735525</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.041473823426763</v>
+        <v>3.210629845603709</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.579556826506508</v>
+        <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.799371185816439</v>
+        <v>-3.729638831125013</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.059451927866185</v>
+        <v>1.195851296807548</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6451129039479535</v>
+        <v>0.7461955624682097</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.96662456887528</v>
+        <v>3.135780591052227</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.585048122337175</v>
+        <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.839295280399011</v>
+        <v>-3.769562925707584</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.048973585863824</v>
+        <v>1.185372954805187</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6451129039479535</v>
+        <v>0.7461955624682097</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.972115864705947</v>
+        <v>3.141271886882894</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.596545324105714</v>
+        <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.867075678300364</v>
+        <v>-3.797343323608938</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.049358628471821</v>
+        <v>1.185757997413184</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6173325060466004</v>
+        <v>0.7184151645668566</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.966944827733675</v>
+        <v>3.136100849910621</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.434901044106367</v>
+        <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.985456351030502</v>
+        <v>-3.915723996339076</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8403620793804194</v>
+        <v>0.9767614483217821</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5501146538956242</v>
+        <v>0.6511973124158804</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.764969836443742</v>
+        <v>2.934125858620689</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.555050704825573</v>
+        <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.094070429473833</v>
+        <v>-4.024338074782408</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9170661087222927</v>
+        <v>1.053465477663655</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5501146538956242</v>
+        <v>0.6511973124158804</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.885119497162948</v>
+        <v>3.054275519339894</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.569563730927896</v>
+        <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.05866139122569</v>
+        <v>-3.988929036534265</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9457427501238729</v>
+        <v>1.082142119065235</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5501146538956242</v>
+        <v>0.6511973124158804</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.899632523265271</v>
+        <v>3.068788545442217</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.566983172270265</v>
+        <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.020277728667539</v>
+        <v>-3.950545373976114</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9585156564895019</v>
+        <v>1.094915025430864</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5884983164537754</v>
+        <v>0.6895809749740316</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.92008216214253</v>
+        <v>3.089238184319476</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.563712201115567</v>
+        <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.843161398632373</v>
+        <v>-3.773429043940948</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.02609121734887</v>
+        <v>1.162490586290233</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5884983164537754</v>
+        <v>0.6895809749740316</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.916811190987832</v>
+        <v>3.085967213164778</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.56439559287748</v>
+        <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.888253643465919</v>
+        <v>-3.818521288774494</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.008737711177365</v>
+        <v>1.145137080118728</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5266022732843856</v>
+        <v>0.6276849318046418</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.880356956848111</v>
+        <v>3.049512979025058</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.558182568183894</v>
+        <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.708878222227151</v>
+        <v>-3.639145867535726</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.074274854979286</v>
+        <v>1.210674223920649</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6833790314551043</v>
+        <v>0.7844616899753605</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.968209987056957</v>
+        <v>3.137366009233904</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.538990023515484</v>
+        <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.753892435747757</v>
+        <v>-3.684160081056332</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.037076624902634</v>
+        <v>1.173475993843996</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6530301361404997</v>
+        <v>0.7541127946607559</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.930808105199784</v>
+        <v>3.09996412737673</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.54468158585443</v>
+        <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.020896946020192</v>
+        <v>-3.951164591328768</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9359663831326053</v>
+        <v>1.072365752073968</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4586670980975511</v>
+        <v>0.5597497566178073</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.819881844712961</v>
+        <v>2.989037866889907</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.543885507750931</v>
+        <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.122094727457365</v>
+        <v>-4.05236237276594</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8946911924542378</v>
+        <v>1.0310905613956</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3902582845522319</v>
+        <v>0.4913409430724882</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.778040478482271</v>
+        <v>2.947196500659217</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.541485469305248</v>
+        <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.115583760843053</v>
+        <v>-4.045851406151628</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8948955406542796</v>
+        <v>1.031294909595642</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3902582845522319</v>
+        <v>0.4913409430724882</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.775640440036587</v>
+        <v>2.944796462213533</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.538010188513493</v>
+        <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.096545633135755</v>
+        <v>-4.02681327844433</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8990355109454433</v>
+        <v>1.035434879886806</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3320746732210373</v>
+        <v>0.4331573317412937</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.737254992446116</v>
+        <v>2.906411014623062</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.657304590147683</v>
+        <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.149061435410576</v>
+        <v>-4.079329080719151</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9973235916697054</v>
+        <v>1.133722960611068</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3320746732210373</v>
+        <v>0.4331573317412937</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.856549394080306</v>
+        <v>3.025705416257252</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.658137919133817</v>
+        <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.162928196744494</v>
+        <v>-4.093195842053069</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9926102161222718</v>
+        <v>1.129009585063634</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2942167564872144</v>
+        <v>0.3952994150074707</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.834667973026145</v>
+        <v>3.003823995203092</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.664146449530743</v>
+        <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.122445204822148</v>
+        <v>-4.052712850130724</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.014811943288136</v>
+        <v>1.151211312229498</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2942167564872144</v>
+        <v>0.3952994150074707</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.840676503423071</v>
+        <v>3.009832525600018</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.562096670807942</v>
+        <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.974702234587146</v>
+        <v>-3.904969879895722</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9718593526593362</v>
+        <v>1.108258721600699</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4620241137220976</v>
+        <v>0.5631067722423539</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.839311139041201</v>
+        <v>3.008467161218147</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.564890292339423</v>
+        <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.058523455861844</v>
+        <v>-3.98879110117042</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.941124485680938</v>
+        <v>1.0775238546223</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4620241137220976</v>
+        <v>0.5631067722423539</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.842104760572682</v>
+        <v>3.011260782749628</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.565552640731081</v>
+        <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.05237074980906</v>
+        <v>-3.982638395117635</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9442479164937101</v>
+        <v>1.080647285435073</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4681768197748818</v>
+        <v>0.5692594782951382</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.846458732596011</v>
+        <v>3.015614754772957</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.564633117471192</v>
+        <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.069180047959562</v>
+        <v>-3.999447693268137</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9366046739736196</v>
+        <v>1.073004042914982</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4513675216243802</v>
+        <v>0.5524501801446366</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.83545363044582</v>
+        <v>3.004609652622766</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.630968671268012</v>
+        <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.00688204918344</v>
+        <v>-3.937149694492015</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027859427280889</v>
+        <v>1.164258796222252</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4966617858988223</v>
+        <v>0.5977444444190787</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.928965742807306</v>
+        <v>3.098121764984253</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.43326067298214</v>
+        <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.805091851518283</v>
+        <v>-3.735359496826857</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9108675080610795</v>
+        <v>1.047266877002442</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6946799780679767</v>
+        <v>0.7957626365882331</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.850068659822926</v>
+        <v>3.019224681999872</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.503550905304315</v>
+        <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.855978564204477</v>
+        <v>-3.786246209513052</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9608030553087767</v>
+        <v>1.097202424250139</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6437932653817822</v>
+        <v>0.7448759239020386</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.889826864533384</v>
+        <v>3.058982886710331</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.518178641420358</v>
+        <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.76936782155467</v>
+        <v>-3.699635466863244</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.010075088484743</v>
+        <v>1.146474457426106</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7224189965869404</v>
+        <v>0.8235016551071969</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.951630039372523</v>
+        <v>3.120786061549469</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.51671462224503</v>
+        <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.829577119559954</v>
+        <v>-3.759844764868529</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9845273501073013</v>
+        <v>1.120926719048664</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6622096985816559</v>
+        <v>0.7632923571019123</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.914040441394024</v>
+        <v>3.08319646357097</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.515206240284959</v>
+        <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.780390470875603</v>
+        <v>-3.710658116184177</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.00269362762097</v>
+        <v>1.139092996562333</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6622096985816559</v>
+        <v>0.7632923571019123</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.912532059433953</v>
+        <v>3.081688081610899</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.515069107720395</v>
+        <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.736017339237034</v>
+        <v>-3.666284984545609</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.020305747711834</v>
+        <v>1.156705116653197</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7065828302202245</v>
+        <v>0.8076654887404809</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.93901880585253</v>
+        <v>3.108174828029476</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.509462901858985</v>
+        <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.758497690095919</v>
+        <v>-3.688765335404494</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005707401506871</v>
+        <v>1.142106770448233</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7065828302202245</v>
+        <v>0.8076654887404809</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.93341259999112</v>
+        <v>3.102568622168067</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190327</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.51584465888679</v>
+        <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.710841959534864</v>
+        <v>-3.641109604843438</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.031151450759097</v>
+        <v>1.16755081970046</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7542385607812802</v>
+        <v>0.8553212193015366</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.968387795355558</v>
+        <v>3.137543817532505</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569619</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.520737032261515</v>
+        <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.610323801036109</v>
+        <v>-3.540591446344683</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.076251087533324</v>
+        <v>1.212650456474687</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8547567192800347</v>
+        <v>0.9558393778002912</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.033591063829536</v>
+        <v>3.202747086006482</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557296</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.507491704737387</v>
+        <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.594418471603757</v>
+        <v>-3.52468611691233</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.069367891782137</v>
+        <v>1.2057672607235</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7756440585707958</v>
+        <v>0.8767267170910522</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.972878139879865</v>
+        <v>3.142034162056811</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932771</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.511589407348016</v>
+        <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.549580069995359</v>
+        <v>-3.479847715303932</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.091400955036125</v>
+        <v>1.227800323977488</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7801874915156652</v>
+        <v>0.8812701500359217</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.979701902257415</v>
+        <v>3.148857924434362</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.515750346979094</v>
+        <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.569078526237367</v>
+        <v>-3.499346171545941</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.0877625121704</v>
+        <v>1.224161881111763</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7321028502357609</v>
+        <v>0.8331855087560174</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.95501205712055</v>
+        <v>3.124168079297497</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.521629949506931</v>
+        <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.524875689151466</v>
+        <v>-3.45514333446004</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.111323249532597</v>
+        <v>1.24772261847396</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7763056873216614</v>
+        <v>0.8773883458419178</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.987413361899928</v>
+        <v>3.156569384076874</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.520039949976178</v>
+        <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.532435354988513</v>
+        <v>-3.462703000297087</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.106709383667026</v>
+        <v>1.243108752608389</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8311090913314807</v>
+        <v>0.9321917498517371</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.018705404775067</v>
+        <v>3.187861426952014</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.571287715159218</v>
+        <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.374143937449241</v>
+        <v>-3.304411582757815</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.221273715865774</v>
+        <v>1.357673084807137</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8311090913314807</v>
+        <v>0.9321917498517371</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.069953169958107</v>
+        <v>3.239109192135053</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.569728419753471</v>
+        <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.166501933814765</v>
+        <v>-3.096769579123339</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.302771221913818</v>
+        <v>1.439170590855181</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.038751094965957</v>
+        <v>1.139833753486213</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.192979076733045</v>
+        <v>3.362135098909992</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.564676647991741</v>
+        <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.115469841092237</v>
+        <v>-3.045737486400811</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.318132287241099</v>
+        <v>1.454531656182462</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.089783187688485</v>
+        <v>1.190865846208741</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.218546560604832</v>
+        <v>3.387702582781779</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404855</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.581864052084446</v>
+        <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.050245659965031</v>
+        <v>-2.980513305273605</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.361409363784686</v>
+        <v>1.497808732726049</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.155007368815691</v>
+        <v>1.256090027335947</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.274868473373861</v>
+        <v>3.444024495550807</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.577825024383726</v>
+        <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.012818639893897</v>
+        <v>-2.943086285202471</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.37234114411242</v>
+        <v>1.508740513053783</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.160258906844872</v>
+        <v>1.261341565365129</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.27398036849065</v>
+        <v>3.443136390667596</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.579081816714967</v>
+        <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.032930295928606</v>
+        <v>-2.963197941237179</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.365553274029777</v>
+        <v>1.50195264297114</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.171286251842292</v>
+        <v>1.272368910362548</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.281853567820342</v>
+        <v>3.451009589997288</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636289</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.739639587736177</v>
+        <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.004517032828722</v>
+        <v>-2.934784678137296</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.537476350290942</v>
+        <v>1.673875719232305</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.112310689095863</v>
+        <v>1.213393347616119</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.407026001193695</v>
+        <v>3.576182023370642</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957628</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.859752496953995</v>
+        <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.929734771803709</v>
+        <v>-2.860002417112283</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.687502163918764</v>
+        <v>1.823901532860127</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.187092950120875</v>
+        <v>1.288175608641132</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.57200826702652</v>
+        <v>3.741164289203467</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.851460472967854</v>
+        <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.903650687539901</v>
+        <v>-2.833918332848475</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.689643773638146</v>
+        <v>1.826043142579509</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.187092950120875</v>
+        <v>1.288175608641132</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.563716243040379</v>
+        <v>3.732872265217326</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896933</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.849653668551633</v>
+        <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.815772774430781</v>
+        <v>-2.746040419739355</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.722988134465574</v>
+        <v>1.859387503406937</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.303018592544226</v>
+        <v>1.404101251064483</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.631464824078169</v>
+        <v>3.800620846255116</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959861</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.867208074278425</v>
+        <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.806880313037497</v>
+        <v>-2.737147958346071</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.744099524749678</v>
+        <v>1.880498893691041</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.303018592544226</v>
+        <v>1.404101251064483</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.64901922980496</v>
+        <v>3.818175251981907</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945369</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.859063121683008</v>
+        <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.975356430007375</v>
+        <v>-2.905624075315949</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.668564125366311</v>
+        <v>1.804963494307674</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.275070756827646</v>
+        <v>1.376153415347902</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.624105575779596</v>
+        <v>3.793261597956543</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782713</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.84033281887087</v>
+        <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.529100237377935</v>
+        <v>-2.459367882686509</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.828336299605949</v>
+        <v>1.964735668547312</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.180352087158013</v>
+        <v>1.281434745678269</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.548544071165678</v>
+        <v>3.717700093342625</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563264</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.830996841367775</v>
+        <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.506379133694783</v>
+        <v>-2.436646779003357</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.828088763576115</v>
+        <v>1.964488132517478</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.180352087158013</v>
+        <v>1.281434745678269</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.539208093662583</v>
+        <v>3.70836411583953</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777677</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.989902967218944</v>
+        <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.635580946988825</v>
+        <v>-2.565848592297399</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.935314164109667</v>
+        <v>2.07171353305103</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.051150273863971</v>
+        <v>1.152232932384227</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.620593131537326</v>
+        <v>3.789749153714273</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644416</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.02698078971259</v>
+        <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.661455345462851</v>
+        <v>-2.591722990771425</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.962042227213703</v>
+        <v>2.098441596155066</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.096061882575712</v>
+        <v>1.197144541095968</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.684617919258018</v>
+        <v>3.853773941434964</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.023656145702136</v>
+        <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.654400655247677</v>
+        <v>-2.584668300556251</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.961539459289318</v>
+        <v>2.097938828230681</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.103116572790886</v>
+        <v>1.204199231311142</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.685526089376667</v>
+        <v>3.854682111553614</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633112</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.033662299346877</v>
+        <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.627449430921189</v>
+        <v>-2.557717076229763</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.982326102664654</v>
+        <v>2.118725471606017</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.117996918818605</v>
+        <v>1.219079577338861</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.70446045063804</v>
+        <v>3.873616472814987</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784112</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.217765431491837</v>
+        <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.648993658751976</v>
+        <v>-2.57926130406055</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.157811543677299</v>
+        <v>2.294210912618662</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.117996918818605</v>
+        <v>1.219079577338861</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.888563582783</v>
+        <v>4.057719604959947</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571443</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.20988212639483</v>
+        <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.671401776556849</v>
+        <v>-2.601669421865422</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.140964991458343</v>
+        <v>2.277364360399706</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.117996918818605</v>
+        <v>1.219079577338861</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.880680277685993</v>
+        <v>4.04983629986294</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155036</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.211936125944467</v>
+        <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.699626012134449</v>
+        <v>-2.629893657443023</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.131729296776941</v>
+        <v>2.268128665718304</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.135973671269913</v>
+        <v>1.23705632979017</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.893520328706416</v>
+        <v>4.062676350883362</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.268189843666315</v>
+        <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.709066938022979</v>
+        <v>-2.639334583331553</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.184206644143376</v>
+        <v>2.320606013084739</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.258400788813305</v>
+        <v>1.359483447333561</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.023230316954297</v>
+        <v>4.192386339131244</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.271080938211615</v>
+        <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.797943569191453</v>
+        <v>-2.728211214500027</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.151547086221287</v>
+        <v>2.28794645516265</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.169524157644831</v>
+        <v>1.270606816165087</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.972795432798514</v>
+        <v>4.141951454975461</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347707</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.269192751105391</v>
+        <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.874273546792359</v>
+        <v>-2.804541192100932</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.1191269080747</v>
+        <v>2.255526277016063</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.169524157644831</v>
+        <v>1.270606816165087</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.970907245692289</v>
+        <v>4.140063267869236</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887752</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.264012980708253</v>
+        <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.9679374914699</v>
+        <v>-2.898205136778474</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.076481559806546</v>
+        <v>2.212880928747909</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.07586021296729</v>
+        <v>1.176942871487546</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.909529108488627</v>
+        <v>4.078685130665574</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.262446990918405</v>
+        <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.129505916997155</v>
+        <v>-3.059773562305729</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.010288199805796</v>
+        <v>2.146687568747159</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9490772891694103</v>
+        <v>1.050159947689667</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.831893364420051</v>
+        <v>4.001049386596998</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.275520397784324</v>
+        <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.237806578867275</v>
+        <v>-3.168074224175848</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.980041341923667</v>
+        <v>2.11644071086503</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9490772891694103</v>
+        <v>1.050159947689667</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.844966771285971</v>
+        <v>4.014122793462917</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378396</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.267525594567264</v>
+        <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.255610550588019</v>
+        <v>-3.185878195896592</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.964924950018309</v>
+        <v>2.101324318959672</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8785426662642091</v>
+        <v>0.9796253247844655</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.79465119432579</v>
+        <v>3.963807216502736</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006979</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.266049635694266</v>
+        <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.283511337697492</v>
+        <v>-3.213778983006065</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.952288676301522</v>
+        <v>2.088688045242885</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8439457421212743</v>
+        <v>0.9450284006415307</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.772417080967031</v>
+        <v>3.941573103143977</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787391</v>
+        <v>3.684895778787389</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.262814079671465</v>
+        <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.406037440400385</v>
+        <v>-3.336305085708959</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.900042679197563</v>
+        <v>2.036442048138926</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7214196394183804</v>
+        <v>0.8225022979386368</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.695665863322493</v>
+        <v>3.86482188549944</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585942</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.329520039261968</v>
+        <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.636551936585974</v>
+        <v>-3.566819581894548</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.874542840313832</v>
+        <v>2.010942209255195</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4909051432327917</v>
+        <v>0.5919878017530481</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.624063125201644</v>
+        <v>3.79321914737859</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814669</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.469831758263815</v>
+        <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.985297021810418</v>
+        <v>-3.915564667118992</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.875356525225901</v>
+        <v>2.011755894167264</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.4832398478341503</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.699126071852152</v>
+        <v>3.868282094029099</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237099</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.538812027409455</v>
+        <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.139283439586558</v>
+        <v>-4.069551084895132</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.882742227261085</v>
+        <v>2.019141596202448</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.4832398478341503</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.768106340997792</v>
+        <v>3.937262363174738</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423392</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.524863229529576</v>
+        <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.088761535758892</v>
+        <v>-4.019029181067467</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.889002190912272</v>
+        <v>2.025401559853635</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.4832398478341503</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.754157543117913</v>
+        <v>3.923313565294859</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609758</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.53673371858499</v>
+        <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.341236689766617</v>
+        <v>-4.271504335075191</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.799882618364596</v>
+        <v>1.936281987305959</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.4832398478341503</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.766028032173327</v>
+        <v>3.935184054350273</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973162</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.537944253103934</v>
+        <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.634132446246029</v>
+        <v>-4.564400091554603</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.683934850291775</v>
+        <v>1.820334219233138</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.4832398478341503</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.76723856669227</v>
+        <v>3.936394588869216</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.542065995331255</v>
+        <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.820796574380837</v>
+        <v>-4.751064219689411</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.613390941265173</v>
+        <v>1.749790310206536</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.355418218489334</v>
+        <v>0.4565008770095904</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.755316926424856</v>
+        <v>3.924472948601802</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.537143848067445</v>
+        <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.966817261294799</v>
+        <v>-4.897084906603373</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.550060519235778</v>
+        <v>1.686459888177141</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.346335126695477</v>
+        <v>0.4474177852157334</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.744944924084731</v>
+        <v>3.914100946261677</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830332</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.699347904766489</v>
+        <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.058531270404384</v>
+        <v>-4.988798915712959</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.675578972290988</v>
+        <v>1.811978341232351</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.346335126695477</v>
+        <v>0.4474177852157334</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.907148980783775</v>
+        <v>4.076305002960722</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.694194542730303</v>
+        <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.090182929464353</v>
+        <v>-5.020450574772928</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.657764946630814</v>
+        <v>1.794164315572177</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3411666694510368</v>
+        <v>0.4422493279712932</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.898894544400925</v>
+        <v>4.068050566577872</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.704423960298794</v>
+        <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.172117747733236</v>
+        <v>-5.102385393041811</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.635220436891752</v>
+        <v>1.771619805833115</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3312319238639566</v>
+        <v>0.4323145823842131</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.903163114617168</v>
+        <v>4.072319136794115</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.713349598754697</v>
+        <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.274093869981644</v>
+        <v>-5.204361515290219</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.603355626448292</v>
+        <v>1.739754995389654</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.229255801615549</v>
+        <v>0.3303384601358055</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.850903079724026</v>
+        <v>4.020059101900973</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.79829678423181</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.705502485998872</v>
+        <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.164087586504422</v>
+        <v>-5.094355231812997</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.639511027083356</v>
+        <v>1.775910396024718</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2524603735328242</v>
+        <v>0.3535430320530807</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.856978710118567</v>
+        <v>4.026134732295513</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818525</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.709752496720846</v>
+        <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.021028010763496</v>
+        <v>-4.951295656072071</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.7009848681017</v>
+        <v>1.837384237043063</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2604738001228035</v>
+        <v>0.36155645864306</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.866036776794529</v>
+        <v>4.035192798971475</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.717013379603382</v>
+        <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.719581285291659</v>
+        <v>-4.649848930600234</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.828824441172971</v>
+        <v>1.965223810114334</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5619205255946408</v>
+        <v>0.6630031841148972</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.054165694960167</v>
+        <v>4.223321717137114</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679626</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.717984557356093</v>
+        <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.744171529526843</v>
+        <v>-4.674439174835418</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.819959521231608</v>
+        <v>1.956358890172971</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5619205255946408</v>
+        <v>0.6630031841148972</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.055136872712877</v>
+        <v>4.224292894889824</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.718827461735848</v>
+        <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.693133153520322</v>
+        <v>-4.623400798828897</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.841217776013972</v>
+        <v>1.977617144955335</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5619205255946408</v>
+        <v>0.6630031841148972</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.055979777092633</v>
+        <v>4.225135799269579</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.737865560609994</v>
+        <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.651993858653691</v>
+        <v>-4.582261503962267</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.87671159283477</v>
+        <v>2.013110961776133</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6030598204612716</v>
+        <v>0.704142478981528</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.099701452886757</v>
+        <v>4.268857475063704</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.554049556733928</v>
+        <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.555358946635051</v>
+        <v>-4.485626591943626</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.73154955376616</v>
+        <v>1.867948922707523</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6996947324799115</v>
+        <v>0.800777391000168</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.973866396221876</v>
+        <v>4.143022418398822</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.557551600807892</v>
+        <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.685939681165894</v>
+        <v>-4.616207326474469</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.682819304027788</v>
+        <v>1.81921867296915</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.569113997949069</v>
+        <v>0.6701966564693255</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.899019999577334</v>
+        <v>4.06817602175428</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.541978419883975</v>
+        <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.521443346974932</v>
+        <v>-4.451710992283507</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.733044656780255</v>
+        <v>1.869444025721617</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7336103321400309</v>
+        <v>0.8346929906602873</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.982144619167994</v>
+        <v>4.151300641344941</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.541166130320405</v>
+        <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.444344745433059</v>
+        <v>-4.374612390741635</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.763071807833434</v>
+        <v>1.899471176774796</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7336103321400309</v>
+        <v>0.8346929906602873</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.981332329604424</v>
+        <v>4.15048835178137</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.551034909445477</v>
+        <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.454729940322949</v>
+        <v>-4.384997585631524</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.76878650900255</v>
+        <v>1.905185877943913</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7232251372501416</v>
+        <v>0.824307795770398</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.984969991795563</v>
+        <v>4.154126013972509</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.621871915221902</v>
+        <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.473318099045174</v>
+        <v>-4.403585744353749</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.832188251290086</v>
+        <v>1.968587620231448</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7046369785279163</v>
+        <v>0.8057196370481727</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.044654102338653</v>
+        <v>4.213810124515599</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.618740926040201</v>
+        <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.47361664574121</v>
+        <v>-4.403884291049785</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.82893784342997</v>
+        <v>1.965337212371332</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7043384318318804</v>
+        <v>0.8054210903521368</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.04134398513933</v>
+        <v>4.210500007316276</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.623271820979592</v>
+        <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.372793512050782</v>
+        <v>-4.303061157359357</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.873797991845532</v>
+        <v>2.010197360786895</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.7168026473162342</v>
+        <v>0.8178853058364907</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.053353409369333</v>
+        <v>4.222509431546279</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.623401074458136</v>
+        <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.182012151298375</v>
+        <v>-4.11227979660695</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.950239789625038</v>
+        <v>2.086639158566401</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9075840080686416</v>
+        <v>1.008666666588898</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.167951479299321</v>
+        <v>4.337107501476267</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.603237920195732</v>
+        <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.075048793448953</v>
+        <v>-4.005316438757529</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.972861978502404</v>
+        <v>2.109261347443766</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9660486160284431</v>
+        <v>1.0671312745487</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.182867089812798</v>
+        <v>4.352023111989745</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.63820485680779</v>
+        <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.019718205547191</v>
+        <v>-3.949985850855767</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.029961150275167</v>
+        <v>2.166360519216529</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.021379203930205</v>
+        <v>1.122461862450462</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.251032379165914</v>
+        <v>4.420188401342861</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.631891424709228</v>
+        <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.007664078634228</v>
+        <v>-3.937931723942804</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.028469368941789</v>
+        <v>2.164868737883152</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.033433330843168</v>
+        <v>1.134515989363424</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.25195142321513</v>
+        <v>4.421107445392076</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.633772054893364</v>
+        <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.048819198202449</v>
+        <v>-3.979086843511025</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.013887951298637</v>
+        <v>2.150287320239999</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9922782112749471</v>
+        <v>1.093360869795204</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.229138981658332</v>
+        <v>4.398295003835279</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.646623080771247</v>
+        <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.980770635510919</v>
+        <v>-3.911038280819495</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.053958402253132</v>
+        <v>2.190357771194494</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.060326773966477</v>
+        <v>1.161409432486733</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.282819145151133</v>
+        <v>4.451975167328079</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013428</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.666825750944841</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.21237102868042</v>
+        <v>-4.142638673988996</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.981520915158925</v>
+        <v>2.117920284100288</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.060326773966477</v>
+        <v>1.161409432486733</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.303021815324727</v>
+        <v>4.472177837501674</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498973</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.650431987011723</v>
+        <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.262422574209639</v>
+        <v>-4.192690219518216</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.94510653301412</v>
+        <v>2.081505901955482</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.060326773966477</v>
+        <v>1.161409432486733</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.28662805139161</v>
+        <v>4.455784073568556</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800102</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.610683900605189</v>
+        <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.329953313139472</v>
+        <v>-4.367797052094661</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.878346151035653</v>
+        <v>1.97171508251837</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.060326773966477</v>
+        <v>1.161409432486733</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.246879964985076</v>
+        <v>4.416035987162022</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660854</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.617706519602129</v>
+        <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.298667292599017</v>
+        <v>-4.336511031554205</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.897883178248775</v>
+        <v>1.991252109731493</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.091612794506932</v>
+        <v>1.192695453027189</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.272674196306289</v>
+        <v>4.441830218483235</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395091</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.716877519175034</v>
+        <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.145641900485733</v>
+        <v>-4.183485639440921</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.058264334666994</v>
+        <v>2.151633266149711</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.244638186620216</v>
+        <v>1.345720845140473</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.463660431147164</v>
+        <v>4.632816453324111</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.904343744083326</v>
+        <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.173949214359003</v>
+        <v>-4.211792953314191</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.234407634025978</v>
+        <v>2.327776565508695</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.244638186620216</v>
+        <v>1.345720845140473</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.651126656055457</v>
+        <v>4.820282678232403</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.873746695437409</v>
+        <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.340542439472525</v>
+        <v>-4.378386178427713</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.137173295334652</v>
+        <v>2.230542226817369</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.078044961506694</v>
+        <v>1.17912762002695</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.520573672341426</v>
+        <v>4.689729694518372</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285649</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.877423098099127</v>
+        <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.317506646110959</v>
+        <v>-4.355350385066147</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.150064015340996</v>
+        <v>2.243432946823713</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.078044961506694</v>
+        <v>1.17912762002695</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.524250075003144</v>
+        <v>4.693406097180089</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399471</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.875041153222622</v>
+        <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.288260665655263</v>
+        <v>-4.326104404610451</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.15938046264677</v>
+        <v>2.252749394129487</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.078044961506694</v>
+        <v>1.17912762002695</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.521868130126639</v>
+        <v>4.691024152303584</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.872334392380257</v>
+        <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.395186213533114</v>
+        <v>-4.433029952488302</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.113903482653265</v>
+        <v>2.207272414135981</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9711194136288425</v>
+        <v>1.072202072149099</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.455006040557563</v>
+        <v>4.624162062734509</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701004</v>
+        <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.873763194523491</v>
+        <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.540204772040362</v>
+        <v>-4.578048510995551</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.057324861393599</v>
+        <v>2.150693792876316</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.8261008551215939</v>
+        <v>0.9271835136418505</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.369423707596448</v>
+        <v>4.538579729773394</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.973694433781244</v>
+        <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.65854653782508</v>
+        <v>-4.696390276780268</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.109919394337465</v>
+        <v>2.203288325820182</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9378695522047406</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.475766569991935</v>
+        <v>4.644922592168881</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790805</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.971480130907183</v>
+        <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.709956960145788</v>
+        <v>-4.747800699100976</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.08714092253512</v>
+        <v>2.180509854017838</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9378695522047406</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.473552267117873</v>
+        <v>4.64270828929482</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437333</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.971383258981472</v>
+        <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.78937641135354</v>
+        <v>-4.827220150308728</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.055276270126309</v>
+        <v>2.148645201609027</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9378695522047406</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.473455395192163</v>
+        <v>4.64261141736911</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298399</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.971377152539516</v>
+        <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.884839409270757</v>
+        <v>-4.922683148225945</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.017084964517466</v>
+        <v>2.110453896000183</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9378695522047406</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.473449288750206</v>
+        <v>4.642605310927153</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218001</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.969473549102126</v>
+        <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.820463498420042</v>
+        <v>-4.858307237375231</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.040931725420362</v>
+        <v>2.134300656903079</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.9011628045351991</v>
+        <v>1.002245463055456</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.510171231823246</v>
+        <v>4.679327254000192</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353537</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.975207366849853</v>
+        <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.875832660552236</v>
+        <v>-4.913676399507424</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.024517878315211</v>
+        <v>2.117886809797929</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.9011628045351991</v>
+        <v>1.002245463055456</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.515905049570972</v>
+        <v>4.685061071747919</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73682287011328</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.974745730192785</v>
+        <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.921270440383063</v>
+        <v>-4.959114179338251</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.005881129725812</v>
+        <v>2.099250061208529</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.8583178138570395</v>
+        <v>0.959400472377296</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.489736418507009</v>
+        <v>4.658892440683955</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113689</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.994620123043104</v>
+        <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.833063606235485</v>
+        <v>-4.870907345190673</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.061038256235163</v>
+        <v>2.15440718771788</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.8583178138570395</v>
+        <v>0.959400472377296</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.509610811357328</v>
+        <v>4.678766833534274</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016443</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.978320823567832</v>
+        <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.727028611030176</v>
+        <v>-4.764872349985364</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.087152954842014</v>
+        <v>2.180521886324732</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.8583178138570395</v>
+        <v>0.959400472377296</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.493311511882056</v>
+        <v>4.662467534059003</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307674</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.980751773031877</v>
+        <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.54381694789708</v>
+        <v>-4.581660686852269</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.162868569559298</v>
+        <v>2.256237501042015</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.041529476990135</v>
+        <v>1.142612135510391</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.605669459225958</v>
+        <v>4.774825481402905</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.946542958879767</v>
+        <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.472095500883229</v>
+        <v>-4.509939239838418</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.157348334212728</v>
+        <v>2.250717265695445</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.113250924003985</v>
+        <v>1.214333582524242</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.614493513282158</v>
+        <v>4.783649535459104</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394116</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.893458704800938</v>
+        <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.449722475275523</v>
+        <v>-4.487566214230712</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.113213290376982</v>
+        <v>2.206582221859699</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.124506675116887</v>
+        <v>1.225589333637143</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.56816270987107</v>
+        <v>4.737318732048017</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456732</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.078656909686294</v>
+        <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.482738771186268</v>
+        <v>-4.520582510141456</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.285204976898039</v>
+        <v>2.378573908380757</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.055069298450135</v>
+        <v>1.156151956970392</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.711698488756375</v>
+        <v>4.880854510933322</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71376253688368</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.070578135514543</v>
+        <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.471211135536659</v>
+        <v>-4.509054874491848</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.281737256986132</v>
+        <v>2.375106188468849</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.114069956651498</v>
+        <v>1.215152615171754</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.739020109505442</v>
+        <v>4.908176131682389</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236299</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.074246248036332</v>
+        <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.568552636879028</v>
+        <v>-4.606396375834216</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.246468768970973</v>
+        <v>2.33983770045369</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.069649774486009</v>
+        <v>1.170732433006266</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.716036112727937</v>
+        <v>4.885192134904884</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427686</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.07549733022917</v>
+        <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.654408666218995</v>
+        <v>-4.692252405174183</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.213377439427824</v>
+        <v>2.306746370910542</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.027273705259874</v>
+        <v>1.128356363780131</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.691861553385094</v>
+        <v>4.861017575562041</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610384</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.057916532049672</v>
+        <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.663245463635114</v>
+        <v>-4.701089202590302</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.192261922281879</v>
+        <v>2.285630853764596</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.019831532618523</v>
+        <v>1.12091419113878</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.669815451620786</v>
+        <v>4.838971473797733</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.068081043094721</v>
+        <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.754628026200573</v>
+        <v>-4.792471765155761</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.165873408300745</v>
+        <v>2.259242339783462</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9284489700530651</v>
+        <v>1.029531628573322</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.62515042512656</v>
+        <v>4.794306447303507</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889193</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.170209300918989</v>
+        <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.742921308213567</v>
+        <v>-4.780765047168755</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.272684353319815</v>
+        <v>2.366053284802533</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.9401556880400715</v>
+        <v>1.041238346560328</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.734302713743032</v>
+        <v>4.903458735919979</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409569</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.173241639650394</v>
+        <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.643257804129904</v>
+        <v>-4.681101543085092</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.315582093684685</v>
+        <v>2.408951025167402</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.003342771243758</v>
+        <v>1.104425429764014</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.775247302396649</v>
+        <v>4.944403324573596</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452574</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.386146472928452</v>
+        <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.653573902296256</v>
+        <v>-4.691417641251444</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.524360487696202</v>
+        <v>2.61772941917892</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.003342771243758</v>
+        <v>1.104425429764014</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.988152135674707</v>
+        <v>5.157308157851654</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762289</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.385325139840542</v>
+        <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.653479934278884</v>
+        <v>-4.691323673234072</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.523576741815241</v>
+        <v>2.616945673297958</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.003712632591076</v>
+        <v>1.104795291111332</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.987552719395188</v>
+        <v>5.156708741572134</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.63321346798802</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.379557125784896</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.660698758478728</v>
+        <v>-4.698542497433916</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.514921198079657</v>
+        <v>2.608290129562374</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.003712632591076</v>
+        <v>1.104795291111332</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.981784705339542</v>
+        <v>5.150940727516488</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740926</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.379557125784896</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.659750335360689</v>
+        <v>-4.697594074315877</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.515300567326872</v>
+        <v>2.60866949880959</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.003712632591076</v>
+        <v>1.104795291111332</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.981784705339542</v>
+        <v>5.150940727516488</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.673485397508232</v>
+        <v>3.673485397508226</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.392284733765988</v>
+        <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.816818793616314</v>
+        <v>-4.988339935249082</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.465200792005715</v>
+        <v>2.505098762417401</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.003712632591076</v>
+        <v>1.104795291111332</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.994512313320634</v>
+        <v>5.163668335497579</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.806741384178846</v>
+        <v>3.804512271758332</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.525388456506701</v>
+        <v>4.702887740237899</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.816818793616314</v>
+        <v>-4.988339935249082</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.465200792005715</v>
+        <v>2.505098762417401</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.003712632591076</v>
+        <v>1.104795291111332</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.518452253493069</v>
+        <v>4.695951537224267</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240910.xlsx
+++ b/tame_output/ON/bt/strategyON_20240910.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>60.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>158.7%</t>
+          <t>164.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-47.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.4%</t>
+          <t>-649.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-125.7%</t>
+          <t>-121.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-353.1%</t>
+          <t>-318.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-113.5%</t>
+          <t>-141.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,42 +1456,42 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
     </row>
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.382578673907894</v>
+        <v>-8.499461964536028</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1932135456438004</v>
+        <v>-0.2399668618950543</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.136943343044216</v>
+        <v>-1.253826633672349</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.478008342406575</v>
+        <v>2.407878368029695</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.557703091294437</v>
+        <v>-8.674586381922571</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2487080918509013</v>
+        <v>-0.2954614081021552</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.312067760430759</v>
+        <v>-1.428951051058893</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.387488912722166</v>
+        <v>2.317358938345286</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.792155185308927</v>
+        <v>-8.909038475937061</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3497080943582929</v>
+        <v>-0.3964614106095468</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.312067760430759</v>
+        <v>-1.428951051058893</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.38026974782057</v>
+        <v>2.310139773443689</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.896529916335373</v>
+        <v>-9.013413206963508</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3981301775428476</v>
+        <v>-0.4448834937941015</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.416442491457205</v>
+        <v>-1.533325782085339</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.310972718430726</v>
+        <v>2.240842744053846</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.059043382033957</v>
+        <v>-9.175926672662092</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4620197739837253</v>
+        <v>-0.5087730902349792</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.514075921875892</v>
+        <v>-1.630959212504025</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.25350845001807</v>
+        <v>2.18337847564119</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.185080175402247</v>
+        <v>-9.301963466030381</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5097407627019264</v>
+        <v>-0.5564940789531803</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.48882429906615</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.27135315233303</v>
+        <v>2.20122317795615</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.128008403506316</v>
+        <v>-9.24489169413445</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.482921718257153</v>
+        <v>-0.5296750345084069</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.48882429906615</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.275343488019431</v>
+        <v>2.205213513642551</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.269680245230436</v>
+        <v>-9.386563535858571</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5410656818455428</v>
+        <v>-0.5878189980967967</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.48882429906615</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.273868261120689</v>
+        <v>2.20373828674381</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.220089400805602</v>
+        <v>-9.336972691433736</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.506175933910737</v>
+        <v>-0.5529292501619909</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.439233454641315</v>
+        <v>-1.556116745269449</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.318676177940462</v>
+        <v>2.248546203563582</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.071171066333745</v>
+        <v>-9.18805435696188</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4596597337686772</v>
+        <v>-0.5064130500199311</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.407983863906142</v>
+        <v>-1.524867154534276</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.324374798734883</v>
+        <v>2.254244824358003</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.845325913614335</v>
+        <v>-8.96220920424247</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3597425996447048</v>
+        <v>-0.4064959158959582</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.366057188318979</v>
+        <v>-1.482940478947112</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.35910987712339</v>
+        <v>2.28897990274651</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.720747257276743</v>
+        <v>-8.837630547904878</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3087719925536088</v>
+        <v>-0.3555253088048627</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.366057188318979</v>
+        <v>-1.482940478947112</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.360249021679449</v>
+        <v>2.290119047302569</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.695710575708233</v>
+        <v>-8.812593866336368</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2961235457640972</v>
+        <v>-0.3428768620153511</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.340728100768243</v>
+        <v>-1.457611391396377</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.378080248371998</v>
+        <v>2.307950273995118</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.623577400420352</v>
+        <v>-8.740460691048487</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2615365714103084</v>
+        <v>-0.3082898876615623</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.340728100768243</v>
+        <v>-1.457611391396377</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.383813952610634</v>
+        <v>2.313683978233754</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.552211007810705</v>
+        <v>-8.669094298438839</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2427272767603146</v>
+        <v>-0.2894805930115685</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.269361708158595</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.416896525782558</v>
+        <v>2.346766551405678</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.45875197382548</v>
+        <v>-8.575635264453615</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2152271444791323</v>
+        <v>-0.2619804607303862</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.269361708158595</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.40701304446965</v>
+        <v>2.33688307009277</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.448098792272049</v>
+        <v>-8.564982082900183</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2128004323571333</v>
+        <v>-0.2595537486083872</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.269361708158595</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.405178483970277</v>
+        <v>2.335048509593396</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.350191753595558</v>
+        <v>-8.467075044223693</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1739379318599981</v>
+        <v>-0.220691248111252</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.201375958298039</v>
+        <v>-1.318259248926172</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.44566961891315</v>
+        <v>2.37553964453627</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.3262382126196</v>
+        <v>-8.443121503247735</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1636880093241211</v>
+        <v>-0.210441325575375</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.177422417322081</v>
+        <v>-1.294305707950215</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.460710249644218</v>
+        <v>2.390580275267338</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.062178274296803</v>
+        <v>-8.179061564924938</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.07132435015675487</v>
+        <v>-0.1180776664080083</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9133624789992849</v>
+        <v>-1.030245769627419</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.605885896476143</v>
+        <v>2.535755922099263</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.355098650791965</v>
+        <v>-7.4719819414201</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2087204655848796</v>
+        <v>0.1619671493336261</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9133624789992849</v>
+        <v>-1.030245769627419</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.603098862815842</v>
+        <v>2.532968888438962</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.314914352425775</v>
+        <v>-7.431797643053909</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2251378088191971</v>
+        <v>0.1783844925679436</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.8731781806330942</v>
+        <v>-0.9900614712612278</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.627553065723398</v>
+        <v>2.557423091346518</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.151514481486412</v>
+        <v>-7.268397772114547</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.289864578415699</v>
+        <v>0.2431112621644456</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7097783096937317</v>
+        <v>-0.8266616003218653</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.724959809507773</v>
+        <v>2.654829835130893</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.918033259256814</v>
+        <v>-7.034916549884948</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.391181496145391</v>
+        <v>0.3444281798941371</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.4762970874641331</v>
+        <v>-0.5931803780922668</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.872972971683384</v>
+        <v>2.802842997306504</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.768366868249299</v>
+        <v>-6.885250158877433</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4481558422354377</v>
+        <v>0.4014025259841842</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.3833935962215972</v>
+        <v>-0.5002768868497308</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.925822856115947</v>
+        <v>2.855692881739067</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.651892026726289</v>
+        <v>-6.752974685246547</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3960065648517963</v>
+        <v>0.3555735014436934</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.2669187546985879</v>
+        <v>-0.3680014132188442</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.896968547036907</v>
+        <v>2.836318951924753</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.496153694166547</v>
+        <v>-6.597236352686805</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4611169585633297</v>
+        <v>0.4206838951552268</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1111804221388464</v>
+        <v>-0.2122630806591026</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.993226607260389</v>
+        <v>2.932577012148235</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.411189027437228</v>
+        <v>-6.512271685957485</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5080091664787161</v>
+        <v>0.4675761030706136</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.02621575540952681</v>
+        <v>-0.127298413929783</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.057111748521639</v>
+        <v>2.996462153409485</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.516779017210332</v>
+        <v>-6.617861675730589</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3377972409702559</v>
+        <v>0.2973641775621529</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1318057451826312</v>
+        <v>-0.2328884037028874</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.865781825058558</v>
+        <v>2.805132229946404</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.448544432584905</v>
+        <v>-6.549627091105162</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4136354166975131</v>
+        <v>0.3732023532894102</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1133904223100952</v>
+        <v>-0.2144730808303514</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.925375360659165</v>
+        <v>2.864725765547012</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.300604391177306</v>
+        <v>-6.401687049697562</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3561906246221458</v>
+        <v>0.3157575612140429</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.09306950640153761</v>
+        <v>-0.1941521649217938</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.820947101565893</v>
+        <v>2.760297506453739</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.247634868923317</v>
+        <v>-6.348717527443574</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3686644472702629</v>
+        <v>0.3282313838621604</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.04009998414754873</v>
+        <v>-0.1411826426678049</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.844014828664808</v>
+        <v>2.783365233552654</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.081846672963026</v>
+        <v>-6.182929331483283</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4280191135592863</v>
+        <v>0.3875860501511834</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.04009998414754873</v>
+        <v>-0.1411826426678049</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.837054216569715</v>
+        <v>2.776404621457561</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.048483466484257</v>
+        <v>-6.149566125004514</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4558267505319367</v>
+        <v>0.4153936871238342</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.04009998414754873</v>
+        <v>-0.1411826426678049</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.851516570950858</v>
+        <v>2.790866975838704</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.940224329361736</v>
+        <v>-6.041306987881993</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4936625258401404</v>
+        <v>0.4532294624320379</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.04009998414754873</v>
+        <v>-0.1411826426678049</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.846048691410053</v>
+        <v>2.785399096297899</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.816933194544605</v>
+        <v>-5.918015853064862</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5404770737775699</v>
+        <v>0.500044010369467</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.08319115066958177</v>
+        <v>-0.01789150785067445</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.917521466310908</v>
+        <v>2.856871871198754</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.764236327413314</v>
+        <v>-5.865318985933571</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5692567988674115</v>
+        <v>0.5288237354593086</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.135888017800873</v>
+        <v>0.03480535928061673</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.956840564827008</v>
+        <v>2.896190969714854</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.520470885429869</v>
+        <v>-5.621553543950126</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.66254368400784</v>
+        <v>0.6221106205997371</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.135888017800873</v>
+        <v>0.03480535928061673</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.952621273174059</v>
+        <v>2.891971678061905</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.430695213053397</v>
+        <v>-5.531777871573654</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7005782668784448</v>
+        <v>0.6601452034703419</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.197487462715183</v>
+        <v>0.09640480419492675</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.991705254042661</v>
+        <v>2.931055658930507</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.180844819104323</v>
+        <v>-5.281927477624579</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7932604994417769</v>
+        <v>0.752827436033674</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.197487462715183</v>
+        <v>0.09640480419492675</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.984447329026363</v>
+        <v>2.923797733914209</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.004952726636891</v>
+        <v>-5.106035385157147</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8672164599493983</v>
+        <v>0.8267833965412956</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.197487462715183</v>
+        <v>0.09640480419492675</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.988046452547012</v>
+        <v>2.927396857434858</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.833506263614427</v>
+        <v>-4.934588922134684</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9491225512129373</v>
+        <v>0.9086894878048346</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3689339257376461</v>
+        <v>0.2678512672173899</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.104241836415043</v>
+        <v>3.04359224130289</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.753483976505306</v>
+        <v>-4.854566635025563</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9801519436728827</v>
+        <v>0.93971888026478</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.4489562128467671</v>
+        <v>0.3478735543265108</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.151275686296813</v>
+        <v>3.090626091184659</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.689848234271372</v>
+        <v>-4.790930892791629</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.010301041620774</v>
+        <v>0.9698679782126711</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.5125919550807017</v>
+        <v>0.4115092965604454</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.194151932691491</v>
+        <v>3.133502337579337</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.596150916054976</v>
+        <v>-4.697233574575233</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.028974227691128</v>
+        <v>0.9885411642830246</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.5125919550807017</v>
+        <v>0.4115092965604454</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.175346191475287</v>
+        <v>3.114696596363133</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.606653539120265</v>
+        <v>-4.707736197640522</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.026516255089889</v>
+        <v>0.9860831916817865</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.5020893320154127</v>
+        <v>0.4010066734951565</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.170787694260991</v>
+        <v>3.110138099148837</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.494167278451391</v>
+        <v>-4.595249936971648</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.075440073192259</v>
+        <v>1.035007009784157</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.5020893320154127</v>
+        <v>0.4010066734951565</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.174717008095811</v>
+        <v>3.114067412983657</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.476453591573526</v>
+        <v>-4.577536250093782</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.083204131860745</v>
+        <v>1.042771068452643</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.5052706609123295</v>
+        <v>0.4041880023920733</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.177304389351301</v>
+        <v>3.116654794239147</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.352979320260507</v>
+        <v>-4.454061978780764</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.129591911605946</v>
+        <v>1.089158848197843</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.5052706609123295</v>
+        <v>0.4041880023920733</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.174302460571294</v>
+        <v>3.113652865459141</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.132958522223497</v>
+        <v>-4.234041180743754</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.219179267831365</v>
+        <v>1.178746204423262</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6464905059803098</v>
+        <v>0.5454078474600536</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.260613404622696</v>
+        <v>3.199963809510543</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.000090833160218</v>
+        <v>-4.101173491680476</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.288220526258499</v>
+        <v>1.247787462850396</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6464905059803098</v>
+        <v>0.5454078474600536</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.27650758742452</v>
+        <v>3.215857992312366</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.879917749795719</v>
+        <v>-3.981000408315977</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.337435604044601</v>
+        <v>1.297002540636498</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7666635893448087</v>
+        <v>0.6655809308245525</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.349757281883521</v>
+        <v>3.289107686771367</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.744664388465742</v>
+        <v>-3.845747046986</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.401625051138031</v>
+        <v>1.361191987729928</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.9019169506747858</v>
+        <v>0.8008342921545296</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.440997401242948</v>
+        <v>3.380347806130794</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.804539215823434</v>
+        <v>-3.905621874343693</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.36371261159638</v>
+        <v>1.323279548188277</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8420421233170937</v>
+        <v>0.7409594647968375</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.391109996229758</v>
+        <v>3.330460401117604</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.684718984912597</v>
+        <v>-3.785801643432855</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.426929873194924</v>
+        <v>1.386496809786821</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8420421233170937</v>
+        <v>0.7409594647968375</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.406399165463966</v>
+        <v>3.345749570351813</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.687188691374403</v>
+        <v>-3.788271349894661</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.333586189932643</v>
+        <v>1.29315312652454</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8395724168552876</v>
+        <v>0.7384897583350314</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.312561540909324</v>
+        <v>3.251911945797171</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.755558877698413</v>
+        <v>-3.856641536218671</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.22549997688834</v>
+        <v>1.185066913480237</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8488481158915026</v>
+        <v>0.7477654573712463</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.237388821816355</v>
+        <v>3.176739226704201</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.867431157324563</v>
+        <v>-3.968513815844822</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.171187773669771</v>
+        <v>1.130754710261668</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8488481158915026</v>
+        <v>0.7477654573712463</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.227825530448246</v>
+        <v>3.167175935336092</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.922951233217153</v>
+        <v>-4.024033891737411</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.286010580004938</v>
+        <v>1.245577516596835</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8488481158915026</v>
+        <v>0.7477654573712463</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.364856367140448</v>
+        <v>3.304206772028295</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.747476973424684</v>
+        <v>-3.848559631944942</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.360767515913713</v>
+        <v>1.32033445250561</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8488481158915026</v>
+        <v>0.7477654573712463</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.369423599132236</v>
+        <v>3.308774004020083</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.73955259883977</v>
+        <v>-3.840635257360028</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.339679294508886</v>
+        <v>1.299246231100783</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8488481158915026</v>
+        <v>0.7477654573712463</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.345165627893443</v>
+        <v>3.28451603278129</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.733274396269921</v>
+        <v>-3.834357054790179</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.270728888938276</v>
+        <v>1.230295825530172</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8551263184613516</v>
+        <v>0.7540436599410953</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.277470862836803</v>
+        <v>3.216821267724649</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.673421777066197</v>
+        <v>-3.774504435586456</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.304842323051897</v>
+        <v>1.264409259643794</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8551263184613516</v>
+        <v>0.7540436599410953</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.287643249268935</v>
+        <v>3.226993654156781</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.58717831403982</v>
+        <v>-3.688260972560078</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.334285978836308</v>
+        <v>1.293852915428205</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8551263184613516</v>
+        <v>0.7540436599410953</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.282589519842795</v>
+        <v>3.221939924730641</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.6324851334388</v>
+        <v>-3.733567791959058</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.307939026521242</v>
+        <v>1.267505963113139</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8143161554521208</v>
+        <v>0.7132334969318646</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.249879197481782</v>
+        <v>3.189229602369628</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.661518238141102</v>
+        <v>-3.684747979054816</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.296877657673423</v>
+        <v>1.287585761307938</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8143161554521208</v>
+        <v>0.7132334969318646</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.250431070514884</v>
+        <v>3.18978147540273</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.568707756690242</v>
+        <v>-3.591937497603956</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.263274542145132</v>
+        <v>1.253982645779647</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.9071266369029801</v>
+        <v>0.8060439783827239</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.235390051276765</v>
+        <v>3.174740456164611</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.61309722601967</v>
+        <v>-3.636326966933384</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.247392230337962</v>
+        <v>1.238100333972477</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8627371675735525</v>
+        <v>0.7616545090532962</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.210629845603709</v>
+        <v>3.149980250491556</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.729638831125013</v>
+        <v>-3.752868572038727</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.195851296807548</v>
+        <v>1.186559400442063</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7461955624682097</v>
+        <v>0.6451129039479535</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.135780591052227</v>
+        <v>3.075130995940073</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.769562925707584</v>
+        <v>-3.792792666621299</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.185372954805187</v>
+        <v>1.176081058439701</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7461955624682097</v>
+        <v>0.6451129039479535</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.141271886882894</v>
+        <v>3.08062229177074</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.797343323608938</v>
+        <v>-3.820573064522652</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.185757997413184</v>
+        <v>1.176466101047699</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7184151645668566</v>
+        <v>0.6173325060466004</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.136100849910621</v>
+        <v>3.075451254798467</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.915723996339076</v>
+        <v>-3.938953737252791</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9767614483217821</v>
+        <v>0.9674695519562966</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6511973124158804</v>
+        <v>0.5501146538956242</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.934125858620689</v>
+        <v>2.873476263508535</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.024338074782408</v>
+        <v>-4.047567815696121</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.053465477663655</v>
+        <v>1.04417358129817</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6511973124158804</v>
+        <v>0.5501146538956242</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.054275519339894</v>
+        <v>2.99362592422774</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.988929036534265</v>
+        <v>-4.012158777447978</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.082142119065235</v>
+        <v>1.07285022269975</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6511973124158804</v>
+        <v>0.5501146538956242</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.068788545442217</v>
+        <v>3.008138950330063</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.950545373976114</v>
+        <v>-3.973775114889827</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.094915025430864</v>
+        <v>1.085623129065379</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6895809749740316</v>
+        <v>0.5884983164537754</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.089238184319476</v>
+        <v>3.028588589207323</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.773429043940948</v>
+        <v>-3.796658784854661</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.162490586290233</v>
+        <v>1.153198689924747</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6895809749740316</v>
+        <v>0.5884983164537754</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.085967213164778</v>
+        <v>3.025317618052625</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.818521288774494</v>
+        <v>-3.841751029688207</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.145137080118728</v>
+        <v>1.135845183753242</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6276849318046418</v>
+        <v>0.5266022732843856</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.049512979025058</v>
+        <v>2.988863383912904</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.639145867535726</v>
+        <v>-3.662375608449439</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.210674223920649</v>
+        <v>1.201382327555164</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7844616899753605</v>
+        <v>0.6833790314551043</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.137366009233904</v>
+        <v>3.07671641412175</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.684160081056332</v>
+        <v>-3.707389821970045</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.173475993843996</v>
+        <v>1.164184097478511</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7541127946607559</v>
+        <v>0.6530301361404997</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.09996412737673</v>
+        <v>3.039314532264576</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.951164591328768</v>
+        <v>-3.974394332242481</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.072365752073968</v>
+        <v>1.063073855708483</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5597497566178073</v>
+        <v>0.4586670980975511</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.989037866889907</v>
+        <v>2.928388271777753</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.05236237276594</v>
+        <v>-4.075592113679654</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.0310905613956</v>
+        <v>1.021798665030115</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4913409430724882</v>
+        <v>0.3902582845522319</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.947196500659217</v>
+        <v>2.886546905547063</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.045851406151628</v>
+        <v>-4.069081147065341</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.031294909595642</v>
+        <v>1.022003013230157</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4913409430724882</v>
+        <v>0.3902582845522319</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.944796462213533</v>
+        <v>2.88414686710138</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.02681327844433</v>
+        <v>-4.050043019358044</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.035434879886806</v>
+        <v>1.02614298352132</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4331573317412937</v>
+        <v>0.3320746732210373</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.906411014623062</v>
+        <v>2.845761419510908</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.079329080719151</v>
+        <v>-4.102558821632864</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.133722960611068</v>
+        <v>1.124431064245583</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4331573317412937</v>
+        <v>0.3320746732210373</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.025705416257252</v>
+        <v>2.965055821145098</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.093195842053069</v>
+        <v>-4.116425582966782</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.129009585063634</v>
+        <v>1.119717688698149</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3952994150074707</v>
+        <v>0.2942167564872144</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.003823995203092</v>
+        <v>2.943174400090938</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.052712850130724</v>
+        <v>-4.075942591044437</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.151211312229498</v>
+        <v>1.141919415864013</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3952994150074707</v>
+        <v>0.2942167564872144</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.009832525600018</v>
+        <v>2.949182930487864</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.904969879895722</v>
+        <v>-3.928199620809435</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.108258721600699</v>
+        <v>1.098966825235213</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5631067722423539</v>
+        <v>0.4620241137220976</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.008467161218147</v>
+        <v>2.947817566105993</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.98879110117042</v>
+        <v>-4.012020842084133</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.0775238546223</v>
+        <v>1.068231958256815</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5631067722423539</v>
+        <v>0.4620241137220976</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.011260782749628</v>
+        <v>2.950611187637474</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.982638395117635</v>
+        <v>-4.005868136031348</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.080647285435073</v>
+        <v>1.071355389069587</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5692594782951382</v>
+        <v>0.4681768197748818</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.015614754772957</v>
+        <v>2.954965159660803</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.999447693268137</v>
+        <v>-4.02267743418185</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.073004042914982</v>
+        <v>1.063712146549497</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5524501801446366</v>
+        <v>0.4513675216243802</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.004609652622766</v>
+        <v>2.943960057510613</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.937149694492015</v>
+        <v>-3.960379435405728</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.164258796222252</v>
+        <v>1.154966899856766</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5977444444190787</v>
+        <v>0.4966617858988223</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.098121764984253</v>
+        <v>3.037472169872099</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.735359496826857</v>
+        <v>-3.758589237740571</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.047266877002442</v>
+        <v>1.037974980636957</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7957626365882331</v>
+        <v>0.6946799780679767</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.019224681999872</v>
+        <v>2.958575086887719</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.786246209513052</v>
+        <v>-3.809475950426765</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.097202424250139</v>
+        <v>1.087910527884654</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7448759239020386</v>
+        <v>0.6437932653817822</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.058982886710331</v>
+        <v>2.998333291598177</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.699635466863244</v>
+        <v>-3.722865207776958</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.146474457426106</v>
+        <v>1.137182561060621</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8235016551071969</v>
+        <v>0.7224189965869404</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.120786061549469</v>
+        <v>3.060136466437315</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.759844764868529</v>
+        <v>-3.783074505782242</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.120926719048664</v>
+        <v>1.111634822683178</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7632923571019123</v>
+        <v>0.6622096985816559</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.08319646357097</v>
+        <v>3.022546868458817</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.710658116184177</v>
+        <v>-3.733887857097891</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.139092996562333</v>
+        <v>1.129801100196848</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7632923571019123</v>
+        <v>0.6622096985816559</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.081688081610899</v>
+        <v>3.021038486498745</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.666284984545609</v>
+        <v>-3.689514725459322</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.156705116653197</v>
+        <v>1.147413220287711</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8076654887404809</v>
+        <v>0.7065828302202245</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.108174828029476</v>
+        <v>3.047525232917323</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.688765335404494</v>
+        <v>-3.711995076318207</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.142106770448233</v>
+        <v>1.132814874082748</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8076654887404809</v>
+        <v>0.7065828302202245</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.102568622168067</v>
+        <v>3.041919027055913</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.641109604843438</v>
+        <v>-3.664339345757152</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.16755081970046</v>
+        <v>1.158258923334975</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8553212193015366</v>
+        <v>0.7542385607812802</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.137543817532505</v>
+        <v>3.076894222420351</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.540591446344683</v>
+        <v>-3.563821187258397</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.212650456474687</v>
+        <v>1.203358560109201</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9558393778002912</v>
+        <v>0.8547567192800347</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.202747086006482</v>
+        <v>3.142097490894328</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.52468611691233</v>
+        <v>-3.547915857826045</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.2057672607235</v>
+        <v>1.196475364358015</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8767267170910522</v>
+        <v>0.7756440585707958</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.142034162056811</v>
+        <v>3.081384566944657</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.479847715303932</v>
+        <v>-3.503077456217647</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.227800323977488</v>
+        <v>1.218508427612002</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8812701500359217</v>
+        <v>0.7801874915156652</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.148857924434362</v>
+        <v>3.088208329322208</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.499346171545941</v>
+        <v>-3.522575912459655</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.224161881111763</v>
+        <v>1.214869984746277</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8331855087560174</v>
+        <v>0.7321028502357609</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.124168079297497</v>
+        <v>3.063518484185343</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.45514333446004</v>
+        <v>-3.478373075373754</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.24772261847396</v>
+        <v>1.238430722108474</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8773883458419178</v>
+        <v>0.7763056873216614</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.156569384076874</v>
+        <v>3.095919788964721</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.462703000297087</v>
+        <v>-3.485932741210801</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.243108752608389</v>
+        <v>1.233816856242903</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9321917498517371</v>
+        <v>0.8311090913314807</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.187861426952014</v>
+        <v>3.12721183183986</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.304411582757815</v>
+        <v>-3.327641323671529</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.357673084807137</v>
+        <v>1.348381188441652</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9321917498517371</v>
+        <v>0.8311090913314807</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.239109192135053</v>
+        <v>3.178459597022899</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.096769579123339</v>
+        <v>-3.119999320037053</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.439170590855181</v>
+        <v>1.429878694489695</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.139833753486213</v>
+        <v>1.038751094965957</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.362135098909992</v>
+        <v>3.301485503797838</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.045737486400811</v>
+        <v>-3.068967227314525</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.454531656182462</v>
+        <v>1.445239759816977</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.190865846208741</v>
+        <v>1.089783187688485</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.387702582781779</v>
+        <v>3.327052987669625</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.980513305273605</v>
+        <v>-3.003743046187319</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.497808732726049</v>
+        <v>1.488516836360564</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.256090027335947</v>
+        <v>1.155007368815691</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.444024495550807</v>
+        <v>3.383374900438653</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.943086285202471</v>
+        <v>-2.966316026116185</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.508740513053783</v>
+        <v>1.499448616688298</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.261341565365129</v>
+        <v>1.160258906844872</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.443136390667596</v>
+        <v>3.382486795555443</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.963197941237179</v>
+        <v>-2.986427682150893</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.50195264297114</v>
+        <v>1.492660746605655</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.272368910362548</v>
+        <v>1.171286251842292</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.451009589997288</v>
+        <v>3.390359994885134</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.934784678137296</v>
+        <v>-2.95801441905101</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.673875719232305</v>
+        <v>1.664583822866819</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.213393347616119</v>
+        <v>1.112310689095863</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.576182023370642</v>
+        <v>3.515532428258488</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.860002417112283</v>
+        <v>-2.883232158025997</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.823901532860127</v>
+        <v>1.814609636494641</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.288175608641132</v>
+        <v>1.187092950120875</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.741164289203467</v>
+        <v>3.680514694091313</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.833918332848475</v>
+        <v>-2.857148073762189</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.826043142579509</v>
+        <v>1.816751246214023</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.288175608641132</v>
+        <v>1.187092950120875</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.732872265217326</v>
+        <v>3.672222670105172</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.746040419739355</v>
+        <v>-2.769270160653069</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.859387503406937</v>
+        <v>1.850095607041451</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.404101251064483</v>
+        <v>1.303018592544226</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.800620846255116</v>
+        <v>3.739971251142962</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.737147958346071</v>
+        <v>-2.760377699259785</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.880498893691041</v>
+        <v>1.871206997325556</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.404101251064483</v>
+        <v>1.303018592544226</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.818175251981907</v>
+        <v>3.757525656869753</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.905624075315949</v>
+        <v>-2.928853816229663</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.804963494307674</v>
+        <v>1.795671597942189</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.376153415347902</v>
+        <v>1.275070756827646</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.793261597956543</v>
+        <v>3.732612002844389</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.459367882686509</v>
+        <v>-2.482597623600223</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.964735668547312</v>
+        <v>1.955443772181826</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.281434745678269</v>
+        <v>1.180352087158013</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.717700093342625</v>
+        <v>3.657050498230471</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.436646779003357</v>
+        <v>-2.459876519917071</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.964488132517478</v>
+        <v>1.955196236151992</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.281434745678269</v>
+        <v>1.180352087158013</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.70836411583953</v>
+        <v>3.647714520727376</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.565848592297399</v>
+        <v>-2.589078333211113</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.07171353305103</v>
+        <v>2.062421636685544</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.152232932384227</v>
+        <v>1.051150273863971</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.789749153714273</v>
+        <v>3.729099558602119</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.591722990771425</v>
+        <v>-2.614952731685139</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.098441596155066</v>
+        <v>2.08914969978958</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.197144541095968</v>
+        <v>1.096061882575712</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.853773941434964</v>
+        <v>3.79312434632281</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.584668300556251</v>
+        <v>-2.607898041469965</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.097938828230681</v>
+        <v>2.088646931865195</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.204199231311142</v>
+        <v>1.103116572790886</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.854682111553614</v>
+        <v>3.79403251644146</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.557717076229763</v>
+        <v>-2.580946817143477</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.118725471606017</v>
+        <v>2.109433575240532</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.219079577338861</v>
+        <v>1.117996918818605</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.873616472814987</v>
+        <v>3.812966877702833</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.57926130406055</v>
+        <v>-2.602491044974264</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.294210912618662</v>
+        <v>2.284919016253177</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.219079577338861</v>
+        <v>1.117996918818605</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.057719604959947</v>
+        <v>3.997070009847793</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.601669421865422</v>
+        <v>-2.624899162779136</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.277364360399706</v>
+        <v>2.268072464034221</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.219079577338861</v>
+        <v>1.117996918818605</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.04983629986294</v>
+        <v>3.989186704750786</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.629893657443023</v>
+        <v>-2.653123398356737</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.268128665718304</v>
+        <v>2.258836769352818</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.23705632979017</v>
+        <v>1.135973671269913</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.062676350883362</v>
+        <v>4.002026755771208</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.639334583331553</v>
+        <v>-2.662564324245267</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.320606013084739</v>
+        <v>2.311314116719253</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.359483447333561</v>
+        <v>1.258400788813305</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.192386339131244</v>
+        <v>4.13173674401909</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.728211214500027</v>
+        <v>-2.751440955413741</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.28794645516265</v>
+        <v>2.278654558797164</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.270606816165087</v>
+        <v>1.169524157644831</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.141951454975461</v>
+        <v>4.081301859863307</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.804541192100932</v>
+        <v>-2.827770933014647</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.255526277016063</v>
+        <v>2.246234380650577</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.270606816165087</v>
+        <v>1.169524157644831</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.140063267869236</v>
+        <v>4.079413672757082</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.898205136778474</v>
+        <v>-2.921434877692188</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.212880928747909</v>
+        <v>2.203589032382423</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.176942871487546</v>
+        <v>1.07586021296729</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.078685130665574</v>
+        <v>4.01803553555342</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.059773562305729</v>
+        <v>-3.083003303219443</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.146687568747159</v>
+        <v>2.137395672381674</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.050159947689667</v>
+        <v>0.9490772891694103</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.001049386596998</v>
+        <v>3.940399791484844</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.168074224175848</v>
+        <v>-3.191303965089562</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.11644071086503</v>
+        <v>2.107148814499544</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.050159947689667</v>
+        <v>0.9490772891694103</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.014122793462917</v>
+        <v>3.953473198350763</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.185878195896592</v>
+        <v>-3.209107936810307</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.101324318959672</v>
+        <v>2.092032422594187</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9796253247844655</v>
+        <v>0.8785426662642091</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.963807216502736</v>
+        <v>3.903157621390582</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.213778983006065</v>
+        <v>-3.23700872391978</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.088688045242885</v>
+        <v>2.079396148877399</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9450284006415307</v>
+        <v>0.8439457421212743</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.941573103143977</v>
+        <v>3.880923508031823</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.336305085708959</v>
+        <v>-3.359534826622673</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.036442048138926</v>
+        <v>2.027150151773441</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8225022979386368</v>
+        <v>0.7214196394183804</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.86482188549944</v>
+        <v>3.804172290387286</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.566819581894548</v>
+        <v>-3.590049322808262</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.010942209255195</v>
+        <v>2.001650312889709</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5919878017530481</v>
+        <v>0.4909051432327917</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.79321914737859</v>
+        <v>3.732569552266436</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.915564667118992</v>
+        <v>-3.938794408032706</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.011755894167264</v>
+        <v>2.002463997801779</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4832398478341503</v>
+        <v>0.3821571893138939</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.868282094029099</v>
+        <v>3.807632498916945</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.069551084895132</v>
+        <v>-4.092780825808847</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.019141596202448</v>
+        <v>2.009849699836962</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4832398478341503</v>
+        <v>0.3821571893138939</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.937262363174738</v>
+        <v>3.876612768062584</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.019029181067467</v>
+        <v>-4.042258921981181</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.025401559853635</v>
+        <v>2.016109663488149</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4832398478341503</v>
+        <v>0.3821571893138939</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.923313565294859</v>
+        <v>3.862663970182705</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.271504335075191</v>
+        <v>-4.294734075988905</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.936281987305959</v>
+        <v>1.926990090940473</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4832398478341503</v>
+        <v>0.3821571893138939</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.935184054350273</v>
+        <v>3.874534459238119</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.564400091554603</v>
+        <v>-4.587629832468317</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.820334219233138</v>
+        <v>1.811042322867652</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4832398478341503</v>
+        <v>0.3821571893138939</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.936394588869216</v>
+        <v>3.875744993757063</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.751064219689411</v>
+        <v>-4.774293960603125</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.749790310206536</v>
+        <v>1.74049841384105</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4565008770095904</v>
+        <v>0.355418218489334</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.924472948601802</v>
+        <v>3.863823353489649</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.897084906603373</v>
+        <v>-4.920314647517087</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.686459888177141</v>
+        <v>1.677167991811655</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4474177852157334</v>
+        <v>0.346335126695477</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.914100946261677</v>
+        <v>3.853451351149524</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.988798915712959</v>
+        <v>-5.012028656626672</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.811978341232351</v>
+        <v>1.802686444866865</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4474177852157334</v>
+        <v>0.346335126695477</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.076305002960722</v>
+        <v>4.015655407848568</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.020450574772928</v>
+        <v>-5.043680315686641</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.794164315572177</v>
+        <v>1.784872419206692</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4422493279712932</v>
+        <v>0.3411666694510368</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.068050566577872</v>
+        <v>4.007400971465718</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.102385393041811</v>
+        <v>-5.125615133955525</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.771619805833115</v>
+        <v>1.76232790946763</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4323145823842131</v>
+        <v>0.3312319238639566</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.072319136794115</v>
+        <v>4.011669541681961</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.204361515290219</v>
+        <v>-5.227591256203932</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.739754995389654</v>
+        <v>1.730463099024169</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3303384601358055</v>
+        <v>0.229255801615549</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.020059101900973</v>
+        <v>3.959409506788819</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.094355231812997</v>
+        <v>-5.117584972726711</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.775910396024718</v>
+        <v>1.766618499659233</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3535430320530807</v>
+        <v>0.2524603735328242</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.026134732295513</v>
+        <v>3.965485137183359</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.951295656072071</v>
+        <v>-4.974525396985785</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.837384237043063</v>
+        <v>1.828092340677578</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.36155645864306</v>
+        <v>0.2604738001228035</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.035192798971475</v>
+        <v>3.974543203859321</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.649848930600234</v>
+        <v>-4.673078671513947</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.965223810114334</v>
+        <v>1.955931913748849</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6630031841148972</v>
+        <v>0.5619205255946408</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.223321717137114</v>
+        <v>4.16267212202496</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.674439174835418</v>
+        <v>-4.697668915749131</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.956358890172971</v>
+        <v>1.947066993807486</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6630031841148972</v>
+        <v>0.5619205255946408</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.224292894889824</v>
+        <v>4.16364329977767</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.623400798828897</v>
+        <v>-4.646630539742611</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.977617144955335</v>
+        <v>1.968325248589849</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6630031841148972</v>
+        <v>0.5619205255946408</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.225135799269579</v>
+        <v>4.164486204157425</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.582261503962267</v>
+        <v>-4.60549124487598</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.013110961776133</v>
+        <v>2.003819065410647</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.704142478981528</v>
+        <v>0.6030598204612716</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.268857475063704</v>
+        <v>4.20820787995155</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.485626591943626</v>
+        <v>-4.50885633285734</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.867948922707523</v>
+        <v>1.858657026342038</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.800777391000168</v>
+        <v>0.6996947324799115</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.143022418398822</v>
+        <v>4.082372823286669</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.616207326474469</v>
+        <v>-4.639437067388182</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.81921867296915</v>
+        <v>1.809926776603665</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6701966564693255</v>
+        <v>0.569113997949069</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.06817602175428</v>
+        <v>4.007526426642126</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.451710992283507</v>
+        <v>-4.47494073319722</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.869444025721617</v>
+        <v>1.860152129356132</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8346929906602873</v>
+        <v>0.7336103321400309</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.151300641344941</v>
+        <v>4.090651046232787</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.374612390741635</v>
+        <v>-4.397842131655348</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.899471176774796</v>
+        <v>1.890179280409311</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8346929906602873</v>
+        <v>0.7336103321400309</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.15048835178137</v>
+        <v>4.089838756669216</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.384997585631524</v>
+        <v>-4.408227326545237</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.905185877943913</v>
+        <v>1.895893981578428</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.824307795770398</v>
+        <v>0.7232251372501416</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.154126013972509</v>
+        <v>4.093476418860355</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.403585744353749</v>
+        <v>-4.426815485267462</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.968587620231448</v>
+        <v>1.959295723865963</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8057196370481727</v>
+        <v>0.7046369785279163</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.213810124515599</v>
+        <v>4.153160529403445</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.403884291049785</v>
+        <v>-4.427114031963498</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.965337212371332</v>
+        <v>1.956045316005847</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8054210903521368</v>
+        <v>0.7043384318318804</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.210500007316276</v>
+        <v>4.149850412204122</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.303061157359357</v>
+        <v>-4.32629089827307</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.010197360786895</v>
+        <v>2.000905464421409</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8178853058364907</v>
+        <v>0.7168026473162342</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.222509431546279</v>
+        <v>4.161859836434125</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.11227979660695</v>
+        <v>-4.135509537520663</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.086639158566401</v>
+        <v>2.077347262200916</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.008666666588898</v>
+        <v>0.9075840080686416</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.337107501476267</v>
+        <v>4.276457906364113</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.005316438757529</v>
+        <v>-4.028546179671242</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.109261347443766</v>
+        <v>2.099969451078281</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.0671312745487</v>
+        <v>0.9660486160284431</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.352023111989745</v>
+        <v>4.291373516877591</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.949985850855767</v>
+        <v>-3.97321559176948</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.166360519216529</v>
+        <v>2.157068622851044</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.122461862450462</v>
+        <v>1.021379203930205</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.420188401342861</v>
+        <v>4.359538806230707</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.937931723942804</v>
+        <v>-3.961161464856517</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.164868737883152</v>
+        <v>2.155576841517667</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.134515989363424</v>
+        <v>1.033433330843168</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.421107445392076</v>
+        <v>4.360457850279922</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.979086843511025</v>
+        <v>-4.002316584424738</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.150287320239999</v>
+        <v>2.140995423874514</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.093360869795204</v>
+        <v>0.9922782112749471</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.398295003835279</v>
+        <v>4.337645408723125</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.911038280819495</v>
+        <v>-3.934268021733208</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.190357771194494</v>
+        <v>2.181065874829009</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.161409432486733</v>
+        <v>1.060326773966477</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.451975167328079</v>
+        <v>4.391325572215925</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.142638673988996</v>
+        <v>-4.165868414902709</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.117920284100288</v>
+        <v>2.108628387734802</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.161409432486733</v>
+        <v>1.060326773966477</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.472177837501674</v>
+        <v>4.41152824238952</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.192690219518216</v>
+        <v>-4.215919960431929</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.081505901955482</v>
+        <v>2.072214005589997</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.161409432486733</v>
+        <v>1.060326773966477</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.455784073568556</v>
+        <v>4.395134478456402</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.367797052094661</v>
+        <v>-4.391026793008374</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.97171508251837</v>
+        <v>1.962423186152885</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.161409432486733</v>
+        <v>1.060326773966477</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.416035987162022</v>
+        <v>4.355386392049868</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.336511031554205</v>
+        <v>-4.359740772467918</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.991252109731493</v>
+        <v>1.981960213366007</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.192695453027189</v>
+        <v>1.091612794506932</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.441830218483235</v>
+        <v>4.381180623371081</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.183485639440921</v>
+        <v>-4.206715380354634</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.151633266149711</v>
+        <v>2.142341369784226</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.345720845140473</v>
+        <v>1.244638186620216</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.632816453324111</v>
+        <v>4.572166858211957</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.211792953314191</v>
+        <v>-4.235022694227904</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.327776565508695</v>
+        <v>2.31848466914321</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.345720845140473</v>
+        <v>1.244638186620216</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.820282678232403</v>
+        <v>4.759633083120249</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.378386178427713</v>
+        <v>-4.401615919341427</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.230542226817369</v>
+        <v>2.221250330451883</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.17912762002695</v>
+        <v>1.078044961506694</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.689729694518372</v>
+        <v>4.629080099406218</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.355350385066147</v>
+        <v>-4.378580125979861</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.243432946823713</v>
+        <v>2.234141050458228</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.17912762002695</v>
+        <v>1.078044961506694</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.693406097180089</v>
+        <v>4.632756502067935</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.326104404610451</v>
+        <v>-4.349334145524164</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.252749394129487</v>
+        <v>2.243457497764001</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.17912762002695</v>
+        <v>1.078044961506694</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.691024152303584</v>
+        <v>4.630374557191431</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.433029952488302</v>
+        <v>-4.456259693402015</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.207272414135981</v>
+        <v>2.197980517770496</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.072202072149099</v>
+        <v>0.9711194136288425</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.624162062734509</v>
+        <v>4.563512467622355</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.578048510995551</v>
+        <v>-4.601278251909264</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.150693792876316</v>
+        <v>2.141401896510831</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9271835136418505</v>
+        <v>0.8261008551215939</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.538579729773394</v>
+        <v>4.47793013466124</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.696390276780268</v>
+        <v>-4.719620017693981</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.203288325820182</v>
+        <v>2.193996429454697</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9378695522047406</v>
+        <v>0.836786893684484</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.644922592168881</v>
+        <v>4.584272997056727</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.747800699100976</v>
+        <v>-4.771030440014689</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.180509854017838</v>
+        <v>2.171217957652352</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9378695522047406</v>
+        <v>0.836786893684484</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.64270828929482</v>
+        <v>4.582058694182666</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.827220150308728</v>
+        <v>-4.850449891222441</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.148645201609027</v>
+        <v>2.139353305243541</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9378695522047406</v>
+        <v>0.836786893684484</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.64261141736911</v>
+        <v>4.581961822256956</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.922683148225945</v>
+        <v>-4.945912889139659</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.110453896000183</v>
+        <v>2.101161999634698</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9378695522047406</v>
+        <v>0.836786893684484</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.642605310927153</v>
+        <v>4.581955715814999</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.858307237375231</v>
+        <v>-4.881536978288944</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.134300656903079</v>
+        <v>2.125008760537594</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.002245463055456</v>
+        <v>0.9011628045351991</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.679327254000192</v>
+        <v>4.618677658888038</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.913676399507424</v>
+        <v>-4.936906140421137</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.117886809797929</v>
+        <v>2.108594913432444</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.002245463055456</v>
+        <v>0.9011628045351991</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.685061071747919</v>
+        <v>4.624411476635765</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.959114179338251</v>
+        <v>-4.982343920251965</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.099250061208529</v>
+        <v>2.089958164843044</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.959400472377296</v>
+        <v>0.8583178138570395</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.658892440683955</v>
+        <v>4.598242845571802</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.870907345190673</v>
+        <v>-4.894137086104386</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.15440718771788</v>
+        <v>2.145115291352395</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.959400472377296</v>
+        <v>0.8583178138570395</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.678766833534274</v>
+        <v>4.618117238422121</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.764872349985364</v>
+        <v>-4.788102090899077</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.180521886324732</v>
+        <v>2.171229989959246</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.959400472377296</v>
+        <v>0.8583178138570395</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.662467534059003</v>
+        <v>4.601817938946849</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.581660686852269</v>
+        <v>-4.604890427765982</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.256237501042015</v>
+        <v>2.24694560467653</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.142612135510391</v>
+        <v>0.8583178138570395</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.774825481402905</v>
+        <v>4.604248888410894</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.509939239838418</v>
+        <v>-4.533168980752131</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.250717265695445</v>
+        <v>2.24142536932996</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.214333582524242</v>
+        <v>0.9300392608708902</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.783649535459104</v>
+        <v>4.613072942467094</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.487566214230712</v>
+        <v>-4.510795955144425</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.206582221859699</v>
+        <v>2.197290325494214</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.225589333637143</v>
+        <v>0.9412950119837917</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.737318732048017</v>
+        <v>4.566742139056006</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.520582510141456</v>
+        <v>-4.54381225105517</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.378573908380757</v>
+        <v>2.369282012015272</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.156151956970392</v>
+        <v>0.8718576353170402</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.880854510933322</v>
+        <v>4.710277917941311</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.509054874491848</v>
+        <v>-4.532284615405561</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.375106188468849</v>
+        <v>2.365814292103364</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.215152615171754</v>
+        <v>0.9308582935184027</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.908176131682389</v>
+        <v>4.737599538690377</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.606396375834216</v>
+        <v>-4.62962611674793</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.33983770045369</v>
+        <v>2.330545804088205</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.170732433006266</v>
+        <v>0.8864381113529143</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.885192134904884</v>
+        <v>4.714615541912873</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.692252405174183</v>
+        <v>-4.715482146087896</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.306746370910542</v>
+        <v>2.297454474545057</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.128356363780131</v>
+        <v>0.8440620421267793</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.861017575562041</v>
+        <v>4.69044098257003</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.701089202590302</v>
+        <v>-4.724318943504016</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.285630853764596</v>
+        <v>2.276338957399111</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.12091419113878</v>
+        <v>0.8366198694854285</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.838971473797733</v>
+        <v>4.668394880805722</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.792471765155761</v>
+        <v>-4.815701506069474</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.259242339783462</v>
+        <v>2.249950443417977</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.029531628573322</v>
+        <v>0.7452373069199703</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.794306447303507</v>
+        <v>4.623729854311496</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.780765047168755</v>
+        <v>-4.803994788082468</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.366053284802533</v>
+        <v>2.356761388437048</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.041238346560328</v>
+        <v>0.7569440249069767</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.903458735919979</v>
+        <v>4.732882142927968</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.681101543085092</v>
+        <v>-4.704331283998806</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.408951025167402</v>
+        <v>2.399659128801917</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.104425429764014</v>
+        <v>0.8201311081106631</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.944403324573596</v>
+        <v>4.773826731581584</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.691417641251444</v>
+        <v>-4.714647382165158</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.61772941917892</v>
+        <v>2.608437522813435</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.104425429764014</v>
+        <v>0.8201311081106631</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.157308157851654</v>
+        <v>4.986731564859642</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.691323673234072</v>
+        <v>-4.714553414147785</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.616945673297958</v>
+        <v>2.607653776932473</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.104795291111332</v>
+        <v>0.8205009694579811</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.156708741572134</v>
+        <v>4.986132148580123</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.698542497433916</v>
+        <v>-4.721772238347629</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.608290129562374</v>
+        <v>2.598998233196889</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.104795291111332</v>
+        <v>0.8205009694579811</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.150940727516488</v>
+        <v>4.980364134524477</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.697594074315877</v>
+        <v>-4.720823815229591</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.60866949880959</v>
+        <v>2.599377602444105</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.104795291111332</v>
+        <v>0.8205009694579811</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.150940727516488</v>
+        <v>4.980364134524477</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.673485397508226</v>
+        <v>3.673485397508225</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.988339935249082</v>
+        <v>-4.877892273485214</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.505098762417401</v>
+        <v>2.549277827122947</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.104795291111332</v>
+        <v>0.8205009694579811</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.163668335497579</v>
+        <v>4.993091742505569</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.804512271758332</v>
+        <v>3.883546691023242</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.702887740237899</v>
+        <v>4.764312479043966</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.988339935249082</v>
+        <v>-4.877892273485214</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.505098762417401</v>
+        <v>2.549277827122947</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.104795291111332</v>
+        <v>0.8205009694579811</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.695951537224267</v>
+        <v>4.757376276030334</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240910.xlsx
+++ b/tame_output/ON/bt/strategyON_20240910.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>106.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>164.8%</t>
+          <t>154.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.8%</t>
+          <t>422.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-649.4%</t>
+          <t>-664.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-121.3%</t>
+          <t>-141.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-318.6%</t>
+          <t>-322.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-141.9%</t>
+          <t>-129.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -46286,10 +46286,10 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.684747979054816</v>
+        <v>-3.76260089666136</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.287585761307938</v>
+        <v>1.25644459426532</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7132334969318646</v>
@@ -46309,10 +46309,10 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.591937497603956</v>
+        <v>-3.669790415210501</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.253982645779647</v>
+        <v>1.222841478737029</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8060439783827239</v>
@@ -46332,10 +46332,10 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.636326966933384</v>
+        <v>-3.714179884539928</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.238100333972477</v>
+        <v>1.206959166929859</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7616545090532962</v>
@@ -46355,10 +46355,10 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.752868572038727</v>
+        <v>-3.830721489645271</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.186559400442063</v>
+        <v>1.155418233399445</v>
       </c>
       <c r="F1948" t="n">
         <v>0.6451129039479535</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.792792666621299</v>
+        <v>-3.870645584227843</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.176081058439701</v>
+        <v>1.144939891397083</v>
       </c>
       <c r="F1949" t="n">
         <v>0.6451129039479535</v>
@@ -46401,10 +46401,10 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.820573064522652</v>
+        <v>-3.898425982129196</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.176466101047699</v>
+        <v>1.145324934005081</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6173325060466004</v>
@@ -46424,10 +46424,10 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.938953737252791</v>
+        <v>-4.016806654859334</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9674695519562966</v>
+        <v>0.9363283849136792</v>
       </c>
       <c r="F1951" t="n">
         <v>0.5501146538956242</v>
@@ -46447,10 +46447,10 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.047567815696121</v>
+        <v>-4.125420733302665</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.04417358129817</v>
+        <v>1.013032414255552</v>
       </c>
       <c r="F1952" t="n">
         <v>0.5501146538956242</v>
@@ -46470,10 +46470,10 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.012158777447978</v>
+        <v>-4.090011695054522</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.07285022269975</v>
+        <v>1.041709055657133</v>
       </c>
       <c r="F1953" t="n">
         <v>0.5501146538956242</v>
@@ -46493,10 +46493,10 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.973775114889827</v>
+        <v>-4.051628032496371</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.085623129065379</v>
+        <v>1.054481962022762</v>
       </c>
       <c r="F1954" t="n">
         <v>0.5884983164537754</v>
@@ -46516,10 +46516,10 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.796658784854661</v>
+        <v>-3.874511702461205</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.153198689924747</v>
+        <v>1.12205752288213</v>
       </c>
       <c r="F1955" t="n">
         <v>0.5884983164537754</v>
@@ -46539,10 +46539,10 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.841751029688207</v>
+        <v>-3.919603947294751</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.135845183753242</v>
+        <v>1.104704016710625</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5266022732843856</v>
@@ -46562,10 +46562,10 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.662375608449439</v>
+        <v>-3.740228526055983</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.201382327555164</v>
+        <v>1.170241160512546</v>
       </c>
       <c r="F1957" t="n">
         <v>0.6833790314551043</v>
@@ -46585,10 +46585,10 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.707389821970045</v>
+        <v>-3.785242739576589</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.164184097478511</v>
+        <v>1.133042930435894</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6530301361404997</v>
@@ -46608,10 +46608,10 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.974394332242481</v>
+        <v>-4.052247249849025</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.063073855708483</v>
+        <v>1.031932688665865</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4586670980975511</v>
@@ -46631,10 +46631,10 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.075592113679654</v>
+        <v>-4.153445031286197</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.021798665030115</v>
+        <v>0.9906574979874976</v>
       </c>
       <c r="F1960" t="n">
         <v>0.3902582845522319</v>
@@ -46654,10 +46654,10 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.069081147065341</v>
+        <v>-4.146934064671885</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.022003013230157</v>
+        <v>0.9908618461875394</v>
       </c>
       <c r="F1961" t="n">
         <v>0.3902582845522319</v>
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.050043019358044</v>
+        <v>-4.127895936964587</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.02614298352132</v>
+        <v>0.9950018164787031</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3320746732210373</v>
+        <v>0.4674800235907237</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.845761419510908</v>
+        <v>2.92700462973272</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.102558821632864</v>
+        <v>-4.180411739239408</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.124431064245583</v>
+        <v>1.093289897202965</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3320746732210373</v>
+        <v>0.4674800235907237</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.965055821145098</v>
+        <v>3.04629903136691</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.116425582966782</v>
+        <v>-4.194278500573326</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.119717688698149</v>
+        <v>1.088576521655532</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2942167564872144</v>
+        <v>0.4296221068569008</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.943174400090938</v>
+        <v>3.02441761031275</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.075942591044437</v>
+        <v>-4.153795508650981</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.141919415864013</v>
+        <v>1.110778248821396</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2942167564872144</v>
+        <v>0.4296221068569008</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.949182930487864</v>
+        <v>3.030426140709676</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.928199620809435</v>
+        <v>-4.006052538415979</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.098966825235213</v>
+        <v>1.067825658192596</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4620241137220976</v>
+        <v>0.5974294640917839</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.947817566105993</v>
+        <v>3.029060776327805</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.012020842084133</v>
+        <v>-4.089873759690677</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.068231958256815</v>
+        <v>1.037090791214198</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4620241137220976</v>
+        <v>0.5974294640917839</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.950611187637474</v>
+        <v>3.031854397859286</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.005868136031348</v>
+        <v>-4.083721053637893</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.071355389069587</v>
+        <v>1.04021422202697</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4681768197748818</v>
+        <v>0.6035821701445682</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.954965159660803</v>
+        <v>3.036208369882615</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.02267743418185</v>
+        <v>-4.100530351788395</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.063712146549497</v>
+        <v>1.032570979506879</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4513675216243802</v>
+        <v>0.5867728719940666</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.943960057510613</v>
+        <v>3.025203267732425</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.960379435405728</v>
+        <v>-4.038232353012273</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.154966899856766</v>
+        <v>1.123825732814149</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4966617858988223</v>
+        <v>0.6320671362685086</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.037472169872099</v>
+        <v>3.11871538009391</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.758589237740571</v>
+        <v>-3.836442155347115</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.037974980636957</v>
+        <v>1.006833813594339</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6946799780679767</v>
+        <v>0.830085328437663</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.958575086887719</v>
+        <v>3.03981829710953</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.809475950426765</v>
+        <v>-3.887328868033309</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.087910527884654</v>
+        <v>1.056769360842037</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6437932653817822</v>
+        <v>0.7791986157514685</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.998333291598177</v>
+        <v>3.079576501819989</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.722865207776958</v>
+        <v>-3.800718125383502</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.137182561060621</v>
+        <v>1.106041394018003</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7224189965869404</v>
+        <v>0.8578243469566268</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.060136466437315</v>
+        <v>3.141379676659128</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.783074505782242</v>
+        <v>-3.860927423388786</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.111634822683178</v>
+        <v>1.080493655640561</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6622096985816559</v>
+        <v>0.7976150489513423</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.022546868458817</v>
+        <v>3.103790078680628</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.733887857097891</v>
+        <v>-3.811740774704435</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.129801100196848</v>
+        <v>1.09865993315423</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6622096985816559</v>
+        <v>0.7976150489513423</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.021038486498745</v>
+        <v>3.102281696720557</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.689514725459322</v>
+        <v>-3.767367643065866</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.147413220287711</v>
+        <v>1.116272053245094</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7065828302202245</v>
+        <v>0.8419881805899109</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.047525232917323</v>
+        <v>3.128768443139134</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.711995076318207</v>
+        <v>-3.789847993924751</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.132814874082748</v>
+        <v>1.101673707040131</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7065828302202245</v>
+        <v>0.8419881805899109</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.041919027055913</v>
+        <v>3.123162237277725</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.664339345757152</v>
+        <v>-3.742192263363695</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.158258923334975</v>
+        <v>1.127117756292358</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7542385607812802</v>
+        <v>0.8896439111509665</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.076894222420351</v>
+        <v>3.158137432642163</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.563821187258397</v>
+        <v>-3.683397199347205</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.203358560109201</v>
+        <v>1.155528155273679</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8547567192800347</v>
+        <v>0.9484389751674571</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.142097490894328</v>
+        <v>3.198306844426782</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.547915857826045</v>
+        <v>-3.667491869914852</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.196475364358015</v>
+        <v>1.148644959522492</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7756440585707958</v>
+        <v>0.8693263144582182</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.081384566944657</v>
+        <v>3.137593920477111</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.503077456217647</v>
+        <v>-3.622653468306454</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.218508427612002</v>
+        <v>1.17067802277648</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7801874915156652</v>
+        <v>0.8738697474030876</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.088208329322208</v>
+        <v>3.144417682854661</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.522575912459655</v>
+        <v>-3.642151924548462</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.214869984746277</v>
+        <v>1.167039579910754</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7321028502357609</v>
+        <v>0.8257851061231833</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.063518484185343</v>
+        <v>3.119727837717797</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.478373075373754</v>
+        <v>-3.597949087462562</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.238430722108474</v>
+        <v>1.190600317272952</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7763056873216614</v>
+        <v>0.8699879432090838</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.095919788964721</v>
+        <v>3.152129142497174</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.485932741210801</v>
+        <v>-3.605508753299609</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.233816856242903</v>
+        <v>1.185986451407381</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8311090913314807</v>
+        <v>0.9247913472189031</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.12721183183986</v>
+        <v>3.183421185372313</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.327641323671529</v>
+        <v>-3.447217335760337</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.348381188441652</v>
+        <v>1.300550783606129</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8311090913314807</v>
+        <v>0.9247913472189031</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.178459597022899</v>
+        <v>3.234668950555353</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.119999320037053</v>
+        <v>-3.23957533212586</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.429878694489695</v>
+        <v>1.382048289654173</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.038751094965957</v>
+        <v>1.132433350853379</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.301485503797838</v>
+        <v>3.357694857330292</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.068967227314525</v>
+        <v>-3.188543239403332</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.445239759816977</v>
+        <v>1.397409354981454</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.089783187688485</v>
+        <v>1.183465443575907</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.327052987669625</v>
+        <v>3.383262341202078</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.003743046187319</v>
+        <v>-3.123319058276127</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.488516836360564</v>
+        <v>1.440686431525041</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.155007368815691</v>
+        <v>1.248689624703113</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.383374900438653</v>
+        <v>3.439584253971106</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.966316026116185</v>
+        <v>-3.085892038204993</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.499448616688298</v>
+        <v>1.451618211852775</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.160258906844872</v>
+        <v>1.253941162732295</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.382486795555443</v>
+        <v>3.438696149087896</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.986427682150893</v>
+        <v>-3.106003694239701</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.492660746605655</v>
+        <v>1.444830341770132</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.171286251842292</v>
+        <v>1.264968507729714</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.390359994885134</v>
+        <v>3.446569348417588</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.95801441905101</v>
+        <v>-3.077590431139817</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.664583822866819</v>
+        <v>1.616753418031296</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.112310689095863</v>
+        <v>1.205992944983285</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.515532428258488</v>
+        <v>3.571741781790941</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.883232158025997</v>
+        <v>-3.002808170114805</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.814609636494641</v>
+        <v>1.766779231659118</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.187092950120875</v>
+        <v>1.280775206008298</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.680514694091313</v>
+        <v>3.736724047623766</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.857148073762189</v>
+        <v>-2.976724085850997</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.816751246214023</v>
+        <v>1.768920841378501</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.187092950120875</v>
+        <v>1.280775206008298</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.672222670105172</v>
+        <v>3.728432023637625</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.769270160653069</v>
+        <v>-2.888846172741876</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.850095607041451</v>
+        <v>1.802265202205928</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.303018592544226</v>
+        <v>1.396700848431649</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.739971251142962</v>
+        <v>3.796180604675415</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.760377699259785</v>
+        <v>-2.879953711348593</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.871206997325556</v>
+        <v>1.823376592490033</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.303018592544226</v>
+        <v>1.396700848431649</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.757525656869753</v>
+        <v>3.813735010402207</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.928853816229663</v>
+        <v>-3.048429828318471</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.795671597942189</v>
+        <v>1.747841193106666</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.275070756827646</v>
+        <v>1.368753012715068</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.732612002844389</v>
+        <v>3.788821356376842</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.482597623600223</v>
+        <v>-2.602173635689031</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.955443772181826</v>
+        <v>1.907613367346304</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.180352087158013</v>
+        <v>1.274034343045435</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.657050498230471</v>
+        <v>3.713259851762924</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.459876519917071</v>
+        <v>-2.579452532005878</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.955196236151992</v>
+        <v>1.907365831316469</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.180352087158013</v>
+        <v>1.274034343045435</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.647714520727376</v>
+        <v>3.703923874259829</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.589078333211113</v>
+        <v>-2.708654345299921</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.062421636685544</v>
+        <v>2.014591231850021</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.051150273863971</v>
+        <v>1.144832529751393</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.729099558602119</v>
+        <v>3.785308912134572</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.614952731685139</v>
+        <v>-2.734528743773947</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.08914969978958</v>
+        <v>2.041319294954057</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.096061882575712</v>
+        <v>1.189744138463134</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.79312434632281</v>
+        <v>3.849333699855264</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.607898041469965</v>
+        <v>-2.727474053558773</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.088646931865195</v>
+        <v>2.040816527029672</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.103116572790886</v>
+        <v>1.196798828678308</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.79403251644146</v>
+        <v>3.850241869973913</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.580946817143477</v>
+        <v>-2.700522829232285</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.109433575240532</v>
+        <v>2.061603170405009</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.117996918818605</v>
+        <v>1.211679174706027</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.812966877702833</v>
+        <v>3.869176231235286</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.602491044974264</v>
+        <v>-2.722067057063072</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.284919016253177</v>
+        <v>2.237088611417654</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.117996918818605</v>
+        <v>1.211679174706027</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.997070009847793</v>
+        <v>4.053279363380246</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.624899162779136</v>
+        <v>-2.744475174867944</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.268072464034221</v>
+        <v>2.220242059198698</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.117996918818605</v>
+        <v>1.211679174706027</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.989186704750786</v>
+        <v>4.045396058283239</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.653123398356737</v>
+        <v>-2.799437687623457</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.258836769352818</v>
+        <v>2.20031105364613</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.135973671269913</v>
+        <v>1.264078101688177</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.002026755771208</v>
+        <v>4.078889414022167</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.662564324245267</v>
+        <v>-2.808878613511987</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.311314116719253</v>
+        <v>2.252788401012566</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.258400788813305</v>
+        <v>1.386505219231569</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.13173674401909</v>
+        <v>4.208599402270049</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.751440955413741</v>
+        <v>-2.897755244680461</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.278654558797164</v>
+        <v>2.220128843090477</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.169524157644831</v>
+        <v>1.297628588063095</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.081301859863307</v>
+        <v>4.158164518114265</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.827770933014647</v>
+        <v>-2.974085222281367</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.246234380650577</v>
+        <v>2.18770866494389</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.169524157644831</v>
+        <v>1.297628588063095</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.079413672757082</v>
+        <v>4.156276331008041</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.921434877692188</v>
+        <v>-3.067749166958908</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.203589032382423</v>
+        <v>2.145063316675735</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.07586021296729</v>
+        <v>1.203964643385554</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.01803553555342</v>
+        <v>4.094898193804378</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.083003303219443</v>
+        <v>-3.229317592486163</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.137395672381674</v>
+        <v>2.078869956674986</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9490772891694103</v>
+        <v>1.077181719587674</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.940399791484844</v>
+        <v>4.017262449735803</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.191303965089562</v>
+        <v>-3.337618254356283</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.107148814499544</v>
+        <v>2.048623098792857</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9490772891694103</v>
+        <v>1.077181719587674</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.953473198350763</v>
+        <v>4.030335856601721</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.209107936810307</v>
+        <v>-3.355422226077027</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.092032422594187</v>
+        <v>2.033506706887499</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8785426662642091</v>
+        <v>1.006647096682473</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.903157621390582</v>
+        <v>3.980020279641541</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.23700872391978</v>
+        <v>-3.3833230131865</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.079396148877399</v>
+        <v>2.020870433170712</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8439457421212743</v>
+        <v>0.9720501725395384</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.880923508031823</v>
+        <v>3.957786166282782</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787389</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.359534826622673</v>
+        <v>-3.505849115889394</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.027150151773441</v>
+        <v>1.968624436066753</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7214196394183804</v>
+        <v>0.8495240698366445</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.804172290387286</v>
+        <v>3.881034948638244</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.590049322808262</v>
+        <v>-3.736363612074983</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.001650312889709</v>
+        <v>1.943124597183021</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4909051432327917</v>
+        <v>0.6190095736510558</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.732569552266436</v>
+        <v>3.809432210517395</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.938794408032706</v>
+        <v>-4.085108697299426</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.002463997801779</v>
+        <v>1.943938282095091</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.510261619732158</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.807632498916945</v>
+        <v>3.884495157167903</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.092780825808847</v>
+        <v>-4.239095115075567</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.009849699836962</v>
+        <v>1.951323984130275</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.510261619732158</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.876612768062584</v>
+        <v>3.953475426313543</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.042258921981181</v>
+        <v>-4.188573211247901</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.016109663488149</v>
+        <v>1.957583947781461</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.510261619732158</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.862663970182705</v>
+        <v>3.939526628433664</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.294734075988905</v>
+        <v>-4.441048365255625</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.926990090940473</v>
+        <v>1.868464375233786</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.510261619732158</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.874534459238119</v>
+        <v>3.951397117489078</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.587629832468317</v>
+        <v>-4.733944121735037</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.811042322867652</v>
+        <v>1.752516607160965</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3821571893138939</v>
+        <v>0.510261619732158</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.875744993757063</v>
+        <v>3.952607652008021</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.774293960603125</v>
+        <v>-4.920608249869845</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.74049841384105</v>
+        <v>1.681972698134363</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.355418218489334</v>
+        <v>0.4835226489075981</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.863823353489649</v>
+        <v>3.940686011740607</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.920314647517087</v>
+        <v>-5.066628936783808</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.677167991811655</v>
+        <v>1.618642276104967</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.346335126695477</v>
+        <v>0.4744395571137411</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.853451351149524</v>
+        <v>3.930314009400482</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.012028656626672</v>
+        <v>-5.158342945893392</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.802686444866865</v>
+        <v>1.744160729160178</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.346335126695477</v>
+        <v>0.4744395571137411</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.015655407848568</v>
+        <v>4.092518066099526</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.043680315686641</v>
+        <v>-5.189994604953362</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.784872419206692</v>
+        <v>1.726346703500004</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3411666694510368</v>
+        <v>0.4692710998693009</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.007400971465718</v>
+        <v>4.084263629716676</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.125615133955525</v>
+        <v>-5.271929423222245</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.76232790946763</v>
+        <v>1.703802193760942</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3312319238639566</v>
+        <v>0.4593363542822207</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.011669541681961</v>
+        <v>4.088532199932919</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.227591256203932</v>
+        <v>-5.373905545470652</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.730463099024169</v>
+        <v>1.671937383317481</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.229255801615549</v>
+        <v>0.3573602320338132</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.959409506788819</v>
+        <v>4.036272165039778</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.117584972726711</v>
+        <v>-5.263899261993431</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.766618499659233</v>
+        <v>1.708092783952545</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2524603735328242</v>
+        <v>0.3805648039510884</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.965485137183359</v>
+        <v>4.042347795434318</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.974525396985785</v>
+        <v>-5.120839686252505</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.828092340677578</v>
+        <v>1.76956662497089</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2604738001228035</v>
+        <v>0.3885782305410677</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.974543203859321</v>
+        <v>4.05140586211028</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.825519806668175</v>
+        <v>3.678570567796728</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.673078671513947</v>
+        <v>-4.819392960780667</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.955931913748849</v>
+        <v>1.750456959170715</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5619205255946408</v>
+        <v>0.6900249560129049</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.16267212202496</v>
+        <v>4.092585541404471</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.826490984420885</v>
+        <v>3.679541745549439</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.697668915749131</v>
+        <v>-4.843983205015851</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.947066993807486</v>
+        <v>1.741592039229352</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5619205255946408</v>
+        <v>0.6900249560129049</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.16364329977767</v>
+        <v>4.093556719157182</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.680384649929195</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.646630539742611</v>
+        <v>-4.792944829009331</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.968325248589849</v>
+        <v>1.762850294011715</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5619205255946408</v>
+        <v>0.6900249560129049</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.164486204157425</v>
+        <v>4.094399623536938</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.69942274880334</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.60549124487598</v>
+        <v>-4.7518055341427</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.003819065410647</v>
+        <v>1.798344110832513</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6030598204612716</v>
+        <v>0.7311642508795357</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.20820787995155</v>
+        <v>4.138121299331062</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.515606744927275</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.50885633285734</v>
+        <v>-4.65517062212406</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.858657026342038</v>
+        <v>1.653182071763904</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6996947324799115</v>
+        <v>0.8277991628981757</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.082372823286669</v>
+        <v>4.01228624266618</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.519108789001239</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.639437067388182</v>
+        <v>-4.785751356654902</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.809926776603665</v>
+        <v>1.604451822025531</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.569113997949069</v>
+        <v>0.6972184283673332</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.007526426642126</v>
+        <v>3.937439846021639</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.503535608077321</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.47494073319722</v>
+        <v>-4.621255022463941</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.860152129356132</v>
+        <v>1.654677174777998</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7336103321400309</v>
+        <v>0.861714762558295</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.090651046232787</v>
+        <v>4.020564465612298</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.502723318513751</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.397842131655348</v>
+        <v>-4.544156420922068</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.890179280409311</v>
+        <v>1.684704325831177</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7336103321400309</v>
+        <v>0.861714762558295</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.089838756669216</v>
+        <v>4.019752176048728</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.512592097638823</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.408227326545237</v>
+        <v>-4.554541615811957</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.895893981578428</v>
+        <v>1.690419027000293</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7232251372501416</v>
+        <v>0.8513295676684057</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.093476418860355</v>
+        <v>4.023389838239867</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.583429103415249</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.426815485267462</v>
+        <v>-4.573129774534182</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.959295723865963</v>
+        <v>1.753820769287829</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7046369785279163</v>
+        <v>0.8327414089461804</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.153160529403445</v>
+        <v>4.083073948782957</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.85512053549655</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.580298114233547</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.427114031963498</v>
+        <v>-4.573428321230218</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.956045316005847</v>
+        <v>1.750570361427713</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7043384318318804</v>
+        <v>0.8324428622501445</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.149850412204122</v>
+        <v>4.079763831583634</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.584829009172938</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.32629089827307</v>
+        <v>-4.472605187539791</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.000905464421409</v>
+        <v>1.795430509843275</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.7168026473162342</v>
+        <v>0.8449070777344984</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.161859836434125</v>
+        <v>4.091773255813638</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.584958262651482</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.135509537520663</v>
+        <v>-4.281823826787384</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.077347262200916</v>
+        <v>1.871872307622781</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9075840080686416</v>
+        <v>1.035688438486906</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.276457906364113</v>
+        <v>4.206371325743626</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.564795108389078</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.028546179671242</v>
+        <v>-4.174860468937962</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.099969451078281</v>
+        <v>1.894494496500147</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9660486160284431</v>
+        <v>1.094153046446707</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.291373516877591</v>
+        <v>4.221286936257103</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.599762045001137</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.97321559176948</v>
+        <v>-4.1195298810362</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.157068622851044</v>
+        <v>1.95159366827291</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.021379203930205</v>
+        <v>1.149483634348469</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.359538806230707</v>
+        <v>4.289452225610218</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.593448612902574</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.961161464856517</v>
+        <v>-4.107475754123237</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.155576841517667</v>
+        <v>1.950101886939533</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.033433330843168</v>
+        <v>1.161537761261432</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.360457850279922</v>
+        <v>4.290371269659434</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.59532924308671</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.002316584424738</v>
+        <v>-4.148630873691458</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.140995423874514</v>
+        <v>1.93552046929638</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9922782112749471</v>
+        <v>1.120382641693211</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.337645408723125</v>
+        <v>4.267558828102637</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.608180268964593</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.934268021733208</v>
+        <v>-4.080582310999928</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.181065874829009</v>
+        <v>1.975590920250875</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.060326773966477</v>
+        <v>1.188431204384741</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.391325572215925</v>
+        <v>4.321238991595438</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.628382939138187</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.165868414902709</v>
+        <v>-4.312182704169429</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.108628387734802</v>
+        <v>1.903153433156669</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.060326773966477</v>
+        <v>1.188431204384741</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.41152824238952</v>
+        <v>4.341441661769032</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.758938414076515</v>
+        <v>3.611989175205069</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.215919960431929</v>
+        <v>-4.362234249698647</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.072214005589997</v>
+        <v>1.866739051011863</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.060326773966477</v>
+        <v>1.188431204384741</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.395134478456402</v>
+        <v>4.325047897835914</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.719190327669982</v>
+        <v>3.572241088798536</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.391026793008374</v>
+        <v>-4.537341082275092</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.962423186152885</v>
+        <v>1.756948231574752</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.060326773966477</v>
+        <v>1.188431204384741</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.355386392049868</v>
+        <v>4.285299811429381</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.726212946666922</v>
+        <v>3.579263707795476</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.359740772467918</v>
+        <v>-4.506055061734637</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.981960213366007</v>
+        <v>1.776485258787874</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.091612794506932</v>
+        <v>1.219717224925196</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.381180623371081</v>
+        <v>4.311094042750594</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.825383946239826</v>
+        <v>3.67843470736838</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.206715380354634</v>
+        <v>-4.353029669621352</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.142341369784226</v>
+        <v>1.936866415206092</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.244638186620216</v>
+        <v>1.37274261703848</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.572166858211957</v>
+        <v>4.502080277591468</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791145</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.012850171148119</v>
+        <v>3.865900932276673</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.235022694227904</v>
+        <v>-4.381336983494623</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.31848466914321</v>
+        <v>2.113009714565076</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.244638186620216</v>
+        <v>1.37274261703848</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.759633083120249</v>
+        <v>4.689546502499761</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620432</v>
+        <v>3.69911561562043</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.982253122502201</v>
+        <v>3.835303883630755</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.401615919341427</v>
+        <v>-4.547930208608145</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.221250330451883</v>
+        <v>2.01577537587375</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.078044961506694</v>
+        <v>1.206149391924958</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.629080099406218</v>
+        <v>4.55899351878573</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285644</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.985929525163919</v>
+        <v>3.838980286292473</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.378580125979861</v>
+        <v>-4.524894415246579</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.234141050458228</v>
+        <v>2.028666095880094</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.078044961506694</v>
+        <v>1.206149391924958</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.632756502067935</v>
+        <v>4.562669921447448</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399465</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.983547580287414</v>
+        <v>3.836598341415968</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.349334145524164</v>
+        <v>-4.495648434790882</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.243457497764001</v>
+        <v>2.037982543185868</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.078044961506694</v>
+        <v>1.206149391924958</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.630374557191431</v>
+        <v>4.560287976570943</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.980840819445049</v>
+        <v>3.833891580573603</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.456259693402015</v>
+        <v>-4.602573982668734</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.197980517770496</v>
+        <v>1.992505563192363</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9711194136288425</v>
+        <v>1.099223844047107</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.563512467622355</v>
+        <v>4.493425887001868</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.982269621588284</v>
+        <v>3.835320382716838</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.601278251909264</v>
+        <v>-4.747592541175982</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.141401896510831</v>
+        <v>1.935926941932698</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.8261008551215939</v>
+        <v>0.9542052855398582</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.47793013466124</v>
+        <v>4.407843554040753</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.082200860846037</v>
+        <v>3.93525162197459</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.719620017693981</v>
+        <v>-4.8659343069607</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.193996429454697</v>
+        <v>1.988521474876563</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9648913241027482</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.584272997056727</v>
+        <v>4.514186416436239</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.079986557971975</v>
+        <v>3.933037319100529</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.771030440014689</v>
+        <v>-4.917344729281408</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.171217957652352</v>
+        <v>1.965743003074219</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9648913241027482</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.582058694182666</v>
+        <v>4.511972113562178</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.079889686046265</v>
+        <v>3.932940447174818</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.850449891222441</v>
+        <v>-4.996764180489159</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.139353305243541</v>
+        <v>1.933878350665408</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9648913241027482</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.581961822256956</v>
+        <v>4.511875241636467</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.079883579604308</v>
+        <v>3.932934340732862</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.945912889139659</v>
+        <v>-5.092227178406377</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.101161999634698</v>
+        <v>1.895687045056564</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.836786893684484</v>
+        <v>0.9648913241027482</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.581955715814999</v>
+        <v>4.511869135194511</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.077979976166919</v>
+        <v>3.931030737295472</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.881536978288944</v>
+        <v>-5.027851267555662</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.125008760537594</v>
+        <v>1.919533805959461</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.9011628045351991</v>
+        <v>1.029267234953463</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.618677658888038</v>
+        <v>4.548591078267551</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.083713793914646</v>
+        <v>3.936764555043199</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.936906140421137</v>
+        <v>-5.083220429687856</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.108594913432444</v>
+        <v>1.90311995885431</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.9011628045351991</v>
+        <v>1.029267234953463</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.624411476635765</v>
+        <v>4.554324896015277</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.083252157257578</v>
+        <v>3.936302918386131</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.982343920251965</v>
+        <v>-5.128658209518683</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.089958164843044</v>
+        <v>1.884483210264911</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.8583178138570395</v>
+        <v>0.9864222442753037</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.598242845571802</v>
+        <v>4.528156264951313</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.103126550107897</v>
+        <v>3.95617731123645</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.894137086104386</v>
+        <v>-5.040451375371105</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.145115291352395</v>
+        <v>1.939640336774261</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.8583178138570395</v>
+        <v>0.9864222442753037</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.618117238422121</v>
+        <v>4.548030657801633</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.086827250632624</v>
+        <v>3.939878011761178</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.788102090899077</v>
+        <v>-4.934416380165795</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.171229989959246</v>
+        <v>1.965755035381113</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.8583178138570395</v>
+        <v>0.9864222442753037</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.601817938946849</v>
+        <v>4.53173135832636</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.08925820009667</v>
+        <v>3.942308961225224</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.604890427765982</v>
+        <v>-4.7512047170327</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.24694560467653</v>
+        <v>2.041470650098397</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.8583178138570395</v>
+        <v>0.9864222442753037</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.604248888410894</v>
+        <v>4.534162307790406</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863547</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.055049385944559</v>
+        <v>3.908100147073113</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.533168980752131</v>
+        <v>-4.679483270018849</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.24142536932996</v>
+        <v>2.035950414751827</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.9300392608708902</v>
+        <v>1.058143691289154</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.613072942467094</v>
+        <v>4.542986361846606</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.001965131865731</v>
+        <v>3.855015892994285</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.510795955144425</v>
+        <v>-4.657110244411143</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.197290325494214</v>
+        <v>1.991815370916081</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.9412950119837917</v>
+        <v>1.069399442402056</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.566742139056006</v>
+        <v>4.496655558435519</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.187163336751087</v>
+        <v>4.04021409787964</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.54381225105517</v>
+        <v>-4.690126540321888</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.369282012015272</v>
+        <v>2.163807057437138</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.8718576353170402</v>
+        <v>0.9999620657353041</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.710277917941311</v>
+        <v>4.640191337320823</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883673</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.179084562579336</v>
+        <v>4.032135323707889</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.532284615405561</v>
+        <v>-4.678598904672279</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.365814292103364</v>
+        <v>2.16033933752523</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.9308582935184027</v>
+        <v>1.058962723936667</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.737599538690377</v>
+        <v>4.66751295806989</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236292</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.182752675101124</v>
+        <v>4.035803436229678</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.62962611674793</v>
+        <v>-4.775940406014648</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.330545804088205</v>
+        <v>2.125070849510072</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.8864381113529143</v>
+        <v>1.014542541771178</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.714615541912873</v>
+        <v>4.644528961292385</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.184003757293962</v>
+        <v>4.037054518422516</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.715482146087896</v>
+        <v>-4.861796435354615</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.297454474545057</v>
+        <v>2.091979519966923</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.8440620421267793</v>
+        <v>0.9721664725450432</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.69044098257003</v>
+        <v>4.620354401949542</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610377</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.166422959114464</v>
+        <v>4.019473720243018</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.724318943504016</v>
+        <v>-4.870633232770734</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.276338957399111</v>
+        <v>2.070864002820977</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.8366198694854285</v>
+        <v>0.9647242999036925</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.668394880805722</v>
+        <v>4.598308300185233</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.176587470159514</v>
+        <v>4.029638231288067</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.815701506069474</v>
+        <v>-4.962015795336193</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.249950443417977</v>
+        <v>2.044475488839844</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.7452373069199703</v>
+        <v>0.8733417373382342</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.623729854311496</v>
+        <v>4.553643273691008</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.278715727983782</v>
+        <v>4.131766489112335</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.803994788082468</v>
+        <v>-4.950309077349186</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.356761388437048</v>
+        <v>2.151286433858914</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.7569440249069767</v>
+        <v>0.8850484553252406</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.732882142927968</v>
+        <v>4.66279556230748</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.281748066715187</v>
+        <v>4.13479882784374</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.704331283998806</v>
+        <v>-4.850645573265524</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.399659128801917</v>
+        <v>2.194184174223784</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.8201311081106631</v>
+        <v>0.9482355385289271</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.773826731581584</v>
+        <v>4.703740150961097</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452567</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.494652899993245</v>
+        <v>4.347703661121798</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.714647382165158</v>
+        <v>-4.860961671431876</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.608437522813435</v>
+        <v>2.402962568235301</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.8201311081106631</v>
+        <v>0.9482355385289271</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.986731564859642</v>
+        <v>4.916644984239155</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.493831566905334</v>
+        <v>4.346882328033888</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.714553414147785</v>
+        <v>-4.860867703414503</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.607653776932473</v>
+        <v>2.402178822354339</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.8205009694579811</v>
+        <v>0.948605399876245</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.986132148580123</v>
+        <v>4.916045567959635</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.488063552849688</v>
+        <v>4.341114313978242</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.721772238347629</v>
+        <v>-4.868086527614348</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.598998233196889</v>
+        <v>2.393523278618756</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.8205009694579811</v>
+        <v>0.948605399876245</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.980364134524477</v>
+        <v>4.910277553903989</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740919</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.488063552849688</v>
+        <v>4.341114313978242</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.720823815229591</v>
+        <v>-4.867138104496309</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.599377602444105</v>
+        <v>2.393902647865971</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.8205009694579811</v>
+        <v>0.948605399876245</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.980364134524477</v>
+        <v>4.910277553903989</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.673485397508225</v>
+        <v>3.673485397508223</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.50079116083078</v>
+        <v>4.353841921959334</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.877892273485214</v>
+        <v>-5.024206562751933</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.549277827122947</v>
+        <v>2.343802872544814</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.8205009694579811</v>
+        <v>0.948605399876245</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.993091742505569</v>
+        <v>4.923005161885081</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.883546691023242</v>
+        <v>3.797241296252738</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.764312479043966</v>
+        <v>4.658365171500192</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.877892273485214</v>
+        <v>-5.024206562751933</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.549277827122947</v>
+        <v>2.343802872544814</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.8205009694579811</v>
+        <v>0.948605399876245</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.757376276030334</v>
+        <v>4.65142896848656</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240910.xlsx
+++ b/tame_output/ON/bt/strategyON_20240910.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>22.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>106.1%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>154.2%</t>
+          <t>123.4%</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.5%</t>
+          <t>420.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-664.0%</t>
+          <t>-660.7%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-141.8%</t>
+          <t>-140.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.6%</t>
+          <t>-320.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-129.1%</t>
+          <t>-139.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>100.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911636</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213492</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006536</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436232</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074786</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.669790415210501</v>
+        <v>-3.713087437827114</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.222841478737029</v>
+        <v>1.205522669690384</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8060439783827239</v>
+        <v>0.7627469557661106</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.174740456164611</v>
+        <v>3.148762242594643</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.714179884539928</v>
+        <v>-3.757476907156541</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.206959166929859</v>
+        <v>1.189640357883214</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7616545090532962</v>
+        <v>0.718357486436683</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.149980250491556</v>
+        <v>3.124002036921588</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.830721489645271</v>
+        <v>-3.874018512261884</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.155418233399445</v>
+        <v>1.1380994243528</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6451129039479535</v>
+        <v>0.6018158813313401</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.075130995940073</v>
+        <v>3.049152782370105</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.870645584227843</v>
+        <v>-3.913942606844456</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.144939891397083</v>
+        <v>1.127621082350438</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6451129039479535</v>
+        <v>0.6018158813313401</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.08062229177074</v>
+        <v>3.054644078200772</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.898425982129196</v>
+        <v>-3.941723004745809</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.145324934005081</v>
+        <v>1.128006124958436</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6173325060466004</v>
+        <v>0.574035483429987</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.075451254798467</v>
+        <v>3.049473041228499</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.016806654859334</v>
+        <v>-4.060103677475947</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9363283849136792</v>
+        <v>0.919009575867034</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5501146538956242</v>
+        <v>0.5068176312790108</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.873476263508535</v>
+        <v>2.847498049938567</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.125420733302665</v>
+        <v>-4.168717755919278</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.013032414255552</v>
+        <v>0.9957136052089071</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5501146538956242</v>
+        <v>0.5068176312790108</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.99362592422774</v>
+        <v>2.967647710657773</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.090011695054522</v>
+        <v>-4.133308717671135</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.041709055657133</v>
+        <v>1.024390246610487</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5501146538956242</v>
+        <v>0.5068176312790108</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.008138950330063</v>
+        <v>2.982160736760096</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.051628032496371</v>
+        <v>-4.094925055112984</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.054481962022762</v>
+        <v>1.037163152976116</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5884983164537754</v>
+        <v>0.545201293837162</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.028588589207323</v>
+        <v>3.002610375637355</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.874511702461205</v>
+        <v>-3.917808725077818</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.12205752288213</v>
+        <v>1.104738713835485</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5884983164537754</v>
+        <v>0.545201293837162</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.025317618052625</v>
+        <v>2.999339404482657</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.919603947294751</v>
+        <v>-3.962900969911364</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.104704016710625</v>
+        <v>1.08738520766398</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5266022732843856</v>
+        <v>0.4833052506677722</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.988863383912904</v>
+        <v>2.962885170342936</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.740228526055983</v>
+        <v>-3.783525548672596</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.170241160512546</v>
+        <v>1.152922351465901</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6833790314551043</v>
+        <v>0.6400820088384909</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.07671641412175</v>
+        <v>3.050738200551781</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.785242739576589</v>
+        <v>-3.828539762193202</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.133042930435894</v>
+        <v>1.115724121389248</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6530301361404997</v>
+        <v>0.6097331135238863</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.039314532264576</v>
+        <v>3.013336318694608</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.052247249849025</v>
+        <v>-4.095544272465638</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.031932688665865</v>
+        <v>1.01461387961922</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4586670980975511</v>
+        <v>0.4153700754809377</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.928388271777753</v>
+        <v>2.902410058207785</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.153445031286197</v>
+        <v>-4.196742053902811</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9906574979874976</v>
+        <v>0.9733386889408522</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3902582845522319</v>
+        <v>0.3469612619356185</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.886546905547063</v>
+        <v>2.860568691977095</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.146934064671885</v>
+        <v>-4.190231087288498</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9908618461875394</v>
+        <v>0.973543037140894</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3902582845522319</v>
+        <v>0.3469612619356185</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.88414686710138</v>
+        <v>2.858168653531412</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.127895936964587</v>
+        <v>-4.171192959581201</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9950018164787031</v>
+        <v>0.9776830074320577</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4674800235907237</v>
+        <v>0.288777650604424</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.92700462973272</v>
+        <v>2.81978320594094</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.180411739239408</v>
+        <v>-4.223708761856021</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.093289897202965</v>
+        <v>1.07597108815632</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4674800235907237</v>
+        <v>0.288777650604424</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.04629903136691</v>
+        <v>2.93907760757513</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.194278500573326</v>
+        <v>-4.237575523189939</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.088576521655532</v>
+        <v>1.071257712608886</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4296221068569008</v>
+        <v>0.250919733870601</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.02441761031275</v>
+        <v>2.91719618652097</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.153795508650981</v>
+        <v>-4.197092531267594</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.110778248821396</v>
+        <v>1.09345943977475</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4296221068569008</v>
+        <v>0.250919733870601</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.030426140709676</v>
+        <v>2.923204716917896</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.006052538415979</v>
+        <v>-4.049349561032591</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.067825658192596</v>
+        <v>1.050506849145951</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5974294640917839</v>
+        <v>0.4187270911054842</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.029060776327805</v>
+        <v>2.921839352536026</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.089873759690677</v>
+        <v>-4.13317078230729</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.037090791214198</v>
+        <v>1.019771982167552</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5974294640917839</v>
+        <v>0.4187270911054842</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.031854397859286</v>
+        <v>2.924632974067507</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.083721053637893</v>
+        <v>-4.127018076254505</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.04021422202697</v>
+        <v>1.022895412980324</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6035821701445682</v>
+        <v>0.4248797971582685</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.036208369882615</v>
+        <v>2.928986946090835</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.100530351788395</v>
+        <v>-4.143827374405007</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.032570979506879</v>
+        <v>1.015252170460234</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5867728719940666</v>
+        <v>0.4080704990077668</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.025203267732425</v>
+        <v>2.917981843940645</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.038232353012273</v>
+        <v>-4.081529375628885</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.123825732814149</v>
+        <v>1.106506923767504</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6320671362685086</v>
+        <v>0.4533647632822089</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.11871538009391</v>
+        <v>3.011493956302131</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.836442155347115</v>
+        <v>-3.879739177963727</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.006833813594339</v>
+        <v>0.9895150045476941</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.830085328437663</v>
+        <v>0.6513829554513633</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.03981829710953</v>
+        <v>2.93259687331775</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.887328868033309</v>
+        <v>-3.930625890649922</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.056769360842037</v>
+        <v>1.039450551795391</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7791986157514685</v>
+        <v>0.6004962427651688</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.079576501819989</v>
+        <v>2.972355078028209</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.800718125383502</v>
+        <v>-3.844015148000115</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.106041394018003</v>
+        <v>1.088722584971358</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8578243469566268</v>
+        <v>0.679121973970327</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.141379676659128</v>
+        <v>3.034158252867348</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.860927423388786</v>
+        <v>-3.904224446005399</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.080493655640561</v>
+        <v>1.063174846593916</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7976150489513423</v>
+        <v>0.6189126759650425</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.103790078680628</v>
+        <v>2.996568654888848</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.811740774704435</v>
+        <v>-3.855037797321048</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.09865993315423</v>
+        <v>1.081341124107585</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7976150489513423</v>
+        <v>0.6189126759650425</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.102281696720557</v>
+        <v>2.995060272928777</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.767367643065866</v>
+        <v>-3.810664665682479</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.116272053245094</v>
+        <v>1.098953244198449</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8419881805899109</v>
+        <v>0.6632858076036111</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.128768443139134</v>
+        <v>3.021547019347354</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.789847993924751</v>
+        <v>-3.833145016541364</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.101673707040131</v>
+        <v>1.084354897993485</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8419881805899109</v>
+        <v>0.6632858076036111</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.123162237277725</v>
+        <v>3.015940813485945</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.742192263363695</v>
+        <v>-3.785489285980308</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.127117756292358</v>
+        <v>1.109798947245712</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8896439111509665</v>
+        <v>0.7109415381646668</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.158137432642163</v>
+        <v>3.050916008850383</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.683397199347205</v>
+        <v>-3.684971127481553</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.155528155273679</v>
+        <v>1.154898584019939</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9484389751674571</v>
+        <v>0.8114596966634213</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.198306844426782</v>
+        <v>3.11611927732436</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.667491869914852</v>
+        <v>-3.669065798049201</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.148644959522492</v>
+        <v>1.148015388268752</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8693263144582182</v>
+        <v>0.7323470359541824</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.137593920477111</v>
+        <v>3.055406353374689</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.622653468306454</v>
+        <v>-3.624227396440803</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.17067802277648</v>
+        <v>1.17004845152274</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8738697474030876</v>
+        <v>0.7368904688990519</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.144417682854661</v>
+        <v>3.06223011575224</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.642151924548462</v>
+        <v>-3.643725852682811</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.167039579910754</v>
+        <v>1.166410008657015</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8257851061231833</v>
+        <v>0.6888058276191475</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.119727837717797</v>
+        <v>3.037540270615375</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.82668474540596</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.597949087462562</v>
+        <v>-3.59952301559691</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.190600317272952</v>
+        <v>1.189970746019212</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8699879432090838</v>
+        <v>0.733008664705048</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.152129142497174</v>
+        <v>3.069941575394752</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.605508753299609</v>
+        <v>-3.607082681433957</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.185986451407381</v>
+        <v>1.185356880153641</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9247913472189031</v>
+        <v>0.7878120687148673</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.183421185372313</v>
+        <v>3.101233618269891</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.447217335760337</v>
+        <v>-3.448791263894685</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.300550783606129</v>
+        <v>1.299921212352389</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9247913472189031</v>
+        <v>0.7878120687148673</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.234668950555353</v>
+        <v>3.152481383452931</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.23957533212586</v>
+        <v>-3.241149260260209</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.382048289654173</v>
+        <v>1.381418718400433</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.132433350853379</v>
+        <v>0.9954540723493435</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.357694857330292</v>
+        <v>3.27550729022787</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475142</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.188543239403332</v>
+        <v>-3.190117167537681</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.397409354981454</v>
+        <v>1.396779783727714</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.183465443575907</v>
+        <v>1.046486165071872</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.383262341202078</v>
+        <v>3.301074774099657</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404856</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.123319058276127</v>
+        <v>-3.124892986410475</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.440686431525041</v>
+        <v>1.440056860271301</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.248689624703113</v>
+        <v>1.111710346199077</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.439584253971106</v>
+        <v>3.357396686868685</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.085892038204993</v>
+        <v>-3.087465966339341</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.451618211852775</v>
+        <v>1.450988640599035</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.253941162732295</v>
+        <v>1.116961884228259</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.438696149087896</v>
+        <v>3.356508581985475</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992663</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.106003694239701</v>
+        <v>-3.10757762237405</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.444830341770132</v>
+        <v>1.444200770516392</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.264968507729714</v>
+        <v>1.127989229225678</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.446569348417588</v>
+        <v>3.364381781315167</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.82866144563629</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.077590431139817</v>
+        <v>-3.079164359274166</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.616753418031296</v>
+        <v>1.616123846777556</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.205992944983285</v>
+        <v>1.069013666479249</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.571741781790941</v>
+        <v>3.48955421468852</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957629</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.002808170114805</v>
+        <v>-3.004382098249153</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.766779231659118</v>
+        <v>1.766149660405379</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.280775206008298</v>
+        <v>1.143795927504262</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.736724047623766</v>
+        <v>3.654536480521345</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.976724085850997</v>
+        <v>-2.978298013985345</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.768920841378501</v>
+        <v>1.768291270124761</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.280775206008298</v>
+        <v>1.143795927504262</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.728432023637625</v>
+        <v>3.646244456535204</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.888846172741876</v>
+        <v>-2.890420100876225</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.802265202205928</v>
+        <v>1.801635630952189</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.396700848431649</v>
+        <v>1.259721569927613</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.796180604675415</v>
+        <v>3.713993037572994</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.879953711348593</v>
+        <v>-2.881527639482941</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.823376592490033</v>
+        <v>1.822747021236293</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.396700848431649</v>
+        <v>1.259721569927613</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.813735010402207</v>
+        <v>3.731547443299785</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.048429828318471</v>
+        <v>-3.050003756452819</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.747841193106666</v>
+        <v>1.747211621852926</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.368753012715068</v>
+        <v>1.231773734211032</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.788821356376842</v>
+        <v>3.706633789274421</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782711</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.602173635689031</v>
+        <v>-2.603747563823379</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.907613367346304</v>
+        <v>1.906983796092564</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.274034343045435</v>
+        <v>1.137055064541399</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.713259851762924</v>
+        <v>3.631072284660503</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632639</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.579452532005878</v>
+        <v>-2.581026460140227</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.907365831316469</v>
+        <v>1.90673626006273</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.274034343045435</v>
+        <v>1.137055064541399</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.703923874259829</v>
+        <v>3.621736307157407</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777676</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.708654345299921</v>
+        <v>-2.710228273434269</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.014591231850021</v>
+        <v>2.013961660596282</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.144832529751393</v>
+        <v>1.007853251247357</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.785308912134572</v>
+        <v>3.703121345032151</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.734528743773947</v>
+        <v>-2.736102671908295</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.041319294954057</v>
+        <v>2.040689723700318</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.189744138463134</v>
+        <v>1.052764859959098</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.849333699855264</v>
+        <v>3.767146132752842</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.727474053558773</v>
+        <v>-2.729047981693121</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.040816527029672</v>
+        <v>2.040186955775932</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.196798828678308</v>
+        <v>1.059819550174272</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.850241869973913</v>
+        <v>3.768054302871492</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.700522829232285</v>
+        <v>-2.702096757366633</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.061603170405009</v>
+        <v>2.060973599151269</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.211679174706027</v>
+        <v>1.074699896201991</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.869176231235286</v>
+        <v>3.786988664132865</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784111</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.722067057063072</v>
+        <v>-2.723640985197421</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.237088611417654</v>
+        <v>2.236459040163914</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.211679174706027</v>
+        <v>1.074699896201991</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.053279363380246</v>
+        <v>3.971091796277824</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.744475174867944</v>
+        <v>-2.746049103002293</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.220242059198698</v>
+        <v>2.219612487944958</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.211679174706027</v>
+        <v>1.074699896201991</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.045396058283239</v>
+        <v>3.963208491180818</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.799437687623457</v>
+        <v>-2.774273338579893</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.20031105364613</v>
+        <v>2.210376793263555</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.264078101688177</v>
+        <v>1.0926766486533</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.078889414022167</v>
+        <v>3.97604854220124</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.808878613511987</v>
+        <v>-2.783714264468423</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.252788401012566</v>
+        <v>2.262854140629991</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.386505219231569</v>
+        <v>1.215103766196691</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.208599402270049</v>
+        <v>4.105758530449123</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.897755244680461</v>
+        <v>-2.872590895636897</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.220128843090477</v>
+        <v>2.230194582707902</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.297628588063095</v>
+        <v>1.126227135028218</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.158164518114265</v>
+        <v>4.055323646293339</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.974085222281367</v>
+        <v>-2.948920873237803</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.18770866494389</v>
+        <v>2.197774404561315</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.297628588063095</v>
+        <v>1.126227135028218</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.156276331008041</v>
+        <v>4.053435459187114</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.067749166958908</v>
+        <v>-3.042584817915344</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.145063316675735</v>
+        <v>2.155129056293161</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.203964643385554</v>
+        <v>1.032563190350676</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.094898193804378</v>
+        <v>3.992057321983451</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.229317592486163</v>
+        <v>-3.204153243442599</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.078869956674986</v>
+        <v>2.088935696292411</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.077181719587674</v>
+        <v>0.9057802665527969</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.017262449735803</v>
+        <v>3.914421577914876</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389354</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.337618254356283</v>
+        <v>-3.312453905312719</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.048623098792857</v>
+        <v>2.058688838410282</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.077181719587674</v>
+        <v>0.9057802665527969</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.030335856601721</v>
+        <v>3.927494984780795</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.355422226077027</v>
+        <v>-3.330257877033463</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.033506706887499</v>
+        <v>2.043572446504924</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.006647096682473</v>
+        <v>0.8352456436475957</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.980020279641541</v>
+        <v>3.877179407820614</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.3833230131865</v>
+        <v>-3.358158664142936</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.020870433170712</v>
+        <v>2.030936172788137</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9720501725395384</v>
+        <v>0.8006487195046609</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.957786166282782</v>
+        <v>3.854945294461855</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.505849115889394</v>
+        <v>-3.382727161643471</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.968624436066753</v>
+        <v>2.017873217765122</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8495240698366445</v>
+        <v>0.7760802220041259</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.881034948638244</v>
+        <v>3.836968639938733</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.61934808158594</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.736363612074983</v>
+        <v>-3.613241657829059</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.943124597183021</v>
+        <v>1.99237337888139</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6190095736510558</v>
+        <v>0.5455657258185371</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.809432210517395</v>
+        <v>3.765365901817884</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.085108697299426</v>
+        <v>-3.961986743053503</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.943938282095091</v>
+        <v>1.99318706379346</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.510261619732158</v>
+        <v>0.4368177718996393</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.884495157167903</v>
+        <v>3.840428848468392</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.239095115075567</v>
+        <v>-4.115973160829643</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.951323984130275</v>
+        <v>2.000572765828643</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.510261619732158</v>
+        <v>0.4368177718996393</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.953475426313543</v>
+        <v>3.909409117614032</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.188573211247901</v>
+        <v>-4.065451257001977</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.957583947781461</v>
+        <v>2.00683272947983</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.510261619732158</v>
+        <v>0.4368177718996393</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.939526628433664</v>
+        <v>3.895460319734152</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609758</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.441048365255625</v>
+        <v>-4.317926411009702</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.868464375233786</v>
+        <v>1.917713156932155</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.510261619732158</v>
+        <v>0.4368177718996393</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.951397117489078</v>
+        <v>3.907330808789566</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973162</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.733944121735037</v>
+        <v>-4.610822167489114</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.752516607160965</v>
+        <v>1.801765388859334</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.510261619732158</v>
+        <v>0.4368177718996393</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.952607652008021</v>
+        <v>3.90854134330851</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.920608249869845</v>
+        <v>-4.797486295623922</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.681972698134363</v>
+        <v>1.731221479832732</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4835226489075981</v>
+        <v>0.4100788010750794</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.940686011740607</v>
+        <v>3.896619703041096</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916205</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.066628936783808</v>
+        <v>-4.943506982537884</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.618642276104967</v>
+        <v>1.667891057803336</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4744395571137411</v>
+        <v>0.4009957092812225</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.930314009400482</v>
+        <v>3.886247700700971</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830332</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.158342945893392</v>
+        <v>-5.035220991647469</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.744160729160178</v>
+        <v>1.793409510858547</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4744395571137411</v>
+        <v>0.4009957092812225</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.092518066099526</v>
+        <v>4.048451757400015</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.189994604953362</v>
+        <v>-5.066872650707438</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.726346703500004</v>
+        <v>1.775595485198373</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4692710998693009</v>
+        <v>0.3958272520367823</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.084263629716676</v>
+        <v>4.040197321017165</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.75004401586815</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.271929423222245</v>
+        <v>-5.148807468976321</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.703802193760942</v>
+        <v>1.753050975459311</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4593363542822207</v>
+        <v>0.3858925064497021</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.088532199932919</v>
+        <v>4.044465891233409</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.373905545470652</v>
+        <v>-5.250783591224729</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.671937383317481</v>
+        <v>1.72118616501585</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3573602320338132</v>
+        <v>0.2839163842012945</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.036272165039778</v>
+        <v>3.992205856340266</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.263899261993431</v>
+        <v>-5.140777307747507</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.708092783952545</v>
+        <v>1.757341565650914</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3805648039510884</v>
+        <v>0.3071209561185697</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.042347795434318</v>
+        <v>3.998281486734807</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.120839686252505</v>
+        <v>-4.997717732006581</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.76956662497089</v>
+        <v>1.818815406669259</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3885782305410677</v>
+        <v>0.315134382708549</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.05140586211028</v>
+        <v>4.007339553410769</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.678570567796728</v>
+        <v>3.672748950487352</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.819392960780667</v>
+        <v>-4.696900539264362</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.750456959170715</v>
+        <v>1.79363231046786</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6900249560129049</v>
+        <v>0.6159515754507683</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.092585541404471</v>
+        <v>4.042319895757814</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679621</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.679541745549439</v>
+        <v>3.673720128240063</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.843983205015851</v>
+        <v>-4.721490783499546</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.741592039229352</v>
+        <v>1.784767390526497</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6900249560129049</v>
+        <v>0.6159515754507683</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.093556719157182</v>
+        <v>4.043291073510524</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.680384649929195</v>
+        <v>3.674563032619818</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.792944829009331</v>
+        <v>-4.670452407493026</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.762850294011715</v>
+        <v>1.806025645308861</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6900249560129049</v>
+        <v>0.6159515754507683</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.094399623536938</v>
+        <v>4.044133977890279</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.831734516969545</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.69942274880334</v>
+        <v>3.693601131493964</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.7518055341427</v>
+        <v>-4.629313112626395</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.798344110832513</v>
+        <v>1.841519462129658</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7311642508795357</v>
+        <v>0.6570908703173991</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.138121299331062</v>
+        <v>4.087855653684404</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700474</v>
+        <v>3.825752932700481</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.515606744927275</v>
+        <v>3.509785127617898</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.65517062212406</v>
+        <v>-4.532678200607755</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.653182071763904</v>
+        <v>1.696357423061049</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8277991628981757</v>
+        <v>0.753725782336039</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.01228624266618</v>
+        <v>3.962020597019522</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077642</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.519108789001239</v>
+        <v>3.513287171691863</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.785751356654902</v>
+        <v>-4.663258935138598</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.604451822025531</v>
+        <v>1.647627173322676</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6972184283673332</v>
+        <v>0.6231450478051965</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.937439846021639</v>
+        <v>3.887174200374981</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.503535608077321</v>
+        <v>3.497713990767945</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.621255022463941</v>
+        <v>-4.498762600947636</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.654677174777998</v>
+        <v>1.697852526075144</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.861714762558295</v>
+        <v>0.7876413819961584</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.020564465612298</v>
+        <v>3.97029881996564</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.502723318513751</v>
+        <v>3.496901701204375</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.544156420922068</v>
+        <v>-4.421663999405763</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.684704325831177</v>
+        <v>1.727879677128322</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.861714762558295</v>
+        <v>0.7876413819961584</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.019752176048728</v>
+        <v>3.969486530402071</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147906</v>
+        <v>3.832307024147912</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.512592097638823</v>
+        <v>3.506770480329447</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.554541615811957</v>
+        <v>-4.432049194295653</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.690419027000293</v>
+        <v>1.733594378297439</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8513295676684057</v>
+        <v>0.7772561871062691</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.023389838239867</v>
+        <v>3.973124192593209</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735284</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.583429103415249</v>
+        <v>3.577607486105872</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.573129774534182</v>
+        <v>-4.450637353017878</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.753820769287829</v>
+        <v>1.796996120584974</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8327414089461804</v>
+        <v>0.7586680283840437</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.083073948782957</v>
+        <v>4.032808303136299</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.85512053549655</v>
+        <v>3.855120535496556</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.580298114233547</v>
+        <v>3.574476496924171</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.573428321230218</v>
+        <v>-4.450935899713913</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.750570361427713</v>
+        <v>1.793745712724858</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8324428622501445</v>
+        <v>0.7583694816880078</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.079763831583634</v>
+        <v>4.029498185936976</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108859</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.584829009172938</v>
+        <v>3.579007391863562</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.472605187539791</v>
+        <v>-4.350112766023486</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.795430509843275</v>
+        <v>1.838605861140421</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8449070777344984</v>
+        <v>0.7708336971723616</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.091773255813638</v>
+        <v>4.041507610166979</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.80735616812147</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.584958262651482</v>
+        <v>3.579136645342106</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.281823826787384</v>
+        <v>-4.159331405271079</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.871872307622781</v>
+        <v>1.915047658919927</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.035688438486906</v>
+        <v>0.961615057924769</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.206371325743626</v>
+        <v>4.156105680096967</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906083</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.564795108389078</v>
+        <v>3.558973491079702</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.174860468937962</v>
+        <v>-4.052368047421657</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.894494496500147</v>
+        <v>1.937669847797292</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.094153046446707</v>
+        <v>1.020079665884571</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.221286936257103</v>
+        <v>4.171021290610445</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912988</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.599762045001137</v>
+        <v>3.593940427691761</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.1195298810362</v>
+        <v>-3.997037459519895</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.95159366827291</v>
+        <v>1.994769019570055</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.149483634348469</v>
+        <v>1.075410253786333</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.289452225610218</v>
+        <v>4.23918657996356</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539897</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.593448612902574</v>
+        <v>3.587626995593198</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.107475754123237</v>
+        <v>-3.984983332606932</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.950101886939533</v>
+        <v>1.993277238236678</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.161537761261432</v>
+        <v>1.087464380699295</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.290371269659434</v>
+        <v>4.240105624012775</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.59532924308671</v>
+        <v>3.589507625777334</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.148630873691458</v>
+        <v>-4.026138452175154</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.93552046929638</v>
+        <v>1.978695820593526</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.120382641693211</v>
+        <v>1.046309261131074</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.267558828102637</v>
+        <v>4.217293182455979</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382923</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.608180268964593</v>
+        <v>3.602358651655217</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.080582310999928</v>
+        <v>-3.958089889483624</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.975590920250875</v>
+        <v>2.01876627154802</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.188431204384741</v>
+        <v>1.114357823822604</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.321238991595438</v>
+        <v>4.27097334594878</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013431</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.628382939138187</v>
+        <v>3.622561321828811</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.312182704169429</v>
+        <v>-4.189690282653125</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.903153433156669</v>
+        <v>1.946328784453814</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.188431204384741</v>
+        <v>1.114357823822604</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.341441661769032</v>
+        <v>4.291176016122374</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.611989175205069</v>
+        <v>3.606167557895693</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.362234249698647</v>
+        <v>-4.239741828182344</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.866739051011863</v>
+        <v>1.909914402309008</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.188431204384741</v>
+        <v>1.114357823822604</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.325047897835914</v>
+        <v>4.274782252189256</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.572241088798536</v>
+        <v>3.566419471489159</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.537341082275092</v>
+        <v>-4.414848660758789</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.756948231574752</v>
+        <v>1.800123582871897</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.188431204384741</v>
+        <v>1.114357823822604</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.285299811429381</v>
+        <v>4.235034165782722</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660852</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.579263707795476</v>
+        <v>3.5734420904861</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.506055061734637</v>
+        <v>-4.383562640218334</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.776485258787874</v>
+        <v>1.819660610085019</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.219717224925196</v>
+        <v>1.14564384436306</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.311094042750594</v>
+        <v>4.260828397103936</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.67843470736838</v>
+        <v>3.672613090059004</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.353029669621352</v>
+        <v>-4.230537248105049</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.936866415206092</v>
+        <v>1.980041766503237</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.37274261703848</v>
+        <v>1.298669236476344</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.502080277591468</v>
+        <v>4.45181463194481</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791145</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.865900932276673</v>
+        <v>3.860079314967297</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.381336983494623</v>
+        <v>-4.25884456197832</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.113009714565076</v>
+        <v>2.156185065862221</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.37274261703848</v>
+        <v>1.298669236476344</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.689546502499761</v>
+        <v>4.639280856853103</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69911561562043</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.835303883630755</v>
+        <v>3.829482266321379</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.547930208608145</v>
+        <v>-4.425437787091842</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.01577537587375</v>
+        <v>2.058950727170895</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.206149391924958</v>
+        <v>1.132076011362821</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.55899351878573</v>
+        <v>4.508727873139073</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285644</v>
+        <v>3.70818251928565</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.838980286292473</v>
+        <v>3.833158668983097</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.524894415246579</v>
+        <v>-4.402401993730276</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.028666095880094</v>
+        <v>2.071841447177239</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.206149391924958</v>
+        <v>1.132076011362821</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.562669921447448</v>
+        <v>4.51240427580079</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399465</v>
+        <v>3.740581401399472</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.836598341415968</v>
+        <v>3.830776724106592</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.495648434790882</v>
+        <v>-4.373156013274579</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.037982543185868</v>
+        <v>2.081157894483013</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.206149391924958</v>
+        <v>1.132076011362821</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.560287976570943</v>
+        <v>4.510022330924286</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256375</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.833891580573603</v>
+        <v>3.828069963264227</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.602573982668734</v>
+        <v>-4.480081561152431</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.992505563192363</v>
+        <v>2.035680914489508</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.099223844047107</v>
+        <v>1.02515046348497</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.493425887001868</v>
+        <v>4.443160241355209</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600701005</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.835320382716838</v>
+        <v>3.829498765407461</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.747592541175982</v>
+        <v>-4.625100119659679</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.935926941932698</v>
+        <v>1.979102293229842</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9542052855398582</v>
+        <v>0.8801319049777214</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.407843554040753</v>
+        <v>4.357577908394094</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687016</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.93525162197459</v>
+        <v>3.929430004665214</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.8659343069607</v>
+        <v>-4.743441885444397</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.988521474876563</v>
+        <v>2.031696826173708</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9648913241027482</v>
+        <v>0.8908179435406115</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.514186416436239</v>
+        <v>4.463920770789581</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790806</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.933037319100529</v>
+        <v>3.927215701791153</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.917344729281408</v>
+        <v>-4.794852307765105</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.965743003074219</v>
+        <v>2.008918354371364</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9648913241027482</v>
+        <v>0.8908179435406115</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.511972113562178</v>
+        <v>4.46170646791552</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437334</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.932940447174818</v>
+        <v>3.927118829865442</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.996764180489159</v>
+        <v>-4.874271758972856</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.933878350665408</v>
+        <v>1.977053701962553</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9648913241027482</v>
+        <v>0.8908179435406115</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.511875241636467</v>
+        <v>4.46160959598981</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298401</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.932934340732862</v>
+        <v>3.927112723423486</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.092227178406377</v>
+        <v>-4.969734756890074</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.895687045056564</v>
+        <v>1.938862396353709</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9648913241027482</v>
+        <v>0.8908179435406115</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.511869135194511</v>
+        <v>4.461603489547853</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960218004</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.931030737295472</v>
+        <v>3.925209119986096</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.027851267555662</v>
+        <v>-4.905358846039359</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.919533805959461</v>
+        <v>1.962709157256605</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.029267234953463</v>
+        <v>0.9551938543913266</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.548591078267551</v>
+        <v>4.498325432620892</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.73608941335354</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.936764555043199</v>
+        <v>3.930942937733823</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.083220429687856</v>
+        <v>-4.960728008171553</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.90311995885431</v>
+        <v>1.946295310151455</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.029267234953463</v>
+        <v>0.9551938543913266</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.554324896015277</v>
+        <v>4.504059250368619</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113283</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.936302918386131</v>
+        <v>3.930481301076755</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.128658209518683</v>
+        <v>-5.00616578800238</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.884483210264911</v>
+        <v>1.927658561562056</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9864222442753037</v>
+        <v>0.9123488637131669</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.528156264951313</v>
+        <v>4.477890619304655</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113692</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.95617731123645</v>
+        <v>3.950355693927074</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.040451375371105</v>
+        <v>-4.917958953854802</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.939640336774261</v>
+        <v>1.982815688071406</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9864222442753037</v>
+        <v>0.9123488637131669</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.548030657801633</v>
+        <v>4.497765012154974</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.939878011761178</v>
+        <v>3.934056394451802</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.934416380165795</v>
+        <v>-4.811923958649492</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.965755035381113</v>
+        <v>2.008930386678258</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9864222442753037</v>
+        <v>0.9123488637131669</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.53173135832636</v>
+        <v>4.481465712679702</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.794705093307673</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.942308961225224</v>
+        <v>3.936487343915847</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.7512047170327</v>
+        <v>-4.628712295516397</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.041470650098397</v>
+        <v>2.084646001395541</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9864222442753037</v>
+        <v>0.9123488637131669</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.534162307790406</v>
+        <v>4.483896662143747</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863547</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.908100147073113</v>
+        <v>3.902278529763737</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.679483270018849</v>
+        <v>-4.556990848502546</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.035950414751827</v>
+        <v>2.079125766048971</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.058143691289154</v>
+        <v>0.9840703107270176</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.542986361846606</v>
+        <v>4.492720716199948</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394116</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.855015892994285</v>
+        <v>3.849194275684909</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.657110244411143</v>
+        <v>-4.53461782289484</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.991815370916081</v>
+        <v>2.034990722213226</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.069399442402056</v>
+        <v>0.9953260618399191</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.496655558435519</v>
+        <v>4.44638991278886</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456726</v>
+        <v>3.715607446456733</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.04021409787964</v>
+        <v>4.034392480570264</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.690126540321888</v>
+        <v>-4.567634118805585</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.163807057437138</v>
+        <v>2.206982408734283</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9999620657353041</v>
+        <v>0.9258886851731676</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.640191337320823</v>
+        <v>4.589925691674165</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883673</v>
+        <v>3.71376253688368</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.032135323707889</v>
+        <v>4.026313706398513</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.678598904672279</v>
+        <v>-4.556106483155976</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.16033933752523</v>
+        <v>2.203514688822375</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.058962723936667</v>
+        <v>0.98488934337453</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.66751295806989</v>
+        <v>4.617247312423231</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236292</v>
+        <v>3.717150699236301</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.035803436229678</v>
+        <v>4.029981818920302</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.775940406014648</v>
+        <v>-4.653447984498345</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.125070849510072</v>
+        <v>2.168246200807216</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.014542541771178</v>
+        <v>0.9404691612090417</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.644528961292385</v>
+        <v>4.594263315645727</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.705201079427687</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.037054518422516</v>
+        <v>4.03123290111314</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.861796435354615</v>
+        <v>-4.739304013838312</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.091979519966923</v>
+        <v>2.135154871264068</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9721664725450432</v>
+        <v>0.8980930919829067</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.620354401949542</v>
+        <v>4.570088756302884</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610377</v>
+        <v>3.691835499610382</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.019473720243018</v>
+        <v>4.013652102933642</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.870633232770734</v>
+        <v>-4.748140811254431</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.070864002820977</v>
+        <v>2.114039354118122</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9647242999036925</v>
+        <v>0.8906509193415559</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.598308300185233</v>
+        <v>4.548042654538575</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667451</v>
+        <v>3.715544411667458</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.029638231288067</v>
+        <v>4.023816613978691</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.962015795336193</v>
+        <v>-4.83952337381989</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.044475488839844</v>
+        <v>2.087650840136988</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.8733417373382342</v>
+        <v>0.7992683567760976</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.553643273691008</v>
+        <v>4.50337762804435</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889186</v>
+        <v>3.673978374889194</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.131766489112335</v>
+        <v>4.125944871802959</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.950309077349186</v>
+        <v>-4.827816655832883</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.151286433858914</v>
+        <v>2.194461785156059</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.8850484553252406</v>
+        <v>0.810975074763104</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.66279556230748</v>
+        <v>4.612529916660822</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.68247609940957</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.13479882784374</v>
+        <v>4.128977210534364</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.850645573265524</v>
+        <v>-4.728153151749221</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.194184174223784</v>
+        <v>2.237359525520929</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.9482355385289271</v>
+        <v>0.8741621579667905</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.703740150961097</v>
+        <v>4.653474505314438</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452567</v>
+        <v>3.672895177452574</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.347703661121798</v>
+        <v>4.341882043812422</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.860961671431876</v>
+        <v>-4.738469249915573</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.402962568235301</v>
+        <v>2.446137919532446</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.9482355385289271</v>
+        <v>0.8741621579667905</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.916644984239155</v>
+        <v>4.866379338592496</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762291</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.346882328033888</v>
+        <v>4.341060710724512</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.860867703414503</v>
+        <v>-4.7383752818982</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.402178822354339</v>
+        <v>2.445354173651484</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.948605399876245</v>
+        <v>0.8745320193141085</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.916045567959635</v>
+        <v>4.865779922312977</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988013</v>
+        <v>3.633213467988022</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.341114313978242</v>
+        <v>4.335292696668866</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.868086527614348</v>
+        <v>-4.745594106098045</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.393523278618756</v>
+        <v>2.436698629915901</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.948605399876245</v>
+        <v>0.8745320193141085</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.910277553903989</v>
+        <v>4.860011908257331</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740919</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.341114313978242</v>
+        <v>4.335292696668866</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.867138104496309</v>
+        <v>-4.744645682980006</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.393902647865971</v>
+        <v>2.437077999163116</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.948605399876245</v>
+        <v>0.8745320193141085</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.910277553903989</v>
+        <v>4.860011908257331</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.673485397508223</v>
+        <v>3.673485397508225</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.353841921959334</v>
+        <v>4.348020304649958</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.024206562751933</v>
+        <v>-5.049761501573697</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.343802872544814</v>
+        <v>2.327759279706732</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.948605399876245</v>
+        <v>0.8745320193141085</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.923005161885081</v>
+        <v>4.872739516238423</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.797241296252738</v>
+        <v>3.504113543696956</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.658365171500192</v>
+        <v>4.349966303074345</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.024206562751933</v>
+        <v>-4.991639088719591</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.343802872544814</v>
+        <v>2.352954243272761</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.948605399876245</v>
+        <v>0.8407057716246445</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.65142896848656</v>
+        <v>4.854389766049133</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240910.xlsx
+++ b/tame_output/ON/bt/strategyON_20240910.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>100.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>134.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-616.8%</t>
+          <t>-613.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-48.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-47.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.5%</t>
+          <t>417.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.7%</t>
+          <t>-659.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,27 +1135,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-247.1%</t>
+          <t>-245.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-140.9%</t>
+          <t>-129.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-228.8%</t>
+          <t>-225.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.0%</t>
+          <t>-244.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-139.9%</t>
+          <t>-142.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100.6%</t>
+          <t>103.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-137.6%</t>
+          <t>-135.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>48.7%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.3634908492490375</v>
+        <v>0.3984718957764029</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.26761008749881</v>
+        <v>3.281602506109757</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.70757260984084</v>
+        <v>1.742553656368206</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.147113738017447</v>
+        <v>4.168102365933867</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2397963636932034</v>
+        <v>0.2747774102205688</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.253073377774018</v>
+        <v>3.267065796384965</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.70757260984084</v>
+        <v>1.742553656368206</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.182054822514989</v>
+        <v>4.203043450431408</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2448339544207899</v>
+        <v>0.2798150009481553</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.253665854250391</v>
+        <v>3.267658272861337</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.763217066107158</v>
+        <v>1.798198112634523</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.214018936460117</v>
+        <v>4.235007564376536</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.01236008028726682</v>
+        <v>0.02262096624009857</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.129534621990905</v>
+        <v>3.143527040601852</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.506023031399101</v>
+        <v>1.541004077926466</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.03844889725902</v>
+        <v>4.059437525175439</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.07812747033667888</v>
+        <v>-0.04314642380931349</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.104245275101611</v>
+        <v>3.118237693712557</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.506023031399101</v>
+        <v>1.541004077926466</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.03946650638949</v>
+        <v>4.06045513430591</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3104983844983536</v>
+        <v>-0.2755173379709882</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.001924941424697</v>
+        <v>3.015917360035643</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.506023031399101</v>
+        <v>1.541004077926466</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.030094538377246</v>
+        <v>4.051083166293665</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.3922702849261053</v>
+        <v>-0.3572892383987399</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.959298907208834</v>
+        <v>2.97329132581978</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.533058604805237</v>
+        <v>1.568039651332603</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.036398608376166</v>
+        <v>4.057387236292586</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6545912063460799</v>
+        <v>-0.6196101598187145</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.859135855474547</v>
+        <v>2.873128274085493</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.533058604805237</v>
+        <v>1.568039651332603</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.041163925209869</v>
+        <v>4.062152553126287</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6432019696912785</v>
+        <v>-0.6082209231639131</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.861516346255708</v>
+        <v>2.875508764866654</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.544447841460039</v>
+        <v>1.579428887987404</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.045822263321989</v>
+        <v>4.066810891238409</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.8956798641106845</v>
+        <v>-0.860698817583319</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.758452079993008</v>
+        <v>2.772444498603955</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.291969947040633</v>
+        <v>1.326950993567998</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.89226241817541</v>
+        <v>3.913251046091829</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.185811530716116</v>
+        <v>-1.15083048418875</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.642265629949757</v>
+        <v>2.656258048560704</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.316051741780813</v>
+        <v>1.351032788308178</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.906577711618439</v>
+        <v>3.927566339534859</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.393815589069193</v>
+        <v>-1.358834542541828</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.563956151162452</v>
+        <v>2.577948569773398</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.316051741780813</v>
+        <v>1.351032788308178</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.911469856172364</v>
+        <v>3.932458484088784</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.455994000230163</v>
+        <v>-1.421012953702798</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.534166243036052</v>
+        <v>2.548158661646998</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.253873330619843</v>
+        <v>1.288854377147208</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.86924426581377</v>
+        <v>3.89023289373019</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.822062727374816</v>
+        <v>-1.78708168084745</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.38082305148464</v>
+        <v>2.394815470095586</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.88780460347519</v>
+        <v>0.9227856500025552</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.642687328833428</v>
+        <v>3.663675956749847</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.0305535088265</v>
+        <v>-1.995572462299135</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.317765028642734</v>
+        <v>2.331757447253681</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.6793138220235055</v>
+        <v>0.7142948685508708</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.537931149701186</v>
+        <v>3.558919777617604</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.277754693591722</v>
+        <v>-2.242773647064356</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.226983305145214</v>
+        <v>2.24097572375616</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.699467175522318</v>
+        <v>0.7344482220496832</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.558121912209042</v>
+        <v>3.579110540125461</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.770139721615819</v>
+        <v>-2.735158675088453</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.031135685979308</v>
+        <v>2.045128104590254</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.2070821474982212</v>
+        <v>0.2420631940255865</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.263797287438316</v>
+        <v>3.284785915354735</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.155320112545891</v>
+        <v>-3.120339066018526</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.875606068420142</v>
+        <v>1.889598487031088</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.2070821474982212</v>
+        <v>0.2420631940255865</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.262339826251179</v>
+        <v>3.283328454167598</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.405190792560473</v>
+        <v>-3.370209746033107</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.777426919868925</v>
+        <v>1.791419338479872</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.2433448673286845</v>
+        <v>0.2783259138560497</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.285866581604073</v>
+        <v>3.306855209520492</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.611702569447494</v>
+        <v>-3.576721522920129</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.690928267770375</v>
+        <v>1.704920686381321</v>
       </c>
       <c r="F1857" t="n">
-        <v>0.036833090441663</v>
+        <v>0.07181413696902822</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.158065574128118</v>
+        <v>3.179054202044537</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.931046644527996</v>
+        <v>-3.89606559800063</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.564963564438434</v>
+        <v>1.57895598304938</v>
       </c>
       <c r="F1858" t="n">
-        <v>0.036833090441663</v>
+        <v>0.07181413696902822</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.159838500828378</v>
+        <v>3.180827128744796</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.31725647580377</v>
+        <v>-4.282275429276405</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.396812519395528</v>
+        <v>1.410804938006475</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.05393984927578033</v>
+        <v>-0.0189588027484151</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.091707624465316</v>
+        <v>3.112696252381735</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.551950469936322</v>
+        <v>-4.516969423408957</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.291219696744598</v>
+        <v>1.305212115355544</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.04760358204652515</v>
+        <v>-0.01262253551915993</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.08379415980496</v>
+        <v>3.104782787721379</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006536</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.887613117166775</v>
+        <v>-4.85263207063941</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.155535229508382</v>
+        <v>1.169527648119328</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.11553456753543</v>
+        <v>-0.08055352100806473</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.041616160167582</v>
+        <v>3.062604788084001</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309427</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.964057447369647</v>
+        <v>-4.929076400842281</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.131445057661475</v>
+        <v>1.145437476272421</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.03508905844176807</v>
+        <v>-0.0001080119144028502</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.096371025858021</v>
+        <v>3.11735965377444</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970908</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.329184830008393</v>
+        <v>-5.294203783481028</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9846486196118076</v>
+        <v>0.998641038222754</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3313998427407806</v>
+        <v>-0.2964187962134154</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.917839070284444</v>
+        <v>2.938827698200864</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.737773607189072</v>
+        <v>-5.702792560661706</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8199746527542953</v>
+        <v>0.8339670713652421</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7050075733940938</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.671447347990797</v>
+        <v>2.692435975907216</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.851534019211937</v>
+        <v>-5.816552972684571</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7696559204166098</v>
+        <v>0.7836483390275566</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7050075733940938</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.666632780462257</v>
+        <v>2.687621408378676</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.267925893498934</v>
+        <v>-6.232944846971568</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6010932213106881</v>
+        <v>0.6150856399216349</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7050075733940938</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.664626831071135</v>
+        <v>2.685615458987554</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.629099523315922</v>
+        <v>-6.594118476788556</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4668824600525721</v>
+        <v>0.4808748786635189</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7050075733940938</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.674885521739814</v>
+        <v>2.695874149656233</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.972358042958941</v>
+        <v>-6.937376996431575</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3256786173410595</v>
+        <v>0.3396710359520063</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7050075733940938</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.670985086885509</v>
+        <v>2.691973714801928</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.020560860201285</v>
+        <v>-6.985579813673919</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3048024104991232</v>
+        <v>0.31879482911007</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7050075733940938</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.669390006940509</v>
+        <v>2.690378634856929</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.187369520175647</v>
+        <v>-7.152388473648281</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2418579224385864</v>
+        <v>0.2558503410495332</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.7822719436345955</v>
+        <v>-0.7472908971072303</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.647798988641836</v>
+        <v>2.668787616558255</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.37408922848495</v>
+        <v>-7.339108181957584</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1631437345804621</v>
+        <v>0.1771361531914089</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.7822719436345955</v>
+        <v>-0.7472908971072303</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.643772684107433</v>
+        <v>2.664761312023852</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.757090617227581</v>
+        <v>-7.722109570700215</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.009841077761825634</v>
+        <v>0.02383349637277243</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.7822719436345955</v>
+        <v>-0.7472908971072303</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.643670582785849</v>
+        <v>2.664659210702268</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.761577062428969</v>
+        <v>-7.726596015901603</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.01061801565270049</v>
+        <v>0.02461043426364729</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.7867583888359841</v>
+        <v>-0.7517773423086189</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.643550231636446</v>
+        <v>2.664538859552865</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.121107384932973</v>
+        <v>-8.086126338405606</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1278438100508503</v>
+        <v>-0.1138513914399035</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.7867583888359841</v>
+        <v>-0.7517773423086189</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.648900534934496</v>
+        <v>2.669889162850915</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.171456448387195</v>
+        <v>-8.136475401859828</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1400674154753618</v>
+        <v>-0.126074996864415</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8371074522902062</v>
+        <v>-0.802126405762841</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.62660711681914</v>
+        <v>2.647595744735559</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.269075725808591</v>
+        <v>-8.234094679281224</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1760733758221513</v>
+        <v>-0.1620809572112045</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9347267297116029</v>
+        <v>-0.8997456831842376</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.571077300988071</v>
+        <v>2.59206592890449</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.32314722531695</v>
+        <v>-8.288166178789583</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1948084193039228</v>
+        <v>-0.180816000692976</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.9887982292199623</v>
+        <v>-0.9538171826925971</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.541527957604627</v>
+        <v>2.562516585521047</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.326723011408697</v>
+        <v>-8.29174196488133</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1907255366219793</v>
+        <v>-0.1767331180110325</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.014327151136455</v>
+        <v>-0.9793461046090897</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.531723801573374</v>
+        <v>2.552712429489794</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.360375849917171</v>
+        <v>-8.325394803389804</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1997041175409326</v>
+        <v>-0.1857116989299858</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.114740519053492</v>
+        <v>-1.079759472526127</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.475958335307588</v>
+        <v>2.496946963224007</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.499461964536028</v>
+        <v>-8.464480918008661</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2399668618950543</v>
+        <v>-0.2259744432841075</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.253826633672349</v>
+        <v>-1.218845587144984</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.407878368029695</v>
+        <v>2.428866995946114</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.674586381922571</v>
+        <v>-8.639605335395204</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2954614081021552</v>
+        <v>-0.2814689894912084</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.428951051058893</v>
+        <v>-1.393970004531528</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.317358938345286</v>
+        <v>2.338347566261705</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.909038475937061</v>
+        <v>-8.874057429409694</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3964614106095468</v>
+        <v>-0.3824689919986</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.428951051058893</v>
+        <v>-1.393970004531528</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.310139773443689</v>
+        <v>2.331128401360109</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.013413206963508</v>
+        <v>-8.978432160436141</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4448834937941015</v>
+        <v>-0.4308910751831547</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.533325782085339</v>
+        <v>-1.498344735557973</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.240842744053846</v>
+        <v>2.261831371970265</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.175926672662092</v>
+        <v>-9.140945626134725</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5087730902349792</v>
+        <v>-0.4947806716240324</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.630959212504025</v>
+        <v>-1.59597816597666</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.18337847564119</v>
+        <v>2.204367103557609</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.301963466030381</v>
+        <v>-9.266982419503014</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5564940789531803</v>
+        <v>-0.5425016603422335</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.570726543166918</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.20122317795615</v>
+        <v>2.222211805872569</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.24489169413445</v>
+        <v>-9.209910647607083</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5296750345084069</v>
+        <v>-0.5156826158974601</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.570726543166918</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.205213513642551</v>
+        <v>2.22620214155897</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.386563535858571</v>
+        <v>-9.351582489331204</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5878189980967967</v>
+        <v>-0.5738265794858499</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.570726543166918</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.20373828674381</v>
+        <v>2.224726914660228</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.336972691433736</v>
+        <v>-9.301991644906369</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5529292501619909</v>
+        <v>-0.5389368315510441</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.556116745269449</v>
+        <v>-1.521135698742084</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.248546203563582</v>
+        <v>2.269534831480001</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.18805435696188</v>
+        <v>-9.153073310434513</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5064130500199311</v>
+        <v>-0.4924206314089843</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.524867154534276</v>
+        <v>-1.489886108006911</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.254244824358003</v>
+        <v>2.275233452274422</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.96220920424247</v>
+        <v>-8.927228157715103</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4064959158959582</v>
+        <v>-0.3925034972850114</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.447959432419747</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.28897990274651</v>
+        <v>2.309968530662929</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.837630547904878</v>
+        <v>-8.802649501377511</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3555253088048627</v>
+        <v>-0.3415328901939159</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.447959432419747</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.290119047302569</v>
+        <v>2.311107675218988</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.812593866336368</v>
+        <v>-8.777612819809001</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3428768620153511</v>
+        <v>-0.3288844434044043</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.422630344869011</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.307950273995118</v>
+        <v>2.328938901911537</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.740460691048487</v>
+        <v>-8.70547964452112</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3082898876615623</v>
+        <v>-0.2942974690506155</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.422630344869011</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.313683978233754</v>
+        <v>2.334672606150173</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669094298438839</v>
+        <v>-8.634113251911472</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2894805930115685</v>
+        <v>-0.2754881744006217</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.351263952259363</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.346766551405678</v>
+        <v>2.367755179322097</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232416</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.575635264453615</v>
+        <v>-8.540654217926248</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2619804607303862</v>
+        <v>-0.2479880421194394</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.351263952259363</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.33688307009277</v>
+        <v>2.357871698009189</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436232</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.564982082900183</v>
+        <v>-8.530001036372816</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2595537486083872</v>
+        <v>-0.2455613299974404</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.351263952259363</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.335048509593396</v>
+        <v>2.356037137509816</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467075044223693</v>
+        <v>-8.432093997696326</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.220691248111252</v>
+        <v>-0.2066988295003052</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.318259248926172</v>
+        <v>-1.283278202398807</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.37553964453627</v>
+        <v>2.396528272452688</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443121503247735</v>
+        <v>-8.408140456720368</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.210441325575375</v>
+        <v>-0.1964489069644282</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.294305707950215</v>
+        <v>-1.259324661422849</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.390580275267338</v>
+        <v>2.411568903183757</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179061564924938</v>
+        <v>-8.144080518397571</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1180776664080083</v>
+        <v>-0.1040852477970615</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.030245769627419</v>
+        <v>-0.9952647231000533</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.535755922099263</v>
+        <v>2.556744550015682</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.4719819414201</v>
+        <v>-7.437000894892733</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1619671493336261</v>
+        <v>0.1759595679445729</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.030245769627419</v>
+        <v>-0.9952647231000533</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.532968888438962</v>
+        <v>2.553957516355382</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388729</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.431797643053909</v>
+        <v>-7.396816596526542</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1783844925679436</v>
+        <v>0.1923769111788904</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9900614712612278</v>
+        <v>-0.9550804247338626</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.557423091346518</v>
+        <v>2.578411719262937</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.268397772114547</v>
+        <v>-7.23341672558718</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2431112621644456</v>
+        <v>0.2571036807753924</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8266616003218653</v>
+        <v>-0.7916805537945001</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.654829835130893</v>
+        <v>2.675818463047312</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.034916549884948</v>
+        <v>-6.999935503357581</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3444281798941371</v>
+        <v>0.3584205985050839</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5931803780922668</v>
+        <v>-0.5581993315649015</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.802842997306504</v>
+        <v>2.823831625222923</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.885250158877433</v>
+        <v>-6.850269112350066</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4014025259841842</v>
+        <v>0.415394944595131</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5002768868497308</v>
+        <v>-0.4652958403223656</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.855692881739067</v>
+        <v>2.876681509655485</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.752974685246547</v>
+        <v>-6.71799363871918</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3555735014436934</v>
+        <v>0.3695659200546402</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3680014132188442</v>
+        <v>-0.3330203666914789</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.836318951924753</v>
+        <v>2.857307579841172</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.597236352686805</v>
+        <v>-6.562255306159438</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4206838951552268</v>
+        <v>0.4346763137661735</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2122630806591026</v>
+        <v>-0.1772820341317374</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.932577012148235</v>
+        <v>2.953565640064654</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.512271685957485</v>
+        <v>-6.477290639430118</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4675761030706136</v>
+        <v>0.4815685216815604</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.127298413929783</v>
+        <v>-0.0923173674024178</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.996462153409485</v>
+        <v>3.017450781325904</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.617861675730589</v>
+        <v>-6.582880629203222</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2973641775621529</v>
+        <v>0.3113565961730997</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2328884037028874</v>
+        <v>-0.1979073571755222</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.805132229946404</v>
+        <v>2.826120857862823</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.549627091105162</v>
+        <v>-6.514646044577795</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3732023532894102</v>
+        <v>0.387194771900357</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2144730808303514</v>
+        <v>-0.1794920343029862</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.864725765547012</v>
+        <v>2.885714393463431</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.401687049697562</v>
+        <v>-6.366706003170195</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3157575612140429</v>
+        <v>0.3297499798249897</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1941521649217938</v>
+        <v>-0.1591711183944286</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.760297506453739</v>
+        <v>2.781286134370158</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.348717527443574</v>
+        <v>-6.313736480916207</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3282313838621604</v>
+        <v>0.3422238024731072</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.1062015961404397</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.783365233552654</v>
+        <v>2.804353861469074</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.182929331483283</v>
+        <v>-6.147948284955916</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3875860501511834</v>
+        <v>0.4015784687621302</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.1062015961404397</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.776404621457561</v>
+        <v>2.797393249373981</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.149566125004514</v>
+        <v>-6.114585078477147</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4153936871238342</v>
+        <v>0.429386105734781</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.1062015961404397</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.790866975838704</v>
+        <v>2.811855603755124</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.041306987881993</v>
+        <v>-6.006325941354626</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4532294624320379</v>
+        <v>0.4672218810429847</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1411826426678049</v>
+        <v>-0.1062015961404397</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.785399096297899</v>
+        <v>2.806387724214319</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.918015853064862</v>
+        <v>-5.883034806537495</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.500044010369467</v>
+        <v>0.5140364289804138</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.01789150785067445</v>
+        <v>0.01708953867669077</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.856871871198754</v>
+        <v>2.877860499115174</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.865318985933571</v>
+        <v>-5.830337939406204</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5288237354593086</v>
+        <v>0.5428161540702554</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.03480535928061673</v>
+        <v>0.06978640580798195</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.896190969714854</v>
+        <v>2.917179597631274</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.621553543950126</v>
+        <v>-5.586572497422759</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6221106205997371</v>
+        <v>0.6361030392106839</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.03480535928061673</v>
+        <v>0.06978640580798195</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.891971678061905</v>
+        <v>2.912960305978324</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.531777871573654</v>
+        <v>-5.496796825046287</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6601452034703419</v>
+        <v>0.6741376220812887</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.09640480419492675</v>
+        <v>0.131385850722292</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.931055658930507</v>
+        <v>2.952044286846927</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.281927477624579</v>
+        <v>-5.246946431097212</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.752827436033674</v>
+        <v>0.7668198546446208</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.09640480419492675</v>
+        <v>0.131385850722292</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.923797733914209</v>
+        <v>2.944786361830629</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.106035385157147</v>
+        <v>-5.07105433862978</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8267833965412956</v>
+        <v>0.8407758151522424</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.09640480419492675</v>
+        <v>0.131385850722292</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.927396857434858</v>
+        <v>2.948385485351277</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.934588922134684</v>
+        <v>-4.899607875607317</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9086894878048346</v>
+        <v>0.9226819064157814</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2678512672173899</v>
+        <v>0.3028323137447551</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.04359224130289</v>
+        <v>3.064580869219309</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.854566635025563</v>
+        <v>-4.819585588498196</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.93971888026478</v>
+        <v>0.9537112988757268</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3478735543265108</v>
+        <v>0.3828546008538761</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.090626091184659</v>
+        <v>3.111614719101078</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.790930892791629</v>
+        <v>-4.755949846264262</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9698679782126711</v>
+        <v>0.9838603968236179</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4115092965604454</v>
+        <v>0.4464903430878106</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.133502337579337</v>
+        <v>3.154490965495756</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074786</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.697233574575233</v>
+        <v>-4.662252528047866</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9885411642830246</v>
+        <v>1.002533582893971</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4115092965604454</v>
+        <v>0.4464903430878106</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.114696596363133</v>
+        <v>3.135685224279552</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.707736197640522</v>
+        <v>-4.672755151113155</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9860831916817865</v>
+        <v>1.000075610292733</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4010066734951565</v>
+        <v>0.4359877200225217</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.110138099148837</v>
+        <v>3.131126727065256</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.595249936971648</v>
+        <v>-4.560268890444281</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.035007009784157</v>
+        <v>1.048999428395103</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4010066734951565</v>
+        <v>0.4359877200225217</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.114067412983657</v>
+        <v>3.135056040900076</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.577536250093782</v>
+        <v>-4.542555203566415</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.042771068452643</v>
+        <v>1.05676348706359</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4041880023920733</v>
+        <v>0.4391690489194385</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.116654794239147</v>
+        <v>3.137643422155566</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.454061978780764</v>
+        <v>-4.419080932253397</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.089158848197843</v>
+        <v>1.10315126680879</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4041880023920733</v>
+        <v>0.4391690489194385</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.113652865459141</v>
+        <v>3.13464149337556</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.234041180743754</v>
+        <v>-4.199060134216387</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.178746204423262</v>
+        <v>1.192738623034209</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5454078474600536</v>
+        <v>0.5803888939874188</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.199963809510543</v>
+        <v>3.220952437426962</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.101173491680476</v>
+        <v>-4.066192445153109</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.247787462850396</v>
+        <v>1.261779881461343</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5454078474600536</v>
+        <v>0.5803888939874188</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.215857992312366</v>
+        <v>3.236846620228786</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.981000408315977</v>
+        <v>-3.94601936178861</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.297002540636498</v>
+        <v>1.310994959247444</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6655809308245525</v>
+        <v>0.7005619773519177</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.289107686771367</v>
+        <v>3.310096314687787</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.845747046986</v>
+        <v>-3.810766000458633</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.361191987729928</v>
+        <v>1.375184406340875</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8008342921545296</v>
+        <v>0.8358153386818948</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.380347806130794</v>
+        <v>3.401336434047213</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.905621874343693</v>
+        <v>-3.870640827816326</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.323279548188277</v>
+        <v>1.337271966799224</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7409594647968375</v>
+        <v>0.7759405113242027</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.330460401117604</v>
+        <v>3.351449029034023</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.785801643432855</v>
+        <v>-3.750820596905488</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.386496809786821</v>
+        <v>1.400489228397767</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7409594647968375</v>
+        <v>0.7759405113242027</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.345749570351813</v>
+        <v>3.366738198268232</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.788271349894661</v>
+        <v>-3.753290303367294</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.29315312652454</v>
+        <v>1.307145545135487</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7384897583350314</v>
+        <v>0.7734708048623966</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.251911945797171</v>
+        <v>3.27290057371359</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.856641536218671</v>
+        <v>-3.821660489691304</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.185066913480237</v>
+        <v>1.199059332091184</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.7827465038986116</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.176739226704201</v>
+        <v>3.19772785462062</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.968513815844822</v>
+        <v>-3.933532769317455</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.130754710261668</v>
+        <v>1.144747128872615</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.7827465038986116</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.167175935336092</v>
+        <v>3.188164563252511</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.024033891737411</v>
+        <v>-3.989052845210044</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.245577516596835</v>
+        <v>1.259569935207782</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.7827465038986116</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.304206772028295</v>
+        <v>3.325195399944714</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.848559631944942</v>
+        <v>-3.813578585417575</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.32033445250561</v>
+        <v>1.334326871116557</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.7827465038986116</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.308774004020083</v>
+        <v>3.329762631936501</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.840635257360028</v>
+        <v>-3.805654210832661</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.299246231100783</v>
+        <v>1.31323864971173</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7477654573712463</v>
+        <v>0.7827465038986116</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.28451603278129</v>
+        <v>3.305504660697709</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.834357054790179</v>
+        <v>-3.799376008262812</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.230295825530172</v>
+        <v>1.244288244141119</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7540436599410953</v>
+        <v>0.7890247064684606</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.216821267724649</v>
+        <v>3.237809895641068</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.774504435586456</v>
+        <v>-3.739523389059089</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.264409259643794</v>
+        <v>1.278401678254741</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7540436599410953</v>
+        <v>0.7890247064684606</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.226993654156781</v>
+        <v>3.2479822820732</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.688260972560078</v>
+        <v>-3.653279926032711</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.293852915428205</v>
+        <v>1.307845334039152</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7540436599410953</v>
+        <v>0.7890247064684606</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.221939924730641</v>
+        <v>3.242928552647061</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.733567791959058</v>
+        <v>-3.698586745431691</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.267505963113139</v>
+        <v>1.281498381724086</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7132334969318646</v>
+        <v>0.7482145434592298</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.189229602369628</v>
+        <v>3.210218230286047</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.76260089666136</v>
+        <v>-3.727619850133993</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.25644459426532</v>
+        <v>1.270437012876267</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7132334969318646</v>
+        <v>0.7482145434592298</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.18978147540273</v>
+        <v>3.210770103319149</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.713087437827114</v>
+        <v>-3.677950810136901</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.205522669690384</v>
+        <v>1.219577320766469</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7627469557661106</v>
+        <v>0.7978835834563213</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.148762242594643</v>
+        <v>3.16984421920877</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.757476907156541</v>
+        <v>-3.722340279466329</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.189640357883214</v>
+        <v>1.203695008959299</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.718357486436683</v>
+        <v>0.7534941141268936</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.124002036921588</v>
+        <v>3.145084013535714</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.874018512261884</v>
+        <v>-3.838881884571672</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.1380994243528</v>
+        <v>1.152154075428885</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6018158813313401</v>
+        <v>0.6369525090215509</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.049152782370105</v>
+        <v>3.070234758984231</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.913942606844456</v>
+        <v>-3.878805979154244</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.127621082350438</v>
+        <v>1.141675733426523</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6018158813313401</v>
+        <v>0.6369525090215509</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.054644078200772</v>
+        <v>3.075726054814898</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.941723004745809</v>
+        <v>-3.906586377055597</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.128006124958436</v>
+        <v>1.142060776034521</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.574035483429987</v>
+        <v>0.6091721111201978</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.049473041228499</v>
+        <v>3.070555017842626</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.060103677475947</v>
+        <v>-4.024967049785735</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.919009575867034</v>
+        <v>0.9330642269431189</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5068176312790108</v>
+        <v>0.5419542589692216</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.847498049938567</v>
+        <v>2.868580026552693</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.168717755919278</v>
+        <v>-4.133581128229066</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9957136052089071</v>
+        <v>1.009768256284992</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5068176312790108</v>
+        <v>0.5419542589692216</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.967647710657773</v>
+        <v>2.988729687271899</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.133308717671135</v>
+        <v>-4.098172089980923</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.024390246610487</v>
+        <v>1.038444897686572</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5068176312790108</v>
+        <v>0.5419542589692216</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.982160736760096</v>
+        <v>3.003242713374222</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.094925055112984</v>
+        <v>-4.059788427422772</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.037163152976116</v>
+        <v>1.051217804052201</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.545201293837162</v>
+        <v>0.5803379215273727</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.002610375637355</v>
+        <v>3.023692352251481</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.917808725077818</v>
+        <v>-3.882672097387606</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.104738713835485</v>
+        <v>1.11879336491157</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.545201293837162</v>
+        <v>0.5803379215273727</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.999339404482657</v>
+        <v>3.020421381096783</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.962900969911364</v>
+        <v>-3.927764342221152</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.08738520766398</v>
+        <v>1.101439858740064</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4833052506677722</v>
+        <v>0.5184418783579829</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.962885170342936</v>
+        <v>2.983967146957062</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.783525548672596</v>
+        <v>-3.748388920982384</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.152922351465901</v>
+        <v>1.166977002541986</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6400820088384909</v>
+        <v>0.6752186365287016</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.050738200551781</v>
+        <v>3.071820177165908</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.828539762193202</v>
+        <v>-3.79340313450299</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.115724121389248</v>
+        <v>1.129778772465333</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6097331135238863</v>
+        <v>0.644869741214097</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.013336318694608</v>
+        <v>3.034418295308735</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.095544272465638</v>
+        <v>-4.060407644775426</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.01461387961922</v>
+        <v>1.028668530695305</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4153700754809377</v>
+        <v>0.4505067031711484</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.902410058207785</v>
+        <v>2.923492034821912</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.196742053902811</v>
+        <v>-4.161605426212598</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9733386889408522</v>
+        <v>0.987393340016937</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3469612619356185</v>
+        <v>0.3820978896258292</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.860568691977095</v>
+        <v>2.881650668591222</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.190231087288498</v>
+        <v>-4.155094459598286</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.973543037140894</v>
+        <v>0.9875976882169788</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3469612619356185</v>
+        <v>0.3820978896258292</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.858168653531412</v>
+        <v>2.879250630145538</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.171192959581201</v>
+        <v>-4.136056331890988</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9776830074320577</v>
+        <v>0.9917376585081428</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.288777650604424</v>
+        <v>0.3239142782946347</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.81978320594094</v>
+        <v>2.840865182555067</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.223708761856021</v>
+        <v>-4.188572134165809</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.07597108815632</v>
+        <v>1.090025739232405</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.288777650604424</v>
+        <v>0.3239142782946347</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.93907760757513</v>
+        <v>2.960159584189257</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.237575523189939</v>
+        <v>-4.202438895499727</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.071257712608886</v>
+        <v>1.085312363684971</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.250919733870601</v>
+        <v>0.2860563615608118</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.91719618652097</v>
+        <v>2.938278163135096</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.197092531267594</v>
+        <v>-4.161955903577382</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.09345943977475</v>
+        <v>1.107514090850835</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.250919733870601</v>
+        <v>0.2860563615608118</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.923204716917896</v>
+        <v>2.944286693532022</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.049349561032591</v>
+        <v>-4.014212933342379</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.050506849145951</v>
+        <v>1.064561500222036</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4187270911054842</v>
+        <v>0.4538637187956949</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.921839352536026</v>
+        <v>2.942921329150152</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.13317078230729</v>
+        <v>-4.098034154617078</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.019771982167552</v>
+        <v>1.033826633243637</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4187270911054842</v>
+        <v>0.4538637187956949</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.924632974067507</v>
+        <v>2.945714950681633</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.127018076254505</v>
+        <v>-4.091881448564293</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.022895412980324</v>
+        <v>1.03695006405641</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4248797971582685</v>
+        <v>0.4600164248484792</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.928986946090835</v>
+        <v>2.950068922704962</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.143827374405007</v>
+        <v>-4.108690746714795</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.015252170460234</v>
+        <v>1.029306821536319</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4080704990077668</v>
+        <v>0.4432071266979776</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.917981843940645</v>
+        <v>2.939063820554771</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.081529375628885</v>
+        <v>-4.046392747938673</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.106506923767504</v>
+        <v>1.120561574843589</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4533647632822089</v>
+        <v>0.4885013909724196</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.011493956302131</v>
+        <v>3.032575932916257</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.879739177963727</v>
+        <v>-3.844602550273515</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9895150045476941</v>
+        <v>1.003569655623779</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6513829554513633</v>
+        <v>0.686519583141574</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.93259687331775</v>
+        <v>2.953678849931877</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.930625890649922</v>
+        <v>-3.89548926295971</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.039450551795391</v>
+        <v>1.053505202871476</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6004962427651688</v>
+        <v>0.6356328704553795</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.972355078028209</v>
+        <v>2.993437054642335</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.844015148000115</v>
+        <v>-3.808878520309902</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.088722584971358</v>
+        <v>1.102777236047443</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.679121973970327</v>
+        <v>0.7142586016605378</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.034158252867348</v>
+        <v>3.055240229481474</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.904224446005399</v>
+        <v>-3.869087818315187</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.063174846593916</v>
+        <v>1.077229497670001</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6189126759650425</v>
+        <v>0.6540493036552533</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.996568654888848</v>
+        <v>3.017650631502975</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.855037797321048</v>
+        <v>-3.819901169630835</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.081341124107585</v>
+        <v>1.09539577518367</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6189126759650425</v>
+        <v>0.6540493036552533</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.995060272928777</v>
+        <v>3.016142249542904</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.810664665682479</v>
+        <v>-3.775528037992267</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.098953244198449</v>
+        <v>1.113007895274533</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6632858076036111</v>
+        <v>0.6984224352938219</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.021547019347354</v>
+        <v>3.042628995961481</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.833145016541364</v>
+        <v>-3.798008388851152</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.084354897993485</v>
+        <v>1.09840954906957</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6632858076036111</v>
+        <v>0.6984224352938219</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.015940813485945</v>
+        <v>3.037022790100071</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.785489285980308</v>
+        <v>-3.750352658290096</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.109798947245712</v>
+        <v>1.123853598321797</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7109415381646668</v>
+        <v>0.7460781658548775</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.050916008850383</v>
+        <v>3.071997985464509</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.684971127481553</v>
+        <v>-3.649834499791341</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.154898584019939</v>
+        <v>1.168953235096024</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8114596966634213</v>
+        <v>0.8465963243536321</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.11611927732436</v>
+        <v>3.137201253938487</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.669065798049201</v>
+        <v>-3.633929170358988</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.148015388268752</v>
+        <v>1.162070039344837</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7323470359541824</v>
+        <v>0.7674836636443931</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.055406353374689</v>
+        <v>3.076488329988816</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.624227396440803</v>
+        <v>-3.58909076875059</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.17004845152274</v>
+        <v>1.184103102598825</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7368904688990519</v>
+        <v>0.7720270965892626</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.06223011575224</v>
+        <v>3.083312092366366</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.643725852682811</v>
+        <v>-3.608589224992599</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.166410008657015</v>
+        <v>1.180464659733099</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6888058276191475</v>
+        <v>0.7239424553093583</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.037540270615375</v>
+        <v>3.058622247229501</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82668474540596</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.59952301559691</v>
+        <v>-3.564386387906698</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.189970746019212</v>
+        <v>1.204025397095297</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.733008664705048</v>
+        <v>0.7681452923952587</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.069941575394752</v>
+        <v>3.091023552008879</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.607082681433957</v>
+        <v>-3.571946053743745</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.185356880153641</v>
+        <v>1.199411531229726</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7878120687148673</v>
+        <v>0.8229486964050781</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.101233618269891</v>
+        <v>3.122315594884018</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.448791263894685</v>
+        <v>-3.413654636204473</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.299921212352389</v>
+        <v>1.313975863428474</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7878120687148673</v>
+        <v>0.8229486964050781</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.152481383452931</v>
+        <v>3.173563360067058</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.241149260260209</v>
+        <v>-3.206012632569997</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.381418718400433</v>
+        <v>1.395473369476518</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9954540723493435</v>
+        <v>1.030590700039554</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.27550729022787</v>
+        <v>3.296589266841996</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475142</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.190117167537681</v>
+        <v>-3.154980539847469</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.396779783727714</v>
+        <v>1.410834434803799</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.046486165071872</v>
+        <v>1.081622792762082</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.301074774099657</v>
+        <v>3.322156750713783</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404856</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.124892986410475</v>
+        <v>-3.089756358720263</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.440056860271301</v>
+        <v>1.454111511347386</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.111710346199077</v>
+        <v>1.146846973889288</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.357396686868685</v>
+        <v>3.378478663482812</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.087465966339341</v>
+        <v>-3.052329338649129</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.450988640599035</v>
+        <v>1.46504329167512</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.116961884228259</v>
+        <v>1.152098511918469</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.356508581985475</v>
+        <v>3.377590558599601</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992663</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.10757762237405</v>
+        <v>-3.072440994683837</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.444200770516392</v>
+        <v>1.458255421592477</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.127989229225678</v>
+        <v>1.163125856915889</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.364381781315167</v>
+        <v>3.385463757929293</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563629</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.079164359274166</v>
+        <v>-3.044027731583954</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.616123846777556</v>
+        <v>1.630178497853641</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.069013666479249</v>
+        <v>1.10415029416946</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.48955421468852</v>
+        <v>3.510636191302646</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957629</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.004382098249153</v>
+        <v>-2.969245470558941</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.766149660405379</v>
+        <v>1.780204311481464</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.143795927504262</v>
+        <v>1.178932555194472</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.654536480521345</v>
+        <v>3.675618457135471</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.978298013985345</v>
+        <v>-2.943161386295133</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.768291270124761</v>
+        <v>1.782345921200846</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.143795927504262</v>
+        <v>1.178932555194472</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.646244456535204</v>
+        <v>3.66732643314933</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.890420100876225</v>
+        <v>-2.855283473186013</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.801635630952189</v>
+        <v>1.815690282028273</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.259721569927613</v>
+        <v>1.294858197617824</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.713993037572994</v>
+        <v>3.73507501418712</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.881527639482941</v>
+        <v>-2.846391011792729</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.822747021236293</v>
+        <v>1.836801672312378</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.259721569927613</v>
+        <v>1.294858197617824</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.731547443299785</v>
+        <v>3.752629419913911</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.050003756452819</v>
+        <v>-3.014867128762607</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.747211621852926</v>
+        <v>1.761266272929011</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.231773734211032</v>
+        <v>1.266910361901243</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.706633789274421</v>
+        <v>3.727715765888547</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.603747563823379</v>
+        <v>-2.568610936133167</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.906983796092564</v>
+        <v>1.921038447168649</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.137055064541399</v>
+        <v>1.17219169223161</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.631072284660503</v>
+        <v>3.652154261274629</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632639</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.581026460140227</v>
+        <v>-2.545889832450015</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.90673626006273</v>
+        <v>1.920790911138814</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.137055064541399</v>
+        <v>1.17219169223161</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.621736307157407</v>
+        <v>3.642818283771533</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777676</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.710228273434269</v>
+        <v>-2.675091645744057</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.013961660596282</v>
+        <v>2.028016311672366</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.007853251247357</v>
+        <v>1.042989878937568</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.703121345032151</v>
+        <v>3.724203321646277</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.736102671908295</v>
+        <v>-2.700966044218083</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.040689723700318</v>
+        <v>2.054744374776403</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.052764859959098</v>
+        <v>1.087901487649309</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.767146132752842</v>
+        <v>3.788228109366969</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799967</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.729047981693121</v>
+        <v>-2.693911354002909</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.040186955775932</v>
+        <v>2.054241606852017</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.059819550174272</v>
+        <v>1.094956177864483</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.768054302871492</v>
+        <v>3.789136279485618</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.702096757366633</v>
+        <v>-2.666960129676421</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.060973599151269</v>
+        <v>2.075028250227354</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.074699896201991</v>
+        <v>1.109836523892202</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.786988664132865</v>
+        <v>3.808070640746991</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784111</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.723640985197421</v>
+        <v>-2.688504357507208</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.236459040163914</v>
+        <v>2.250513691239999</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.074699896201991</v>
+        <v>1.109836523892202</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.971091796277824</v>
+        <v>3.992173772891951</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.746049103002293</v>
+        <v>-2.71091247531208</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.219612487944958</v>
+        <v>2.233667139021043</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.074699896201991</v>
+        <v>1.109836523892202</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.963208491180818</v>
+        <v>3.984290467794944</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.774273338579893</v>
+        <v>-2.739136710889681</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.210376793263555</v>
+        <v>2.224431444339641</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.0926766486533</v>
+        <v>1.12781327634351</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.97604854220124</v>
+        <v>3.997130518815367</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161981</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.783714264468423</v>
+        <v>-2.748577636778211</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.262854140629991</v>
+        <v>2.276908791706076</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.215103766196691</v>
+        <v>1.250240393886902</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.105758530449123</v>
+        <v>4.126840507063249</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321638</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.872590895636897</v>
+        <v>-2.837454267946685</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.230194582707902</v>
+        <v>2.244249233783987</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.126227135028218</v>
+        <v>1.161363762718428</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.055323646293339</v>
+        <v>4.076405622907465</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.948920873237803</v>
+        <v>-2.91378424554759</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.197774404561315</v>
+        <v>2.2118290556374</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.126227135028218</v>
+        <v>1.161363762718428</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.053435459187114</v>
+        <v>4.074517435801241</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.042584817915344</v>
+        <v>-3.007448190225132</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.155129056293161</v>
+        <v>2.169183707369246</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.032563190350676</v>
+        <v>1.067699818040887</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.992057321983451</v>
+        <v>4.013139298597578</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.204153243442599</v>
+        <v>-3.169016615752387</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.088935696292411</v>
+        <v>2.102990347368496</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9057802665527969</v>
+        <v>0.9409168942430074</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.914421577914876</v>
+        <v>3.935503554529003</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389354</v>
+        <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.312453905312719</v>
+        <v>-3.277317277622506</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.058688838410282</v>
+        <v>2.072743489486367</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9057802665527969</v>
+        <v>0.9409168942430074</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.927494984780795</v>
+        <v>3.948576961394921</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.330257877033463</v>
+        <v>-3.29512124934325</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.043572446504924</v>
+        <v>2.057627097581009</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8352456436475957</v>
+        <v>0.8703822713378062</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.877179407820614</v>
+        <v>3.898261384434741</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006978</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.358158664142936</v>
+        <v>-3.323022036452723</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.030936172788137</v>
+        <v>2.044990823864222</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8006487195046609</v>
+        <v>0.8357853471948714</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.854945294461855</v>
+        <v>3.876027271075982</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.68489577878739</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.382727161643471</v>
+        <v>-3.445548139155617</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.017873217765122</v>
+        <v>1.992744826760263</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7760802220041259</v>
+        <v>0.7132592444919775</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.836968639938733</v>
+        <v>3.799276053431444</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.613241657829059</v>
+        <v>-3.676062635341206</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.99237337888139</v>
+        <v>1.967244987876531</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5455657258185371</v>
+        <v>0.4827447483063888</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.765365901817884</v>
+        <v>3.727673315310595</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814668</v>
+        <v>3.640750087814667</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.961986743053503</v>
+        <v>-4.02480772056565</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.99318706379346</v>
+        <v>1.968058672788601</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4368177718996393</v>
+        <v>0.373996794387491</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.840428848468392</v>
+        <v>3.802736261961103</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.115973160829643</v>
+        <v>-4.17879413834179</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.000572765828643</v>
+        <v>1.975444374823784</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4368177718996393</v>
+        <v>0.373996794387491</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.909409117614032</v>
+        <v>3.871716531106743</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.065451257001977</v>
+        <v>-4.128272234514125</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.00683272947983</v>
+        <v>1.981704338474972</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4368177718996393</v>
+        <v>0.373996794387491</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.895460319734152</v>
+        <v>3.857767733226864</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609758</v>
+        <v>3.656332733609756</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.317926411009702</v>
+        <v>-4.380747388521849</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.917713156932155</v>
+        <v>1.892584765927296</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4368177718996393</v>
+        <v>0.373996794387491</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.907330808789566</v>
+        <v>3.869638222282278</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973162</v>
+        <v>3.67402853597316</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.610822167489114</v>
+        <v>-4.673643145001261</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.801765388859334</v>
+        <v>1.776636997854475</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4368177718996393</v>
+        <v>0.373996794387491</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.90854134330851</v>
+        <v>3.870848756801221</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.797486295623922</v>
+        <v>-4.860307273136069</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.731221479832732</v>
+        <v>1.706093088827873</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4100788010750794</v>
+        <v>0.3472578235629311</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.896619703041096</v>
+        <v>3.858927116533807</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916205</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.943506982537884</v>
+        <v>-5.006327960050031</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.667891057803336</v>
+        <v>1.642762666798478</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4009957092812225</v>
+        <v>0.3381747317690741</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.886247700700971</v>
+        <v>3.848555114193682</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830332</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.035220991647469</v>
+        <v>-5.098041969159617</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.793409510858547</v>
+        <v>1.768281119853687</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4009957092812225</v>
+        <v>0.3381747317690741</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.048451757400015</v>
+        <v>4.010759170892726</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071553</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.066872650707438</v>
+        <v>-5.129693628219586</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.775595485198373</v>
+        <v>1.750467094193514</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3958272520367823</v>
+        <v>0.3330062745246339</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.040197321017165</v>
+        <v>4.002504734509876</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586815</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.148807468976321</v>
+        <v>-5.211628446488469</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.753050975459311</v>
+        <v>1.727922584454451</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3858925064497021</v>
+        <v>0.3230715289375538</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.044465891233409</v>
+        <v>4.006773304726119</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.250783591224729</v>
+        <v>-5.313604568736877</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.72118616501585</v>
+        <v>1.696057774010991</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2839163842012945</v>
+        <v>0.2210954066891462</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.992205856340266</v>
+        <v>3.954513269832977</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231808</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.140777307747507</v>
+        <v>-5.203598285259655</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.757341565650914</v>
+        <v>1.732213174646055</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3071209561185697</v>
+        <v>0.2442999786064214</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.998281486734807</v>
+        <v>3.960588900227518</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.997717732006581</v>
+        <v>-5.060538709518729</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.818815406669259</v>
+        <v>1.7936870156644</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.315134382708549</v>
+        <v>0.2523134051964007</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.007339553410769</v>
+        <v>3.969646966903479</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.672748950487352</v>
+        <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.696900539264362</v>
+        <v>-4.759091984046892</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.79363231046786</v>
+        <v>1.921526588735671</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6159515754507683</v>
+        <v>0.5537601306682379</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.042319895757814</v>
+        <v>4.157775885069118</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.673720128240063</v>
+        <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.721490783499546</v>
+        <v>-4.783682228282076</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.784767390526497</v>
+        <v>1.912661668794308</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6159515754507683</v>
+        <v>0.5537601306682379</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.043291073510524</v>
+        <v>4.158747062821829</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.674563032619818</v>
+        <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.670452407493026</v>
+        <v>-4.732643852275555</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.806025645308861</v>
+        <v>1.933919923576672</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6159515754507683</v>
+        <v>0.5537601306682379</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.044133977890279</v>
+        <v>4.159589967201584</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969545</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.693601131493964</v>
+        <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.629313112626395</v>
+        <v>-4.691504557408924</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.841519462129658</v>
+        <v>1.969413740397469</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6570908703173991</v>
+        <v>0.5948994255348687</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.087855653684404</v>
+        <v>4.203311642995708</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700481</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.509785127617898</v>
+        <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.532678200607755</v>
+        <v>-4.594869645390284</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.696357423061049</v>
+        <v>1.82425170132886</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.753725782336039</v>
+        <v>0.6915343375535087</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.962020597019522</v>
+        <v>4.077476586330826</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077642</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.513287171691863</v>
+        <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.663258935138598</v>
+        <v>-4.725450379921127</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.647627173322676</v>
+        <v>1.775521451590487</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6231450478051965</v>
+        <v>0.5609536030226662</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.887174200374981</v>
+        <v>4.002630189686285</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.497713990767945</v>
+        <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.498762600947636</v>
+        <v>-4.560954045730165</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.697852526075144</v>
+        <v>1.825746804342954</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7876413819961584</v>
+        <v>0.725449937213628</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.97029881996564</v>
+        <v>4.085754809276945</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.496901701204375</v>
+        <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.421663999405763</v>
+        <v>-4.483855444188293</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.727879677128322</v>
+        <v>1.855773955396133</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7876413819961584</v>
+        <v>0.725449937213628</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.969486530402071</v>
+        <v>4.084942519713374</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147912</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.506770480329447</v>
+        <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.432049194295653</v>
+        <v>-4.494240639078182</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.733594378297439</v>
+        <v>1.86148865656525</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7772561871062691</v>
+        <v>0.7150647423237387</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.973124192593209</v>
+        <v>4.088580181904513</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735284</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.577607486105872</v>
+        <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.450637353017878</v>
+        <v>-4.512828797800407</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.796996120584974</v>
+        <v>1.924890398852785</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7586680283840437</v>
+        <v>0.6964765836015134</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.032808303136299</v>
+        <v>4.148264292447603</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496556</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.574476496924171</v>
+        <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.450935899713913</v>
+        <v>-4.513127344496443</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.793745712724858</v>
+        <v>1.921639990992669</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7583694816880078</v>
+        <v>0.6961780369054775</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.029498185936976</v>
+        <v>4.14495417524828</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108859</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.579007391863562</v>
+        <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.350112766023486</v>
+        <v>-4.412304210806015</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.838605861140421</v>
+        <v>1.966500139408232</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.7708336971723616</v>
+        <v>0.7086422523898314</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.041507610166979</v>
+        <v>4.156963599478284</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812147</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.579136645342106</v>
+        <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.159331405271079</v>
+        <v>-4.221522850053608</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.915047658919927</v>
+        <v>2.042941937187738</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.961615057924769</v>
+        <v>0.8994236131422387</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.156105680096967</v>
+        <v>4.271561669408271</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906083</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.558973491079702</v>
+        <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.052368047421657</v>
+        <v>-4.114559492204187</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.937669847797292</v>
+        <v>2.065564126065103</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.020079665884571</v>
+        <v>0.9578882211020402</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.171021290610445</v>
+        <v>4.286477279921749</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912988</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.593940427691761</v>
+        <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.997037459519895</v>
+        <v>-4.059228904302424</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.994769019570055</v>
+        <v>2.122663297837866</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.075410253786333</v>
+        <v>1.013218809003802</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.23918657996356</v>
+        <v>4.354642569274865</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539897</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.587626995593198</v>
+        <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.984983332606932</v>
+        <v>-4.047174777389461</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.993277238236678</v>
+        <v>2.121171516504489</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.087464380699295</v>
+        <v>1.025272935916765</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.240105624012775</v>
+        <v>4.35556161332408</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.589507625777334</v>
+        <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.026138452175154</v>
+        <v>-4.088329896957682</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.978695820593526</v>
+        <v>2.106590098861337</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.046309261131074</v>
+        <v>0.9841178163485442</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.217293182455979</v>
+        <v>4.332749171767284</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382923</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.602358651655217</v>
+        <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.958089889483624</v>
+        <v>-4.020281334266152</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.01876627154802</v>
+        <v>2.146660549815831</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.114357823822604</v>
+        <v>1.052166379040074</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.27097334594878</v>
+        <v>4.386429335260084</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013431</v>
+        <v>3.645256780013426</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.622561321828811</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.189690282653125</v>
+        <v>-4.251881727435653</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.946328784453814</v>
+        <v>2.074223062721625</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.114357823822604</v>
+        <v>1.052166379040074</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.291176016122374</v>
+        <v>4.406632005433679</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498971</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.606167557895693</v>
+        <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.239741828182344</v>
+        <v>-4.301933272964872</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.909914402309008</v>
+        <v>2.037808680576819</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.114357823822604</v>
+        <v>1.052166379040074</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.274782252189256</v>
+        <v>4.39023824150056</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.6700487028001</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.566419471489159</v>
+        <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.414848660758789</v>
+        <v>-4.477040105541317</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.800123582871897</v>
+        <v>1.928017861139708</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.114357823822604</v>
+        <v>1.052166379040074</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.235034165782722</v>
+        <v>4.350490155094027</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745573148660852</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.5734420904861</v>
+        <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.383562640218334</v>
+        <v>-4.445754085000861</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.819660610085019</v>
+        <v>1.94755488835283</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.14564384436306</v>
+        <v>1.083452399580529</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.260828397103936</v>
+        <v>4.37628438641524</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.672613090059004</v>
+        <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.230537248105049</v>
+        <v>-4.292728692887577</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.980041766503237</v>
+        <v>2.107936044771049</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.298669236476344</v>
+        <v>1.236477791693813</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.45181463194481</v>
+        <v>4.567270621256115</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.860079314967297</v>
+        <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.25884456197832</v>
+        <v>-4.321036006760847</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.156185065862221</v>
+        <v>2.284079344130033</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.298669236476344</v>
+        <v>1.236477791693813</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.639280856853103</v>
+        <v>4.754736846164407</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.829482266321379</v>
+        <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.425437787091842</v>
+        <v>-4.48762923187437</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.058950727170895</v>
+        <v>2.186845005438706</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.132076011362821</v>
+        <v>1.069884566580291</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.508727873139073</v>
+        <v>4.624183862450376</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70818251928565</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.833158668983097</v>
+        <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.402401993730276</v>
+        <v>-4.464593438512804</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.071841447177239</v>
+        <v>2.19973572544505</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.132076011362821</v>
+        <v>1.069884566580291</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.51240427580079</v>
+        <v>4.627860265112094</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399472</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.830776724106592</v>
+        <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.373156013274579</v>
+        <v>-4.435347458057107</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.081157894483013</v>
+        <v>2.209052172750824</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.132076011362821</v>
+        <v>1.069884566580291</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.510022330924286</v>
+        <v>4.625478320235589</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256375</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.828069963264227</v>
+        <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.480081561152431</v>
+        <v>-4.542273005934958</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.035680914489508</v>
+        <v>2.163575192757319</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.02515046348497</v>
+        <v>0.9629590187024396</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.443160241355209</v>
+        <v>4.558616230666513</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701005</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.829498765407461</v>
+        <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.625100119659679</v>
+        <v>-4.687291564442207</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.979102293229842</v>
+        <v>2.106996571497653</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.8801319049777214</v>
+        <v>0.8179404601951911</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.357577908394094</v>
+        <v>4.473033897705398</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687016</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.929430004665214</v>
+        <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.743441885444397</v>
+        <v>-4.805633330226924</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.031696826173708</v>
+        <v>2.159591104441519</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.8908179435406115</v>
+        <v>0.8286264987580811</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.463920770789581</v>
+        <v>4.579376760100885</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.927215701791153</v>
+        <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.794852307765105</v>
+        <v>-4.857043752547632</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.008918354371364</v>
+        <v>2.136812632639175</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.8908179435406115</v>
+        <v>0.8286264987580811</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.46170646791552</v>
+        <v>4.577162457226824</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437334</v>
+        <v>3.704757949437331</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.927118829865442</v>
+        <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.874271758972856</v>
+        <v>-4.936463203755384</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.977053701962553</v>
+        <v>2.104947980230364</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.8908179435406115</v>
+        <v>0.8286264987580811</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.46160959598981</v>
+        <v>4.577065585301114</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298401</v>
+        <v>3.736804952298398</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.927112723423486</v>
+        <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.969734756890074</v>
+        <v>-5.031926201672602</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.938862396353709</v>
+        <v>2.06675667462152</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.8908179435406115</v>
+        <v>0.8286264987580811</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.461603489547853</v>
+        <v>4.577059478859157</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218004</v>
+        <v>3.715372960218</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.925209119986096</v>
+        <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.905358846039359</v>
+        <v>-4.967550290821887</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.962709157256605</v>
+        <v>2.090603435524417</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.9551938543913266</v>
+        <v>0.8930024096087963</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.498325432620892</v>
+        <v>4.613781421932197</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73608941335354</v>
+        <v>3.736089413353535</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.930942937733823</v>
+        <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.960728008171553</v>
+        <v>-5.02291945295408</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.946295310151455</v>
+        <v>2.074189588419266</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.9551938543913266</v>
+        <v>0.8930024096087963</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.504059250368619</v>
+        <v>4.619515239679924</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113283</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.930481301076755</v>
+        <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.00616578800238</v>
+        <v>-5.068357232784908</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.927658561562056</v>
+        <v>2.055552839829867</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9123488637131669</v>
+        <v>0.8501574189306367</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.477890619304655</v>
+        <v>4.59334660861596</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113692</v>
+        <v>3.790272500113687</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.950355693927074</v>
+        <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.917958953854802</v>
+        <v>-4.980150398637329</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.982815688071406</v>
+        <v>2.110709966339217</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9123488637131669</v>
+        <v>0.8501574189306367</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.497765012154974</v>
+        <v>4.613221001466279</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.934056394451802</v>
+        <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.811923958649492</v>
+        <v>-4.87411540343202</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.008930386678258</v>
+        <v>2.136824664946069</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9123488637131669</v>
+        <v>0.8501574189306367</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.481465712679702</v>
+        <v>4.596921701991007</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307673</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.936487343915847</v>
+        <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.628712295516397</v>
+        <v>-4.690903740298925</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.084646001395541</v>
+        <v>2.212540279663353</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9123488637131669</v>
+        <v>0.8501574189306367</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.483896662143747</v>
+        <v>4.599352651455052</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.902278529763737</v>
+        <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.556990848502546</v>
+        <v>-4.619182293285074</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.079125766048971</v>
+        <v>2.207020044316782</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.9840703107270176</v>
+        <v>0.9218788659444873</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.492720716199948</v>
+        <v>4.608176705511251</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394116</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.849194275684909</v>
+        <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.53461782289484</v>
+        <v>-4.596809267677368</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.034990722213226</v>
+        <v>2.162885000481037</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.9953260618399191</v>
+        <v>0.9331346170573889</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.44638991278886</v>
+        <v>4.561845902100164</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456733</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.034392480570264</v>
+        <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.567634118805585</v>
+        <v>-4.629825563588112</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.206982408734283</v>
+        <v>2.334876687002094</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9258886851731676</v>
+        <v>0.8636972403906373</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.589925691674165</v>
+        <v>4.705381680985469</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71376253688368</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.026313706398513</v>
+        <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.556106483155976</v>
+        <v>-4.618297927938504</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.203514688822375</v>
+        <v>2.331408967090187</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.98488934337453</v>
+        <v>0.9226978985919998</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.617247312423231</v>
+        <v>4.732703301734536</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236301</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.029981818920302</v>
+        <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.653447984498345</v>
+        <v>-4.715639429280873</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.168246200807216</v>
+        <v>2.296140479075028</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.9404691612090417</v>
+        <v>0.8782777164265114</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.594263315645727</v>
+        <v>4.709719304957031</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427687</v>
+        <v>3.705201079427683</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.03123290111314</v>
+        <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.739304013838312</v>
+        <v>-4.801495458620839</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.135154871264068</v>
+        <v>2.263049149531879</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.8980930919829067</v>
+        <v>0.8359016472003764</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.570088756302884</v>
+        <v>4.685544745614188</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610382</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.013652102933642</v>
+        <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.748140811254431</v>
+        <v>-4.810332256036959</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.114039354118122</v>
+        <v>2.241933632385933</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.8906509193415559</v>
+        <v>0.8284594745590257</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.548042654538575</v>
+        <v>4.66349864384988</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.715544411667454</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.023816613978691</v>
+        <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.83952337381989</v>
+        <v>-4.901714818602417</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.087650840136988</v>
+        <v>2.215545118404799</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.7992683567760976</v>
+        <v>0.7370769119935674</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.50337762804435</v>
+        <v>4.618833617355654</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889194</v>
+        <v>3.67397837488919</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.125944871802959</v>
+        <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.827816655832883</v>
+        <v>-4.890008100615411</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.194461785156059</v>
+        <v>2.32235606342387</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.810975074763104</v>
+        <v>0.7487836299805738</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.612529916660822</v>
+        <v>4.727985905972126</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940957</v>
+        <v>3.682476099409566</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.128977210534364</v>
+        <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.728153151749221</v>
+        <v>-4.790344596531749</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.237359525520929</v>
+        <v>2.36525380378874</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.8741621579667905</v>
+        <v>0.8119707131842603</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.653474505314438</v>
+        <v>4.768930494625743</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452574</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.341882043812422</v>
+        <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.738469249915573</v>
+        <v>-4.800660694698101</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.446137919532446</v>
+        <v>2.574032197800257</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.8741621579667905</v>
+        <v>0.8119707131842603</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.866379338592496</v>
+        <v>4.981835327903801</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762291</v>
+        <v>3.623960959762286</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.341060710724512</v>
+        <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.7383752818982</v>
+        <v>-4.800566726680728</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.445354173651484</v>
+        <v>2.573248451919296</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.8745320193141085</v>
+        <v>0.8123405745315783</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.865779922312977</v>
+        <v>4.981235911624282</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988022</v>
+        <v>3.633213467988017</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.335292696668866</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.745594106098045</v>
+        <v>-4.807785550880572</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.436698629915901</v>
+        <v>2.564592908183712</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.8745320193141085</v>
+        <v>0.8123405745315783</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.860011908257331</v>
+        <v>4.975467897568636</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.335292696668866</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.744645682980006</v>
+        <v>-4.806837127762534</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.437077999163116</v>
+        <v>2.564972277430927</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.8745320193141085</v>
+        <v>0.8123405745315783</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.860011908257331</v>
+        <v>4.975467897568636</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.673485397508225</v>
+        <v>3.673485397508226</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.348020304649958</v>
+        <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.049761501573697</v>
+        <v>-4.963905586018157</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.327759279706732</v>
+        <v>2.51487250210977</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.8745320193141085</v>
+        <v>0.8123405745315783</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.872739516238423</v>
+        <v>4.988195505549728</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.504113543696956</v>
+        <v>3.82112428978796</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.349966303074345</v>
+        <v>4.460294955256545</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.991639088719591</v>
+        <v>-4.979122560675393</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.352954243272761</v>
+        <v>2.468289506672641</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.8407057716246445</v>
+        <v>0.8123405745315783</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.854389766049133</v>
+        <v>4.947699299975493</v>
       </c>
     </row>
   </sheetData>
